--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -77,7 +77,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -92,11 +92,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,13 +133,6 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -617,13 +605,13 @@
         <v>4758</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>13744</v>
+        <v>23130</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11376</v>
+        <v>20762</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>10098</v>
+        <v>15004</v>
       </c>
       <c r="G5" s="8">
         <f>D5/1000</f>
@@ -642,23 +630,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T37</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>140.75</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>5173</v>
+        <v>3607</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>13118</v>
+        <v>22685</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>10542</v>
+        <v>20893</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>9032</v>
+        <v>16250</v>
       </c>
       <c r="G6" s="15">
         <f>D6/1000</f>
@@ -677,23 +665,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T-05A</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>175.27</v>
+        <v>140.75</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5486</v>
+        <v>5173</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>13106</v>
+        <v>22531</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>10484</v>
+        <v>19955</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>9226</v>
+        <v>15747</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -712,23 +700,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-05S</t>
+          <t>T-05A</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>71.5</v>
+        <v>175.27</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4054</v>
+        <v>5486</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>13102</v>
+        <v>22492</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>11081</v>
+        <v>19870</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>9806</v>
+        <v>13634</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -747,23 +735,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T-06B</t>
+          <t>T-05S</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>144.9</v>
+        <v>71.5</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4944</v>
+        <v>4054</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>12547</v>
+        <v>22488</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>10294</v>
+        <v>20467</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9953</v>
+        <v>14361</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -782,23 +770,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T-16B</t>
+          <t>T33</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>66.45999999999999</v>
+        <v>149.61</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>3913</v>
+        <v>5003</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>12433</v>
+        <v>22356</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>10707</v>
+        <v>20129</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>10256</v>
+        <v>15887</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -817,23 +805,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>T37</t>
+          <t>T38</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>67.45999999999999</v>
+        <v>140.69</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3607</v>
+        <v>4981</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>12072</v>
+        <v>21968</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>10281</v>
+        <v>19497</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>8100</v>
+        <v>14856</v>
       </c>
       <c r="G11" s="8">
         <f>D11/1000</f>
@@ -852,23 +840,23 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>T-16A</t>
+          <t>T-06B</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>56.03</v>
+        <v>144.9</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>3746</v>
+        <v>4944</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>11982</v>
+        <v>21954</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>10297</v>
+        <v>19708</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>9900</v>
+        <v>15014</v>
       </c>
       <c r="G12" s="15">
         <f>D12/1000</f>
@@ -887,23 +875,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-16B</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>302.63</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>7372</v>
+        <v>3913</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>11974</v>
+        <v>21847</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>8397</v>
+        <v>20121</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7210</v>
+        <v>16110</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -922,23 +910,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>T33</t>
+          <t>T-16A</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>149.61</v>
+        <v>56.03</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>5003</v>
+        <v>3746</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>11744</v>
+        <v>21395</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>9517</v>
+        <v>19710</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>7372</v>
+        <v>15750</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -957,23 +945,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-15C</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>136.18</v>
+        <v>302.63</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4817</v>
+        <v>7372</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>11598</v>
+        <v>21360</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>9355</v>
+        <v>17783</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8991</v>
+        <v>11657</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -992,23 +980,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-06A</t>
+          <t>T34</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>132.93</v>
+        <v>131.51</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4758</v>
+        <v>4710</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>11549</v>
+        <v>21142</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>9342</v>
+        <v>18784</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>9006</v>
+        <v>14642</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1027,23 +1015,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-15C</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>136.18</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>3691</v>
+        <v>4817</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>11443</v>
+        <v>21011</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9772</v>
+        <v>18769</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>7315</v>
+        <v>14928</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1062,23 +1050,23 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>T38</t>
+          <t>T-06A</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>140.69</v>
+        <v>132.93</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>4981</v>
+        <v>4758</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11356</v>
+        <v>20952</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>8884</v>
+        <v>18755</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>6809</v>
+        <v>14217</v>
       </c>
       <c r="G18" s="15">
         <f>D18/1000</f>
@@ -1097,23 +1085,23 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>115.23</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4528</v>
+        <v>3691</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>10706</v>
+        <v>20857</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>8455</v>
+        <v>19186</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>6961</v>
+        <v>15125</v>
       </c>
       <c r="G19" s="8">
         <f>D19/1000</f>
@@ -1132,23 +1120,23 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T-07B</t>
+          <t>T31</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>53.96</v>
+        <v>239.17</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>3674</v>
+        <v>6359</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>10628</v>
+        <v>20685</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>8967</v>
+        <v>17519</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>8626</v>
+        <v>15489</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1167,23 +1155,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T34</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>131.51</v>
+        <v>115.23</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>4710</v>
+        <v>4528</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>10530</v>
+        <v>20120</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>8172</v>
+        <v>17868</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>6345</v>
+        <v>14106</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1202,23 +1190,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>T-07A</t>
+          <t>T-07B</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>254.67</v>
+        <v>53.96</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>6809</v>
+        <v>3674</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>10260</v>
+        <v>20029</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>7258</v>
+        <v>18380</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>6925</v>
+        <v>13875</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1247,13 +1235,13 @@
         <v>4103</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>10258</v>
+        <v>19671</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8464</v>
+        <v>17878</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7999</v>
+        <v>14168</v>
       </c>
       <c r="G23" s="8">
         <f>D23/1000</f>
@@ -1272,23 +1260,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-07A</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>150.72</v>
+        <v>254.67</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>5638</v>
+        <v>6809</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>10084</v>
+        <v>19667</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>7284</v>
+        <v>16672</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>5766</v>
+        <v>12367</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1307,23 +1295,23 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>T-19</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>239.17</v>
+        <v>150.72</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6359</v>
+        <v>5638</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>10073</v>
+        <v>19497</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>6907</v>
+        <v>16697</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>6454</v>
+        <v>13240</v>
       </c>
       <c r="G25" s="8">
         <f>D25/1000</f>
@@ -1352,13 +1340,13 @@
         <v>7339</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>9933</v>
+        <v>19319</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>6394</v>
+        <v>15780</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>5324</v>
+        <v>9892</v>
       </c>
       <c r="G26" s="15">
         <f>D26/1000</f>
@@ -1387,13 +1375,13 @@
         <v>5278</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>9733</v>
+        <v>19146</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7258</v>
+        <v>16672</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>6900</v>
+        <v>13180</v>
       </c>
       <c r="G27" s="8">
         <f>D27/1000</f>
@@ -1422,13 +1410,13 @@
         <v>6729</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>8605</v>
+        <v>18018</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>5253</v>
+        <v>14666</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>4896</v>
+        <v>11611</v>
       </c>
       <c r="G28" s="15">
         <f>D28/1000</f>
@@ -1457,13 +1445,13 @@
         <v>7008</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>8572</v>
+        <v>17974</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>5253</v>
+        <v>14666</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>4931</v>
+        <v>10680</v>
       </c>
       <c r="G29" s="8">
         <f>D29/1000</f>
@@ -1482,23 +1470,23 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>299.8</v>
+        <v>43.67</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>7001</v>
+        <v>3710</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>7886</v>
+        <v>17936</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>4386</v>
+        <v>16107</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>3565</v>
+        <v>14089</v>
       </c>
       <c r="G30" s="15">
         <f>D30/1000</f>
@@ -1517,23 +1505,23 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>43.67</v>
+        <v>201.87</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>3710</v>
+        <v>6413</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>7323</v>
+        <v>17482</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>5495</v>
+        <v>14382</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>5086</v>
+        <v>11986</v>
       </c>
       <c r="G31" s="8">
         <f>D31/1000</f>
@@ -1552,23 +1540,23 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>201.87</v>
+        <v>299.8</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>6413</v>
+        <v>7001</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>7050</v>
+        <v>17272</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>4082</v>
+        <v>13772</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>2918</v>
+        <v>8178</v>
       </c>
       <c r="G32" s="15">
         <f>D32/1000</f>
@@ -1597,13 +1585,13 @@
         <v>7000</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>6570</v>
+        <v>15968</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>3251</v>
+        <v>12664</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>2954</v>
+        <v>9125</v>
       </c>
       <c r="G33" s="8">
         <f>D33/1000</f>
@@ -1622,23 +1610,23 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>196.28</v>
+        <v>58.7</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>6359</v>
+        <v>4507</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>6265</v>
+        <v>15912</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>3251</v>
+        <v>13667</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>2898</v>
+        <v>11674</v>
       </c>
       <c r="G34" s="15">
         <f>D34/1000</f>
@@ -1657,23 +1645,23 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T-01C</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>302.68</v>
+        <v>196.28</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>6953</v>
+        <v>6359</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>5885</v>
+        <v>15834</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>2415</v>
+        <v>12664</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>2263</v>
+        <v>10196</v>
       </c>
       <c r="G35" s="8">
         <f>D35/1000</f>
@@ -1692,23 +1680,23 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-22A</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>58.7</v>
+        <v>131.93</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>4507</v>
+        <v>5328</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>5473</v>
+        <v>15638</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>3353</v>
+        <v>13233</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2582</v>
+        <v>11332</v>
       </c>
       <c r="G36" s="15">
         <f>D36/1000</f>
@@ -1727,23 +1715,23 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T-22A</t>
+          <t>T-20</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>131.93</v>
+        <v>140.68</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>5328</v>
+        <v>4965</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>5181</v>
+        <v>15418</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>2621</v>
+        <v>12956</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>2422</v>
+        <v>10711</v>
       </c>
       <c r="G37" s="8">
         <f>D37/1000</f>
@@ -1762,23 +1750,23 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-01C</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>140.68</v>
+        <v>302.68</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>4965</v>
+        <v>6953</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>5120</v>
+        <v>15271</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>2657</v>
+        <v>11801</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1940</v>
+        <v>6693</v>
       </c>
       <c r="G38" s="15">
         <f>D38/1000</f>
@@ -1797,23 +1785,23 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>T-01B</t>
+          <t>T-20S</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>65</v>
+        <v>58.94</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>3845</v>
+        <v>3772</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4697</v>
+        <v>14434</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2822</v>
+        <v>12558</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>2468</v>
+        <v>10512</v>
       </c>
       <c r="G39" s="8">
         <f>D39/1000</f>
@@ -1832,23 +1820,23 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T-10B</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>177.61</v>
+        <v>174.68</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>5367</v>
+        <v>5276</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>4561</v>
+        <v>14095</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>2068</v>
+        <v>11481</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>1812</v>
+        <v>9459</v>
       </c>
       <c r="G40" s="15">
         <f>D40/1000</f>
@@ -1867,23 +1855,23 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>T-29</t>
+          <t>T-01B</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>75.31</v>
+        <v>65</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>3891</v>
+        <v>3845</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>4495</v>
+        <v>14083</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>2743</v>
+        <v>12208</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>2237</v>
+        <v>6902</v>
       </c>
       <c r="G41" s="8">
         <f>D41/1000</f>
@@ -1902,23 +1890,23 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>T-01A</t>
+          <t>T-21</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>60.51</v>
+        <v>60.19</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>3703</v>
+        <v>3809</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>4265</v>
+        <v>14051</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>2422</v>
+        <v>12160</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>2273</v>
+        <v>10313</v>
       </c>
       <c r="G42" s="15">
         <f>D42/1000</f>
@@ -1937,23 +1925,23 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-10B</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>174.68</v>
+        <v>177.61</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>5276</v>
+        <v>5367</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4246</v>
+        <v>13969</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>2068</v>
+        <v>11481</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>1708</v>
+        <v>8285</v>
       </c>
       <c r="G43" s="8">
         <f>D43/1000</f>
@@ -1972,23 +1960,23 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>T-20S</t>
+          <t>T-21A</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>58.94</v>
+        <v>124</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>3772</v>
+        <v>4814</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>4135</v>
+        <v>13916</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>2258</v>
+        <v>11664</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>1598</v>
+        <v>9977</v>
       </c>
       <c r="G44" s="15">
         <f>D44/1000</f>
@@ -2007,23 +1995,23 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>T-21</t>
+          <t>T-01A</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>60.19</v>
+        <v>60.51</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>3809</v>
+        <v>3703</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3751</v>
+        <v>13651</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1846</v>
+        <v>11808</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1281</v>
+        <v>6700</v>
       </c>
       <c r="G45" s="8">
         <f>D45/1000</f>
@@ -2042,23 +2030,23 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>T-28</t>
+          <t>T-12S</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>88.51000000000001</v>
+        <v>59.61</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>3848</v>
+        <v>3784</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>3511</v>
+        <v>12948</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>1594</v>
+        <v>11072</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>1229</v>
+        <v>9228</v>
       </c>
       <c r="G46" s="15">
         <f>D46/1000</f>
@@ -2075,60 +2063,60 @@
       <c r="J46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>T-21A</t>
-        </is>
-      </c>
-      <c r="B47" s="19" t="n">
-        <v>124</v>
-      </c>
-      <c r="C47" s="20" t="n">
-        <v>4814</v>
-      </c>
-      <c r="D47" s="21" t="n">
-        <v>3454</v>
-      </c>
-      <c r="E47" s="21" t="n">
-        <v>1052</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>922</v>
-      </c>
-      <c r="G47" s="22">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>T-10S</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>3801</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>12767</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>11069</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>8017</v>
+      </c>
+      <c r="G47" s="8">
         <f>D47/1000</f>
         <v/>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="8">
         <f>E47/1000</f>
         <v/>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="9">
         <f>IFERROR(D47/F47,"")</f>
         <v/>
       </c>
-      <c r="J47" s="24" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>T-10S</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>60.87</v>
+        <v>59.79</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>3801</v>
+        <v>3770</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>3368</v>
+        <v>12552</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>1656</v>
+        <v>10674</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>1426</v>
+        <v>9014</v>
       </c>
       <c r="G48" s="15">
         <f>D48/1000</f>
@@ -2147,23 +2135,23 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>T-12S</t>
+          <t>T-10A</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>59.61</v>
+        <v>80.13</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>3784</v>
+        <v>4466</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>3094</v>
+        <v>12363</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1659</v>
+        <v>10156</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>1302</v>
+        <v>7792</v>
       </c>
       <c r="G49" s="8">
         <f>D49/1000</f>
@@ -2180,95 +2168,95 @@
       <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>T-10A</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n">
-        <v>80.13</v>
-      </c>
-      <c r="C50" s="20" t="n">
-        <v>4466</v>
-      </c>
-      <c r="D50" s="21" t="n">
-        <v>2970</v>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>747</v>
-      </c>
-      <c r="F50" s="21" t="n">
-        <v>704</v>
-      </c>
-      <c r="G50" s="22">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>T-11A</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>113.78</v>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>4554</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>12305</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>10165</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>8753</v>
+      </c>
+      <c r="G50" s="15">
         <f>D50/1000</f>
         <v/>
       </c>
-      <c r="H50" s="22">
+      <c r="H50" s="15">
         <f>E50/1000</f>
         <v/>
       </c>
-      <c r="I50" s="23">
+      <c r="I50" s="16">
         <f>IFERROR(D50/F50,"")</f>
         <v/>
       </c>
-      <c r="J50" s="24" t="inlineStr"/>
+      <c r="J50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>T-11</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="C51" s="20" t="n">
-        <v>3770</v>
-      </c>
-      <c r="D51" s="21" t="n">
-        <v>2690</v>
-      </c>
-      <c r="E51" s="21" t="n">
-        <v>1261</v>
-      </c>
-      <c r="F51" s="21" t="n">
-        <v>893</v>
-      </c>
-      <c r="G51" s="22">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>T-25</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>10645</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>9642</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>8848</v>
+      </c>
+      <c r="G51" s="8">
         <f>D51/1000</f>
         <v/>
       </c>
-      <c r="H51" s="22">
+      <c r="H51" s="8">
         <f>E51/1000</f>
         <v/>
       </c>
-      <c r="I51" s="23">
+      <c r="I51" s="9">
         <f>IFERROR(D51/F51,"")</f>
         <v/>
       </c>
-      <c r="J51" s="24" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>T-25</t>
+          <t>T-27</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>19.78</v>
+        <v>70.98</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>2018</v>
+        <v>3651</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>2635</v>
+        <v>10341</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>1629</v>
+        <v>8544</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>1077</v>
+        <v>7484</v>
       </c>
       <c r="G52" s="15">
         <f>D52/1000</f>
@@ -2285,95 +2273,95 @@
       <c r="J52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>T-27</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="n">
-        <v>70.98</v>
-      </c>
-      <c r="C53" s="20" t="n">
-        <v>3651</v>
-      </c>
-      <c r="D53" s="21" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E53" s="21" t="n">
-        <v>1126</v>
-      </c>
-      <c r="F53" s="21" t="n">
-        <v>628</v>
-      </c>
-      <c r="G53" s="22">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>T-26</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>10203</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>9546</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>8310</v>
+      </c>
+      <c r="G53" s="8">
         <f>D53/1000</f>
         <v/>
       </c>
-      <c r="H53" s="22">
+      <c r="H53" s="8">
         <f>E53/1000</f>
         <v/>
       </c>
-      <c r="I53" s="23">
+      <c r="I53" s="9">
         <f>IFERROR(D53/F53,"")</f>
         <v/>
       </c>
-      <c r="J53" s="24" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>T-11A</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="n">
-        <v>113.78</v>
-      </c>
-      <c r="C54" s="20" t="n">
-        <v>4554</v>
-      </c>
-      <c r="D54" s="21" t="n">
-        <v>2285</v>
-      </c>
-      <c r="E54" s="21" t="n">
-        <v>277</v>
-      </c>
-      <c r="F54" s="21" t="n">
-        <v>174</v>
-      </c>
-      <c r="G54" s="22">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>T-28</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>3848</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>9761</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>8591</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>6820</v>
+      </c>
+      <c r="G54" s="15">
         <f>D54/1000</f>
         <v/>
       </c>
-      <c r="H54" s="22">
+      <c r="H54" s="15">
         <f>E54/1000</f>
         <v/>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="16">
         <f>IFERROR(D54/F54,"")</f>
         <v/>
       </c>
-      <c r="J54" s="24" t="inlineStr"/>
+      <c r="J54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>T-26</t>
+          <t>T-29</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>18.11</v>
+        <v>75.31</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1911</v>
+        <v>3891</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2077</v>
+        <v>9346</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1126</v>
+        <v>7427</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>836</v>
+        <v>6142</v>
       </c>
       <c r="G55" s="8">
         <f>D55/1000</f>
@@ -2390,30 +2378,30 @@
       <c r="J55" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>TOTAL / MÁXIMO</t>
         </is>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="19">
         <f>SUM(B5:B55)</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="20">
         <f>MAX(IFERROR(D5:D55*1,0))</f>
         <v/>
       </c>
-      <c r="G57" s="28">
+      <c r="G57" s="21">
         <f>IFERROR(MAX(G5:G55),"")</f>
         <v/>
       </c>
-      <c r="I57" s="29">
+      <c r="I57" s="22">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="inlineStr">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>Fundo amarelo = precisa de conferência: fator ≥ 3,0, ligação suposta, ou talhão sem estrada. Veja a coluna Observação.</t>
         </is>
@@ -2438,127 +2426,127 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Como estes números foram calculados</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>Ponto de sede do projeto do Google Earth (-13.560205, -57.475789).</t>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Ponto de sede do projeto do Google Earth (-13.586393, -57.555499).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Talhões</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>51 polígonos da pasta FAZENDA P.PEDRA.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Malha de estradas</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Divisas dos talhões (os carreadores correm nas divisas), costuradas onde talhões vizinhos são separados pela faixa do carreador (até 45 m), mais as estradas de dados/estradas_extra.json.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Dist. máxima</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Menor caminho pela estrada, da sede até o ponto MAIS EXTREMO do perímetro do talhão. Não corta por dentro da lavoura.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Dist. mínima</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Menor caminho pela estrada, da sede até o ponto de acesso mais próximo.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Linha reta</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Distância em linha reta da sede até a borda do talhão. Só referência.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Fator</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Dist. máxima ÷ linha reta. Fator alto = rota indireta, ou estrada faltando na malha.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Coordenadas</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>SIRGAS 2000 / UTM 21S (EPSG:31981) para distâncias e áreas.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Resolução</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Malha densificada a cada 25 m — é a precisão do 'ponto mais extremo'.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Validação</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>A malha precisa ser conferida por quem roda a fazenda. Use o arquivo _bancada.html.</t>
         </is>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -605,10 +605,10 @@
         <v>4758</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>23130</v>
+        <v>25353</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>20762</v>
+        <v>22092</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>15004</v>
@@ -630,23 +630,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>T37</t>
+          <t>T-05A</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>67.45999999999999</v>
+        <v>175.27</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>3607</v>
+        <v>5486</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>22685</v>
+        <v>24549</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>20893</v>
+        <v>21184</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>16250</v>
+        <v>13634</v>
       </c>
       <c r="G6" s="15">
         <f>D6/1000</f>
@@ -665,23 +665,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-05S</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>140.75</v>
+        <v>71.5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5173</v>
+        <v>4054</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>22531</v>
+        <v>24529</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>19955</v>
+        <v>21806</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>15747</v>
+        <v>14361</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -700,23 +700,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-05A</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>175.27</v>
+        <v>140.75</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>5486</v>
+        <v>5173</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>22492</v>
+        <v>24010</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>19870</v>
+        <v>21227</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>13634</v>
+        <v>15747</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -735,23 +735,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T-05S</t>
+          <t>T-16B</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>71.5</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4054</v>
+        <v>3913</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>22488</v>
+        <v>23656</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>20467</v>
+        <v>21083</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14361</v>
+        <v>16110</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -770,23 +770,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T33</t>
+          <t>T-16A</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>149.61</v>
+        <v>56.03</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>5003</v>
+        <v>3746</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>22356</v>
+        <v>23633</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>20129</v>
+        <v>20670</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>15887</v>
+        <v>15750</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -805,23 +805,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>T38</t>
+          <t>T37</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>140.69</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4981</v>
+        <v>3607</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>21968</v>
+        <v>23541</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>19497</v>
+        <v>21011</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>14856</v>
+        <v>16250</v>
       </c>
       <c r="G11" s="8">
         <f>D11/1000</f>
@@ -850,10 +850,10 @@
         <v>4944</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>21954</v>
+        <v>23390</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>19708</v>
+        <v>20665</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>15014</v>
@@ -875,23 +875,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-16B</t>
+          <t>T33</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>66.45999999999999</v>
+        <v>149.61</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3913</v>
+        <v>5003</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>21847</v>
+        <v>23180</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>20121</v>
+        <v>20249</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>16110</v>
+        <v>15887</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -910,23 +910,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>T-16A</t>
+          <t>T38</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>56.03</v>
+        <v>140.69</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>3746</v>
+        <v>4981</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>21395</v>
+        <v>23130</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>19710</v>
+        <v>19615</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>15750</v>
+        <v>14856</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -945,23 +945,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-24</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>302.63</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>7372</v>
+        <v>3691</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>21360</v>
+        <v>22815</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>17783</v>
+        <v>20565</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>11657</v>
+        <v>15125</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -980,23 +980,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T34</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>131.51</v>
+        <v>302.63</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4710</v>
+        <v>7372</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>21142</v>
+        <v>22713</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>18784</v>
+        <v>19126</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>14642</v>
+        <v>11657</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1015,23 +1015,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-15C</t>
+          <t>T-06A</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>136.18</v>
+        <v>132.93</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4817</v>
+        <v>4758</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>21011</v>
+        <v>22494</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>18769</v>
+        <v>19706</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>14928</v>
+        <v>14217</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1050,23 +1050,23 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>T-06A</t>
+          <t>T-15C</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>132.93</v>
+        <v>136.18</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>4758</v>
+        <v>4817</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>20952</v>
+        <v>22282</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>18755</v>
+        <v>19720</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>14217</v>
+        <v>14928</v>
       </c>
       <c r="G18" s="15">
         <f>D18/1000</f>
@@ -1085,23 +1085,23 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T-24</t>
+          <t>T-18</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>115.23</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>3691</v>
+        <v>4528</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>20857</v>
+        <v>21806</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>19186</v>
+        <v>19673</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>15125</v>
+        <v>14106</v>
       </c>
       <c r="G19" s="8">
         <f>D19/1000</f>
@@ -1120,23 +1120,23 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>T34</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>239.17</v>
+        <v>131.51</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>6359</v>
+        <v>4710</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>20685</v>
+        <v>21433</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>17519</v>
+        <v>18886</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>15489</v>
+        <v>14642</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1155,23 +1155,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T-18</t>
+          <t>T-19</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>115.23</v>
+        <v>150.72</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>4528</v>
+        <v>5638</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>20120</v>
+        <v>21415</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>17868</v>
+        <v>18064</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14106</v>
+        <v>13240</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1190,23 +1190,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>T-07B</t>
+          <t>T-15B</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>53.96</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>3674</v>
+        <v>4103</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>20029</v>
+        <v>21265</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>18380</v>
+        <v>18851</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>13875</v>
+        <v>14168</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1225,23 +1225,23 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>T-15B</t>
+          <t>T-07B</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>80.43000000000001</v>
+        <v>53.96</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4103</v>
+        <v>3674</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>19671</v>
+        <v>21184</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>17878</v>
+        <v>19336</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>14168</v>
+        <v>13875</v>
       </c>
       <c r="G23" s="8">
         <f>D23/1000</f>
@@ -1260,23 +1260,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-07A</t>
+          <t>T31</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>254.67</v>
+        <v>239.17</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>6809</v>
+        <v>6359</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>19667</v>
+        <v>21057</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>16672</v>
+        <v>17607</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>12367</v>
+        <v>15489</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1295,23 +1295,23 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-07A</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>150.72</v>
+        <v>254.67</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>5638</v>
+        <v>6809</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>19497</v>
+        <v>21008</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>16697</v>
+        <v>17997</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>13240</v>
+        <v>12367</v>
       </c>
       <c r="G25" s="8">
         <f>D25/1000</f>
@@ -1340,10 +1340,10 @@
         <v>7339</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>19319</v>
+        <v>20865</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>15780</v>
+        <v>17123</v>
       </c>
       <c r="F26" s="14" t="n">
         <v>9892</v>
@@ -1375,10 +1375,10 @@
         <v>5278</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>19146</v>
+        <v>20715</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>16672</v>
+        <v>17745</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>13180</v>
@@ -1410,10 +1410,10 @@
         <v>6729</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>18018</v>
+        <v>19854</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>14666</v>
+        <v>17000</v>
       </c>
       <c r="F28" s="14" t="n">
         <v>11611</v>
@@ -1445,10 +1445,10 @@
         <v>7008</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>17974</v>
+        <v>19532</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>14666</v>
+        <v>17123</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>10680</v>
@@ -1470,23 +1470,23 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>43.67</v>
+        <v>299.8</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>3710</v>
+        <v>7001</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>17936</v>
+        <v>18622</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>16107</v>
+        <v>15114</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>14089</v>
+        <v>8178</v>
       </c>
       <c r="G30" s="15">
         <f>D30/1000</f>
@@ -1505,23 +1505,23 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T-23</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>201.87</v>
+        <v>43.67</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>6413</v>
+        <v>3710</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>17482</v>
+        <v>18458</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>14382</v>
+        <v>16191</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>11986</v>
+        <v>14089</v>
       </c>
       <c r="G31" s="8">
         <f>D31/1000</f>
@@ -1540,23 +1540,23 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-09</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>299.8</v>
+        <v>300.31</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>7001</v>
+        <v>7000</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>17272</v>
+        <v>18431</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>13772</v>
+        <v>13616</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>8178</v>
+        <v>9125</v>
       </c>
       <c r="G32" s="15">
         <f>D32/1000</f>
@@ -1575,23 +1575,23 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>300.31</v>
+        <v>196.28</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>7000</v>
+        <v>6359</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>15968</v>
+        <v>18431</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>12664</v>
+        <v>13616</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>9125</v>
+        <v>10196</v>
       </c>
       <c r="G33" s="8">
         <f>D33/1000</f>
@@ -1610,23 +1610,23 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-23</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>58.7</v>
+        <v>201.87</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>4507</v>
+        <v>6413</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>15912</v>
+        <v>17860</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>13667</v>
+        <v>14771</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>11674</v>
+        <v>11986</v>
       </c>
       <c r="G34" s="15">
         <f>D34/1000</f>
@@ -1645,23 +1645,23 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-01C</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>196.28</v>
+        <v>302.68</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>6359</v>
+        <v>6953</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>15834</v>
+        <v>16929</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>12664</v>
+        <v>13521</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>10196</v>
+        <v>6693</v>
       </c>
       <c r="G35" s="8">
         <f>D35/1000</f>
@@ -1680,23 +1680,23 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T-22A</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>131.93</v>
+        <v>58.7</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>5328</v>
+        <v>4507</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>15638</v>
+        <v>16679</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>13233</v>
+        <v>14441</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>11332</v>
+        <v>11674</v>
       </c>
       <c r="G36" s="15">
         <f>D36/1000</f>
@@ -1715,23 +1715,23 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T-20</t>
+          <t>T-22A</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>140.68</v>
+        <v>131.93</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>4965</v>
+        <v>5328</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>15418</v>
+        <v>16679</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>12956</v>
+        <v>13308</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>10711</v>
+        <v>11332</v>
       </c>
       <c r="G37" s="8">
         <f>D37/1000</f>
@@ -1750,23 +1750,23 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T-01C</t>
+          <t>T-20</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>302.68</v>
+        <v>140.68</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>6953</v>
+        <v>4965</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>15271</v>
+        <v>16221</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>11801</v>
+        <v>13338</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>6693</v>
+        <v>10711</v>
       </c>
       <c r="G38" s="15">
         <f>D38/1000</f>
@@ -1785,23 +1785,23 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>T-20S</t>
+          <t>T-10B</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>58.94</v>
+        <v>177.61</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>3772</v>
+        <v>5367</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>14434</v>
+        <v>16000</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>12558</v>
+        <v>12433</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>10512</v>
+        <v>8285</v>
       </c>
       <c r="G39" s="8">
         <f>D39/1000</f>
@@ -1820,23 +1820,23 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-01A</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>174.68</v>
+        <v>60.51</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>5276</v>
+        <v>3703</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>14095</v>
+        <v>15908</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>11481</v>
+        <v>13518</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>9459</v>
+        <v>6700</v>
       </c>
       <c r="G40" s="15">
         <f>D40/1000</f>
@@ -1865,10 +1865,10 @@
         <v>3845</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>14083</v>
+        <v>15777</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>12208</v>
+        <v>13548</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>6902</v>
@@ -1890,23 +1890,23 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>T-21</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>60.19</v>
+        <v>174.68</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>3809</v>
+        <v>5276</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>14051</v>
+        <v>15623</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>12160</v>
+        <v>12433</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>10313</v>
+        <v>9459</v>
       </c>
       <c r="G42" s="15">
         <f>D42/1000</f>
@@ -1925,23 +1925,23 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>T-10B</t>
+          <t>T-20S</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>177.61</v>
+        <v>58.94</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>5367</v>
+        <v>3772</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>13969</v>
+        <v>15144</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>11481</v>
+        <v>12939</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>8285</v>
+        <v>10512</v>
       </c>
       <c r="G43" s="8">
         <f>D43/1000</f>
@@ -1960,23 +1960,23 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>T-21A</t>
+          <t>T-21</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>124</v>
+        <v>60.19</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>4814</v>
+        <v>3809</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>13916</v>
+        <v>14994</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>11664</v>
+        <v>12530</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>9977</v>
+        <v>10313</v>
       </c>
       <c r="G44" s="15">
         <f>D44/1000</f>
@@ -1995,23 +1995,23 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>T-01A</t>
+          <t>T-21A</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>60.51</v>
+        <v>124</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>3703</v>
+        <v>4814</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>13651</v>
+        <v>14994</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>11808</v>
+        <v>11745</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>6700</v>
+        <v>9977</v>
       </c>
       <c r="G45" s="8">
         <f>D45/1000</f>
@@ -2030,23 +2030,23 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>T-12S</t>
+          <t>T-10S</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>59.61</v>
+        <v>60.87</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>3784</v>
+        <v>3801</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>12948</v>
+        <v>14364</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11072</v>
+        <v>12020</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>9228</v>
+        <v>8017</v>
       </c>
       <c r="G46" s="15">
         <f>D46/1000</f>
@@ -2065,23 +2065,23 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>T-10S</t>
+          <t>T-10A</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>60.87</v>
+        <v>80.13</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>3801</v>
+        <v>4466</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>12767</v>
+        <v>14036</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>11069</v>
+        <v>11107</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>8017</v>
+        <v>7792</v>
       </c>
       <c r="G47" s="8">
         <f>D47/1000</f>
@@ -2100,23 +2100,23 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-12S</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>59.79</v>
+        <v>59.61</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>3770</v>
+        <v>3784</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>12552</v>
+        <v>13865</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>10674</v>
+        <v>12023</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>9014</v>
+        <v>9228</v>
       </c>
       <c r="G48" s="15">
         <f>D48/1000</f>
@@ -2135,23 +2135,23 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>T-10A</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>80.13</v>
+        <v>59.79</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>4466</v>
+        <v>3770</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>12363</v>
+        <v>13247</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>10156</v>
+        <v>11634</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7792</v>
+        <v>9014</v>
       </c>
       <c r="G49" s="8">
         <f>D49/1000</f>
@@ -2180,10 +2180,10 @@
         <v>4554</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>12305</v>
+        <v>12853</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>10165</v>
+        <v>10985</v>
       </c>
       <c r="F50" s="14" t="n">
         <v>8753</v>
@@ -2215,10 +2215,10 @@
         <v>2018</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>10645</v>
+        <v>10885</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>9642</v>
+        <v>9664</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>8848</v>
@@ -2250,10 +2250,10 @@
         <v>3651</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>10341</v>
+        <v>10836</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>8544</v>
+        <v>8569</v>
       </c>
       <c r="F52" s="14" t="n">
         <v>7484</v>
@@ -2285,10 +2285,10 @@
         <v>1911</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>10203</v>
+        <v>10329</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>9546</v>
+        <v>9575</v>
       </c>
       <c r="F53" s="7" t="n">
         <v>8310</v>
@@ -2320,10 +2320,10 @@
         <v>3848</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>9761</v>
+        <v>10275</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>8591</v>
+        <v>8643</v>
       </c>
       <c r="F54" s="14" t="n">
         <v>6820</v>
@@ -2355,10 +2355,10 @@
         <v>3891</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>9346</v>
+        <v>9469</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7427</v>
+        <v>7441</v>
       </c>
       <c r="F55" s="7" t="n">
         <v>6142</v>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1DF147-29C1-4142-AD66-8209024576C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248CF181-3BC4-46A4-9521-FCBE82BE1757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="2610" windowWidth="17625" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248CF181-3BC4-46A4-9521-FCBE82BE1757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECEB2EF-6A79-4EBB-8A10-29CC513A9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2353,7 +2353,7 @@
         <v>11453</v>
       </c>
       <c r="E52" s="14">
-        <v>8595</v>
+        <v>9730</v>
       </c>
       <c r="F52" s="14">
         <v>7484</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
-        <v>8.5950000000000006</v>
+        <v>9.73</v>
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECEB2EF-6A79-4EBB-8A10-29CC513A9D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80D2A3C-6A57-4981-B255-8E947EBDFFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="89">
   <si>
     <t>FAZENDA P.PEDRA — distância dos talhões até a sede</t>
   </si>
@@ -72,157 +72,166 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-23</t>
+  </si>
+  <si>
+    <t>T-20</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-19</t>
+  </si>
+  <si>
+    <t>T-24</t>
+  </si>
+  <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-17</t>
+  </si>
+  <si>
+    <t>T-05A</t>
+  </si>
+  <si>
+    <t>T-05S</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-18</t>
+  </si>
+  <si>
+    <t>T-16B</t>
+  </si>
+  <si>
+    <t>T-15B</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
+    <t>T-06A</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
+    <t>T-16A</t>
+  </si>
+  <si>
+    <t>T-07A</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-15A</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-01C</t>
+  </si>
+  <si>
+    <t>T-22</t>
+  </si>
+  <si>
+    <t>T-22A</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-01A</t>
+  </si>
+  <si>
+    <t>T-20S</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-01B</t>
+  </si>
+  <si>
+    <t>T-21A</t>
+  </si>
+  <si>
+    <t>T-10B</t>
+  </si>
+  <si>
+    <t>T-10A</t>
+  </si>
+  <si>
+    <t>T-10S</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
+    <t>T-12S</t>
+  </si>
+  <si>
+    <t>T-11A</t>
+  </si>
+  <si>
+    <t>T-26</t>
+  </si>
+  <si>
+    <t>T-27</t>
+  </si>
+  <si>
+    <t>T-25</t>
+  </si>
+  <si>
+    <t>T-28</t>
+  </si>
+  <si>
+    <t>T-29</t>
+  </si>
+  <si>
     <t>T33</t>
   </si>
   <si>
+    <t>sem acesso</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>sem estrada até este talhão</t>
+  </si>
+  <si>
+    <t>T34</t>
+  </si>
+  <si>
     <t>T37</t>
   </si>
   <si>
-    <t>T-18</t>
-  </si>
-  <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>T34</t>
-  </si>
-  <si>
     <t>T38</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-15A</t>
-  </si>
-  <si>
-    <t>T-05S</t>
-  </si>
-  <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-07A</t>
-  </si>
-  <si>
-    <t>T-16A</t>
-  </si>
-  <si>
-    <t>T-15C</t>
-  </si>
-  <si>
-    <t>T-16B</t>
-  </si>
-  <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-15B</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-06A</t>
-  </si>
-  <si>
-    <t>T31</t>
-  </si>
-  <si>
-    <t>T-22</t>
-  </si>
-  <si>
-    <t>T-22A</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-13</t>
-  </si>
-  <si>
-    <t>T-23</t>
-  </si>
-  <si>
-    <t>T-10B</t>
-  </si>
-  <si>
-    <t>T-12</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T30</t>
-  </si>
-  <si>
-    <t>T-01C</t>
-  </si>
-  <si>
-    <t>T-20</t>
-  </si>
-  <si>
-    <t>T-01A</t>
-  </si>
-  <si>
-    <t>T-01B</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-21A</t>
-  </si>
-  <si>
-    <t>T-20S</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-10S</t>
-  </si>
-  <si>
-    <t>T-12S</t>
-  </si>
-  <si>
-    <t>T-10A</t>
-  </si>
-  <si>
-    <t>T-26</t>
-  </si>
-  <si>
-    <t>T-27</t>
-  </si>
-  <si>
-    <t>T-25</t>
-  </si>
-  <si>
-    <t>T-28</t>
-  </si>
-  <si>
-    <t>T-29</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -301,7 +310,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,6 +356,17 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
@@ -358,7 +378,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +388,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -397,13 +422,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -411,20 +450,21 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -793,97 +833,97 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>149.61000000000001</v>
+        <v>201.87</v>
       </c>
       <c r="C5" s="6">
-        <v>5003</v>
+        <v>6413</v>
       </c>
       <c r="D5" s="7">
-        <v>27126</v>
+        <v>39828</v>
       </c>
       <c r="E5" s="7">
-        <v>21296</v>
+        <v>36213</v>
       </c>
       <c r="F5" s="7">
-        <v>15887</v>
+        <v>11986</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G36" si="0">D5/1000</f>
-        <v>27.126000000000001</v>
+        <f t="shared" ref="G5:G51" si="0">D5/1000</f>
+        <v>39.828000000000003</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H36" si="1">E5/1000</f>
-        <v>21.295999999999999</v>
+        <f t="shared" ref="H5:H51" si="1">E5/1000</f>
+        <v>36.213000000000001</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
-        <v>1.7074337508654875</v>
+        <f t="shared" ref="I5:I51" si="2">IFERROR(D5/F5,"")</f>
+        <v>3.3228766894710495</v>
       </c>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12">
-        <v>67.459999999999994</v>
-      </c>
-      <c r="C6" s="13">
-        <v>3607</v>
-      </c>
-      <c r="D6" s="14">
-        <v>27126</v>
-      </c>
-      <c r="E6" s="14">
-        <v>23749</v>
-      </c>
-      <c r="F6" s="14">
-        <v>16250</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" si="0"/>
-        <v>27.126000000000001</v>
-      </c>
-      <c r="H6" s="15">
-        <f t="shared" si="1"/>
-        <v>23.748999999999999</v>
-      </c>
-      <c r="I6" s="16">
-        <f t="shared" si="2"/>
-        <v>1.6692923076923076</v>
-      </c>
-      <c r="J6" s="17"/>
+      <c r="B6" s="5">
+        <v>140.68</v>
+      </c>
+      <c r="C6" s="6">
+        <v>4965</v>
+      </c>
+      <c r="D6" s="7">
+        <v>36293</v>
+      </c>
+      <c r="E6" s="7">
+        <v>34692</v>
+      </c>
+      <c r="F6" s="7">
+        <v>10711</v>
+      </c>
+      <c r="G6" s="8">
+        <f t="shared" si="0"/>
+        <v>36.292999999999999</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="1"/>
+        <v>34.692</v>
+      </c>
+      <c r="I6" s="9">
+        <f t="shared" si="2"/>
+        <v>3.388385771636635</v>
+      </c>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>115.23</v>
+        <v>174.68</v>
       </c>
       <c r="C7" s="6">
-        <v>4528</v>
+        <v>5276</v>
       </c>
       <c r="D7" s="7">
-        <v>26812</v>
+        <v>35804</v>
       </c>
       <c r="E7" s="7">
-        <v>21622</v>
+        <v>34302</v>
       </c>
       <c r="F7" s="7">
-        <v>14106</v>
+        <v>9459</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>26.812000000000001</v>
+        <v>35.804000000000002</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>21.622</v>
+        <v>34.302</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.9007514532822911</v>
+        <v>3.785178137223808</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -898,390 +938,390 @@
         <v>5638</v>
       </c>
       <c r="D8" s="14">
-        <v>26812</v>
+        <v>31060</v>
       </c>
       <c r="E8" s="14">
-        <v>18665</v>
+        <v>28518</v>
       </c>
       <c r="F8" s="14">
         <v>13240</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>26.812000000000001</v>
+        <v>31.06</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>18.664999999999999</v>
+        <v>28.518000000000001</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.0250755287009063</v>
+        <v>2.3459214501510575</v>
       </c>
       <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5">
-        <v>131.51</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4710</v>
-      </c>
-      <c r="D9" s="7">
-        <v>26773</v>
-      </c>
-      <c r="E9" s="7">
-        <v>19934</v>
-      </c>
-      <c r="F9" s="7">
-        <v>14642</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="0"/>
-        <v>26.773</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="1"/>
-        <v>19.934000000000001</v>
-      </c>
-      <c r="I9" s="9">
-        <f t="shared" si="2"/>
-        <v>1.8285070345581205</v>
-      </c>
-      <c r="J9" s="10"/>
+      <c r="B9" s="19">
+        <v>83.32</v>
+      </c>
+      <c r="C9" s="20">
+        <v>3691</v>
+      </c>
+      <c r="D9" s="21">
+        <v>28627</v>
+      </c>
+      <c r="E9" s="21">
+        <v>27162</v>
+      </c>
+      <c r="F9" s="21">
+        <v>15125</v>
+      </c>
+      <c r="G9" s="22">
+        <f t="shared" si="0"/>
+        <v>28.626999999999999</v>
+      </c>
+      <c r="H9" s="22">
+        <f t="shared" si="1"/>
+        <v>27.161999999999999</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="2"/>
+        <v>1.8926942148760331</v>
+      </c>
+      <c r="J9" s="24"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>140.69</v>
+        <v>124.34</v>
       </c>
       <c r="C10" s="13">
-        <v>4981</v>
+        <v>4758</v>
       </c>
       <c r="D10" s="14">
-        <v>26773</v>
+        <v>25385</v>
       </c>
       <c r="E10" s="14">
-        <v>20662</v>
+        <v>24763</v>
       </c>
       <c r="F10" s="14">
-        <v>14856</v>
+        <v>15004</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>26.773</v>
+        <v>25.385000000000002</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>20.661999999999999</v>
+        <v>24.763000000000002</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.8021674744211094</v>
+        <v>1.6918821647560651</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5">
-        <v>270.48</v>
-      </c>
-      <c r="C11" s="6">
-        <v>6729</v>
-      </c>
-      <c r="D11" s="7">
-        <v>26462</v>
-      </c>
-      <c r="E11" s="7">
-        <v>17588</v>
-      </c>
-      <c r="F11" s="7">
-        <v>11611</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>26.462</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="1"/>
-        <v>17.588000000000001</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="2"/>
-        <v>2.2790457324950477</v>
-      </c>
-      <c r="J11" s="10"/>
+      <c r="B11" s="19">
+        <v>140.75</v>
+      </c>
+      <c r="C11" s="20">
+        <v>5173</v>
+      </c>
+      <c r="D11" s="21">
+        <v>25382</v>
+      </c>
+      <c r="E11" s="21">
+        <v>23120</v>
+      </c>
+      <c r="F11" s="21">
+        <v>15747</v>
+      </c>
+      <c r="G11" s="22">
+        <f t="shared" si="0"/>
+        <v>25.382000000000001</v>
+      </c>
+      <c r="H11" s="22">
+        <f t="shared" si="1"/>
+        <v>23.12</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6118625769987933</v>
+      </c>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>124.34</v>
+        <v>175.27</v>
       </c>
       <c r="C12" s="13">
-        <v>4758</v>
+        <v>5486</v>
       </c>
       <c r="D12" s="14">
-        <v>26412</v>
+        <v>24841</v>
       </c>
       <c r="E12" s="14">
-        <v>22134</v>
+        <v>23291</v>
       </c>
       <c r="F12" s="14">
-        <v>15004</v>
+        <v>13634</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>26.411999999999999</v>
+        <v>24.841000000000001</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>22.134</v>
+        <v>23.291</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.7603305785123966</v>
+        <v>1.821989144785096</v>
       </c>
       <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="5">
-        <v>169.72</v>
-      </c>
-      <c r="C13" s="6">
-        <v>5278</v>
-      </c>
-      <c r="D13" s="7">
-        <v>26279</v>
-      </c>
-      <c r="E13" s="7">
-        <v>17745</v>
-      </c>
-      <c r="F13" s="7">
-        <v>13180</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="0"/>
-        <v>26.279</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="1"/>
-        <v>17.745000000000001</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="2"/>
-        <v>1.9938543247344462</v>
-      </c>
-      <c r="J13" s="10"/>
+      <c r="B13" s="19">
+        <v>71.5</v>
+      </c>
+      <c r="C13" s="20">
+        <v>4054</v>
+      </c>
+      <c r="D13" s="21">
+        <v>24816</v>
+      </c>
+      <c r="E13" s="21">
+        <v>24054</v>
+      </c>
+      <c r="F13" s="21">
+        <v>14361</v>
+      </c>
+      <c r="G13" s="22">
+        <f t="shared" si="0"/>
+        <v>24.815999999999999</v>
+      </c>
+      <c r="H13" s="22">
+        <f t="shared" si="1"/>
+        <v>24.053999999999998</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="2"/>
+        <v>1.7280133695425111</v>
+      </c>
+      <c r="J13" s="24"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>71.5</v>
+        <v>302.63</v>
       </c>
       <c r="C14" s="13">
-        <v>4054</v>
+        <v>7372</v>
       </c>
       <c r="D14" s="14">
-        <v>25595</v>
+        <v>23342</v>
       </c>
       <c r="E14" s="14">
-        <v>21824</v>
+        <v>21162</v>
       </c>
       <c r="F14" s="14">
-        <v>14361</v>
+        <v>11657</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>25.594999999999999</v>
+        <v>23.341999999999999</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>21.824000000000002</v>
+        <v>21.161999999999999</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.7822575029594039</v>
+        <v>2.0024019902204686</v>
       </c>
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5">
-        <v>175.27</v>
-      </c>
-      <c r="C15" s="6">
-        <v>5486</v>
-      </c>
-      <c r="D15" s="7">
-        <v>25591</v>
-      </c>
-      <c r="E15" s="7">
-        <v>21184</v>
-      </c>
-      <c r="F15" s="7">
-        <v>13634</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="0"/>
-        <v>25.591000000000001</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="1"/>
-        <v>21.184000000000001</v>
-      </c>
-      <c r="I15" s="9">
-        <f t="shared" si="2"/>
-        <v>1.8769986797711604</v>
-      </c>
-      <c r="J15" s="10"/>
+      <c r="B15" s="19">
+        <v>115.23</v>
+      </c>
+      <c r="C15" s="20">
+        <v>4528</v>
+      </c>
+      <c r="D15" s="21">
+        <v>23335</v>
+      </c>
+      <c r="E15" s="21">
+        <v>22531</v>
+      </c>
+      <c r="F15" s="21">
+        <v>14106</v>
+      </c>
+      <c r="G15" s="22">
+        <f t="shared" si="0"/>
+        <v>23.335000000000001</v>
+      </c>
+      <c r="H15" s="22">
+        <f t="shared" si="1"/>
+        <v>22.530999999999999</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6542605983269532</v>
+      </c>
+      <c r="J15" s="24"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>140.75</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="C16" s="13">
-        <v>5173</v>
+        <v>3913</v>
       </c>
       <c r="D16" s="14">
-        <v>25360</v>
+        <v>23178</v>
       </c>
       <c r="E16" s="14">
-        <v>21227</v>
+        <v>21042</v>
       </c>
       <c r="F16" s="14">
-        <v>15747</v>
+        <v>16110</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>25.36</v>
+        <v>23.178000000000001</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>21.227</v>
+        <v>21.042000000000002</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.6104654854892995</v>
+        <v>1.438733705772812</v>
       </c>
       <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5">
-        <v>300.64</v>
-      </c>
-      <c r="C17" s="6">
-        <v>7008</v>
-      </c>
-      <c r="D17" s="7">
-        <v>25352</v>
-      </c>
-      <c r="E17" s="7">
-        <v>17123</v>
-      </c>
-      <c r="F17" s="7">
-        <v>10680</v>
-      </c>
-      <c r="G17" s="8">
-        <f t="shared" si="0"/>
-        <v>25.352</v>
-      </c>
-      <c r="H17" s="8">
-        <f t="shared" si="1"/>
-        <v>17.123000000000001</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="2"/>
-        <v>2.3737827715355806</v>
-      </c>
-      <c r="J17" s="10"/>
+      <c r="B17" s="19">
+        <v>80.430000000000007</v>
+      </c>
+      <c r="C17" s="20">
+        <v>4103</v>
+      </c>
+      <c r="D17" s="21">
+        <v>22284</v>
+      </c>
+      <c r="E17" s="21">
+        <v>21674</v>
+      </c>
+      <c r="F17" s="21">
+        <v>14168</v>
+      </c>
+      <c r="G17" s="22">
+        <f t="shared" si="0"/>
+        <v>22.283999999999999</v>
+      </c>
+      <c r="H17" s="22">
+        <f t="shared" si="1"/>
+        <v>21.673999999999999</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="2"/>
+        <v>1.572840203274986</v>
+      </c>
+      <c r="J17" s="24"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>254.67</v>
+        <v>144.9</v>
       </c>
       <c r="C18" s="13">
-        <v>6809</v>
+        <v>4944</v>
       </c>
       <c r="D18" s="14">
-        <v>24947</v>
+        <v>21610</v>
       </c>
       <c r="E18" s="14">
-        <v>17997</v>
+        <v>20631</v>
       </c>
       <c r="F18" s="14">
-        <v>12367</v>
+        <v>15014</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>24.946999999999999</v>
+        <v>21.61</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>17.997</v>
+        <v>20.631</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.0172232554378589</v>
+        <v>1.439323298254962</v>
       </c>
       <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="5">
-        <v>56.03</v>
-      </c>
-      <c r="C19" s="6">
-        <v>3746</v>
-      </c>
-      <c r="D19" s="7">
-        <v>24232</v>
-      </c>
-      <c r="E19" s="7">
-        <v>20670</v>
-      </c>
-      <c r="F19" s="7">
-        <v>15750</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>24.231999999999999</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="1"/>
-        <v>20.67</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>1.5385396825396824</v>
-      </c>
-      <c r="J19" s="10"/>
+      <c r="B19" s="19">
+        <v>239.17</v>
+      </c>
+      <c r="C19" s="20">
+        <v>6359</v>
+      </c>
+      <c r="D19" s="21">
+        <v>21504</v>
+      </c>
+      <c r="E19" s="21">
+        <v>18621</v>
+      </c>
+      <c r="F19" s="21">
+        <v>15489</v>
+      </c>
+      <c r="G19" s="22">
+        <f t="shared" si="0"/>
+        <v>21.504000000000001</v>
+      </c>
+      <c r="H19" s="22">
+        <f t="shared" si="1"/>
+        <v>18.620999999999999</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="2"/>
+        <v>1.3883401123377881</v>
+      </c>
+      <c r="J19" s="24"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
@@ -1294,1207 +1334,1203 @@
         <v>4817</v>
       </c>
       <c r="D20" s="14">
-        <v>24230</v>
+        <v>21249</v>
       </c>
       <c r="E20" s="14">
-        <v>19725</v>
+        <v>19706</v>
       </c>
       <c r="F20" s="14">
         <v>14928</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>24.23</v>
+        <v>21.248999999999999</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>19.725000000000001</v>
+        <v>19.706</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.6231243301178992</v>
+        <v>1.4234324758842443</v>
       </c>
       <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="5">
-        <v>66.459999999999994</v>
-      </c>
-      <c r="C21" s="6">
-        <v>3913</v>
-      </c>
-      <c r="D21" s="7">
-        <v>24060</v>
-      </c>
-      <c r="E21" s="7">
-        <v>21083</v>
-      </c>
-      <c r="F21" s="7">
-        <v>16110</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="0"/>
-        <v>24.06</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="1"/>
-        <v>21.082999999999998</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="2"/>
-        <v>1.4934823091247673</v>
-      </c>
-      <c r="J21" s="10"/>
+      <c r="B21" s="19">
+        <v>132.93</v>
+      </c>
+      <c r="C21" s="20">
+        <v>4758</v>
+      </c>
+      <c r="D21" s="21">
+        <v>21215</v>
+      </c>
+      <c r="E21" s="21">
+        <v>19669</v>
+      </c>
+      <c r="F21" s="21">
+        <v>14217</v>
+      </c>
+      <c r="G21" s="22">
+        <f t="shared" si="0"/>
+        <v>21.215</v>
+      </c>
+      <c r="H21" s="22">
+        <f t="shared" si="1"/>
+        <v>19.669</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="2"/>
+        <v>1.4922276148273195</v>
+      </c>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>83.32</v>
+        <v>278.49</v>
       </c>
       <c r="C22" s="13">
-        <v>3691</v>
+        <v>7339</v>
       </c>
       <c r="D22" s="14">
-        <v>23666</v>
+        <v>21212</v>
       </c>
       <c r="E22" s="14">
-        <v>21153</v>
+        <v>19208</v>
       </c>
       <c r="F22" s="14">
-        <v>15125</v>
+        <v>9892</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>23.666</v>
+        <v>21.212</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>21.152999999999999</v>
+        <v>19.207999999999998</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.564694214876033</v>
+        <v>2.144359078042863</v>
       </c>
       <c r="J22" s="17"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="5">
-        <v>144.9</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4944</v>
-      </c>
-      <c r="D23" s="7">
-        <v>23635</v>
-      </c>
-      <c r="E23" s="7">
-        <v>20665</v>
-      </c>
-      <c r="F23" s="7">
-        <v>15014</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" si="0"/>
-        <v>23.635000000000002</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="1"/>
-        <v>20.664999999999999</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="2"/>
-        <v>1.5741974157453045</v>
-      </c>
-      <c r="J23" s="10"/>
+      <c r="B23" s="19">
+        <v>53.96</v>
+      </c>
+      <c r="C23" s="20">
+        <v>3674</v>
+      </c>
+      <c r="D23" s="21">
+        <v>21189</v>
+      </c>
+      <c r="E23" s="21">
+        <v>19314</v>
+      </c>
+      <c r="F23" s="21">
+        <v>13875</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="0"/>
+        <v>21.189</v>
+      </c>
+      <c r="H23" s="22">
+        <f t="shared" si="1"/>
+        <v>19.314</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5271351351351352</v>
+      </c>
+      <c r="J23" s="24"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>302.63</v>
+        <v>56.03</v>
       </c>
       <c r="C24" s="13">
-        <v>7372</v>
+        <v>3746</v>
       </c>
       <c r="D24" s="14">
-        <v>23345</v>
+        <v>21092</v>
       </c>
       <c r="E24" s="14">
-        <v>19126</v>
+        <v>20631</v>
       </c>
       <c r="F24" s="14">
-        <v>11657</v>
+        <v>15750</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>23.344999999999999</v>
+        <v>21.091999999999999</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>19.126000000000001</v>
+        <v>20.631</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>2.0026593463155185</v>
+        <v>1.3391746031746032</v>
       </c>
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="5">
-        <v>80.430000000000007</v>
-      </c>
-      <c r="C25" s="6">
-        <v>4103</v>
-      </c>
-      <c r="D25" s="7">
-        <v>22996</v>
-      </c>
-      <c r="E25" s="7">
-        <v>18851</v>
-      </c>
-      <c r="F25" s="7">
-        <v>14168</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="0"/>
-        <v>22.995999999999999</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="1"/>
-        <v>18.850999999999999</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="2"/>
-        <v>1.6230942970073405</v>
-      </c>
-      <c r="J25" s="10"/>
+      <c r="B25" s="19">
+        <v>254.67</v>
+      </c>
+      <c r="C25" s="20">
+        <v>6809</v>
+      </c>
+      <c r="D25" s="21">
+        <v>19570</v>
+      </c>
+      <c r="E25" s="21">
+        <v>17594</v>
+      </c>
+      <c r="F25" s="21">
+        <v>12367</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="0"/>
+        <v>19.57</v>
+      </c>
+      <c r="H25" s="22">
+        <f t="shared" si="1"/>
+        <v>17.594000000000001</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5824371310746341</v>
+      </c>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>278.49</v>
+        <v>299.8</v>
       </c>
       <c r="C26" s="13">
-        <v>7339</v>
+        <v>7001</v>
       </c>
       <c r="D26" s="14">
-        <v>22877</v>
+        <v>19257</v>
       </c>
       <c r="E26" s="14">
-        <v>17123</v>
+        <v>17178</v>
       </c>
       <c r="F26" s="14">
-        <v>9892</v>
+        <v>8178</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>22.876999999999999</v>
+        <v>19.257000000000001</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>17.123000000000001</v>
+        <v>17.178000000000001</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.3126769106348566</v>
+        <v>2.3547322083639033</v>
       </c>
       <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="5">
-        <v>132.93</v>
-      </c>
-      <c r="C27" s="6">
-        <v>4758</v>
-      </c>
-      <c r="D27" s="7">
-        <v>22815</v>
-      </c>
-      <c r="E27" s="7">
-        <v>19706</v>
-      </c>
-      <c r="F27" s="7">
-        <v>14217</v>
-      </c>
-      <c r="G27" s="8">
-        <f t="shared" si="0"/>
-        <v>22.815000000000001</v>
-      </c>
-      <c r="H27" s="8">
-        <f t="shared" si="1"/>
-        <v>19.706</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="2"/>
-        <v>1.6047689385946402</v>
-      </c>
-      <c r="J27" s="10"/>
+      <c r="B27" s="19">
+        <v>169.72</v>
+      </c>
+      <c r="C27" s="20">
+        <v>5278</v>
+      </c>
+      <c r="D27" s="21">
+        <v>18861</v>
+      </c>
+      <c r="E27" s="21">
+        <v>17594</v>
+      </c>
+      <c r="F27" s="21">
+        <v>13180</v>
+      </c>
+      <c r="G27" s="22">
+        <f t="shared" si="0"/>
+        <v>18.861000000000001</v>
+      </c>
+      <c r="H27" s="22">
+        <f t="shared" si="1"/>
+        <v>17.594000000000001</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="2"/>
+        <v>1.43103186646434</v>
+      </c>
+      <c r="J27" s="24"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>239.17</v>
+        <v>43.67</v>
       </c>
       <c r="C28" s="13">
-        <v>6359</v>
+        <v>3710</v>
       </c>
       <c r="D28" s="14">
-        <v>22282</v>
+        <v>18671</v>
       </c>
       <c r="E28" s="14">
-        <v>18654</v>
+        <v>17219</v>
       </c>
       <c r="F28" s="14">
-        <v>15489</v>
+        <v>14089</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>22.282</v>
+        <v>18.670999999999999</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>18.654</v>
+        <v>17.219000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.4385693072503067</v>
+        <v>1.3252182553765348</v>
       </c>
       <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="5">
-        <v>58.7</v>
-      </c>
-      <c r="C29" s="6">
-        <v>4507</v>
-      </c>
-      <c r="D29" s="7">
-        <v>21718</v>
-      </c>
-      <c r="E29" s="7">
-        <v>15036</v>
-      </c>
-      <c r="F29" s="7">
-        <v>11674</v>
-      </c>
-      <c r="G29" s="8">
-        <f t="shared" si="0"/>
-        <v>21.718</v>
-      </c>
-      <c r="H29" s="8">
-        <f t="shared" si="1"/>
-        <v>15.036</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" si="2"/>
-        <v>1.8603734795271543</v>
-      </c>
-      <c r="J29" s="10"/>
+      <c r="B29" s="19">
+        <v>300.64</v>
+      </c>
+      <c r="C29" s="20">
+        <v>7008</v>
+      </c>
+      <c r="D29" s="21">
+        <v>17643</v>
+      </c>
+      <c r="E29" s="21">
+        <v>15587</v>
+      </c>
+      <c r="F29" s="21">
+        <v>10680</v>
+      </c>
+      <c r="G29" s="22">
+        <f t="shared" si="0"/>
+        <v>17.643000000000001</v>
+      </c>
+      <c r="H29" s="22">
+        <f t="shared" si="1"/>
+        <v>15.587</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6519662921348315</v>
+      </c>
+      <c r="J29" s="24"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>131.93</v>
+        <v>270.48</v>
       </c>
       <c r="C30" s="13">
-        <v>5328</v>
+        <v>6729</v>
       </c>
       <c r="D30" s="14">
-        <v>21718</v>
+        <v>17643</v>
       </c>
       <c r="E30" s="14">
-        <v>14356</v>
+        <v>15587</v>
       </c>
       <c r="F30" s="14">
-        <v>11332</v>
+        <v>11611</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>21.718</v>
+        <v>17.643000000000001</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>14.356</v>
+        <v>15.587</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.9165195905400636</v>
+        <v>1.5195073637068297</v>
       </c>
       <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="5">
-        <v>53.96</v>
-      </c>
-      <c r="C31" s="6">
-        <v>3674</v>
-      </c>
-      <c r="D31" s="7">
-        <v>21211</v>
-      </c>
-      <c r="E31" s="7">
-        <v>19360</v>
-      </c>
-      <c r="F31" s="7">
-        <v>13875</v>
-      </c>
-      <c r="G31" s="8">
-        <f t="shared" si="0"/>
-        <v>21.210999999999999</v>
-      </c>
-      <c r="H31" s="8">
-        <f t="shared" si="1"/>
-        <v>19.36</v>
-      </c>
-      <c r="I31" s="9">
-        <f t="shared" si="2"/>
-        <v>1.5287207207207207</v>
-      </c>
-      <c r="J31" s="10"/>
+      <c r="B31" s="19">
+        <v>302.68</v>
+      </c>
+      <c r="C31" s="20">
+        <v>6953</v>
+      </c>
+      <c r="D31" s="21">
+        <v>17255</v>
+      </c>
+      <c r="E31" s="21">
+        <v>14983</v>
+      </c>
+      <c r="F31" s="21">
+        <v>6693</v>
+      </c>
+      <c r="G31" s="22">
+        <f t="shared" si="0"/>
+        <v>17.254999999999999</v>
+      </c>
+      <c r="H31" s="22">
+        <f t="shared" si="1"/>
+        <v>14.983000000000001</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="2"/>
+        <v>2.5780666367847003</v>
+      </c>
+      <c r="J31" s="24"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>300.31</v>
+        <v>58.7</v>
       </c>
       <c r="C32" s="13">
-        <v>7000</v>
+        <v>4507</v>
       </c>
       <c r="D32" s="14">
-        <v>21210</v>
+        <v>16968</v>
       </c>
       <c r="E32" s="14">
-        <v>15130</v>
+        <v>15008</v>
       </c>
       <c r="F32" s="14">
-        <v>9125</v>
+        <v>11674</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>21.21</v>
+        <v>16.968</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>15.13</v>
+        <v>15.007999999999999</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.3243835616438355</v>
+        <v>1.4534863799897209</v>
       </c>
       <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="5">
-        <v>196.28</v>
-      </c>
-      <c r="C33" s="6">
-        <v>6359</v>
-      </c>
-      <c r="D33" s="7">
-        <v>21210</v>
-      </c>
-      <c r="E33" s="7">
-        <v>15375</v>
-      </c>
-      <c r="F33" s="7">
-        <v>10196</v>
-      </c>
-      <c r="G33" s="8">
-        <f t="shared" si="0"/>
-        <v>21.21</v>
-      </c>
-      <c r="H33" s="8">
-        <f t="shared" si="1"/>
-        <v>15.375</v>
-      </c>
-      <c r="I33" s="9">
-        <f t="shared" si="2"/>
-        <v>2.080227540211848</v>
-      </c>
-      <c r="J33" s="10"/>
+      <c r="B33" s="19">
+        <v>131.93</v>
+      </c>
+      <c r="C33" s="20">
+        <v>5328</v>
+      </c>
+      <c r="D33" s="21">
+        <v>16610</v>
+      </c>
+      <c r="E33" s="21">
+        <v>14351</v>
+      </c>
+      <c r="F33" s="21">
+        <v>11332</v>
+      </c>
+      <c r="G33" s="22">
+        <f t="shared" si="0"/>
+        <v>16.61</v>
+      </c>
+      <c r="H33" s="22">
+        <f t="shared" si="1"/>
+        <v>14.351000000000001</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="2"/>
+        <v>1.4657606777267913</v>
+      </c>
+      <c r="J33" s="24"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>201.87</v>
+        <v>300.31</v>
       </c>
       <c r="C34" s="13">
-        <v>6413</v>
+        <v>7000</v>
       </c>
       <c r="D34" s="14">
-        <v>21142</v>
+        <v>15638</v>
       </c>
       <c r="E34" s="14">
-        <v>15352</v>
+        <v>13577</v>
       </c>
       <c r="F34" s="14">
-        <v>11986</v>
+        <v>9125</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>21.141999999999999</v>
+        <v>15.638</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>15.352</v>
+        <v>13.577</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.7638912064074754</v>
+        <v>1.7137534246575343</v>
       </c>
       <c r="J34" s="17"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="5">
-        <v>177.61</v>
-      </c>
-      <c r="C35" s="6">
-        <v>5367</v>
-      </c>
-      <c r="D35" s="7">
-        <v>20793</v>
-      </c>
-      <c r="E35" s="7">
-        <v>12433</v>
-      </c>
-      <c r="F35" s="7">
-        <v>8285</v>
-      </c>
-      <c r="G35" s="8">
-        <f t="shared" si="0"/>
-        <v>20.792999999999999</v>
-      </c>
-      <c r="H35" s="8">
-        <f t="shared" si="1"/>
-        <v>12.433</v>
-      </c>
-      <c r="I35" s="9">
-        <f t="shared" si="2"/>
-        <v>2.5097163548581776</v>
-      </c>
-      <c r="J35" s="10"/>
+      <c r="B35" s="19">
+        <v>196.28</v>
+      </c>
+      <c r="C35" s="20">
+        <v>6359</v>
+      </c>
+      <c r="D35" s="21">
+        <v>15638</v>
+      </c>
+      <c r="E35" s="21">
+        <v>13577</v>
+      </c>
+      <c r="F35" s="21">
+        <v>10196</v>
+      </c>
+      <c r="G35" s="22">
+        <f t="shared" si="0"/>
+        <v>15.638</v>
+      </c>
+      <c r="H35" s="22">
+        <f t="shared" si="1"/>
+        <v>13.577</v>
+      </c>
+      <c r="I35" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5337387210670852</v>
+      </c>
+      <c r="J35" s="24"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>174.68</v>
+        <v>60.51</v>
       </c>
       <c r="C36" s="13">
-        <v>5276</v>
+        <v>3703</v>
       </c>
       <c r="D36" s="14">
-        <v>20793</v>
+        <v>15600</v>
       </c>
       <c r="E36" s="14">
-        <v>12433</v>
+        <v>13480</v>
       </c>
       <c r="F36" s="14">
-        <v>9459</v>
+        <v>6700</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>20.792999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>12.433</v>
+        <v>13.48</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>2.1982239137329529</v>
+        <v>2.3283582089552239</v>
       </c>
       <c r="J36" s="17"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="5">
-        <v>299.8</v>
-      </c>
-      <c r="C37" s="6">
-        <v>7001</v>
-      </c>
-      <c r="D37" s="7">
-        <v>20509</v>
-      </c>
-      <c r="E37" s="7">
-        <v>15130</v>
-      </c>
-      <c r="F37" s="7">
-        <v>8178</v>
-      </c>
-      <c r="G37" s="8">
-        <f t="shared" ref="G37:G55" si="3">D37/1000</f>
-        <v>20.509</v>
-      </c>
-      <c r="H37" s="8">
-        <f t="shared" ref="H37:H55" si="4">E37/1000</f>
-        <v>15.13</v>
-      </c>
-      <c r="I37" s="9">
-        <f t="shared" ref="I37:I55" si="5">IFERROR(D37/F37,"")</f>
-        <v>2.507825874296894</v>
-      </c>
-      <c r="J37" s="10"/>
+      <c r="B37" s="19">
+        <v>58.94</v>
+      </c>
+      <c r="C37" s="20">
+        <v>3772</v>
+      </c>
+      <c r="D37" s="21">
+        <v>15058</v>
+      </c>
+      <c r="E37" s="21">
+        <v>13501</v>
+      </c>
+      <c r="F37" s="21">
+        <v>10512</v>
+      </c>
+      <c r="G37" s="22">
+        <f t="shared" si="0"/>
+        <v>15.058</v>
+      </c>
+      <c r="H37" s="22">
+        <f t="shared" si="1"/>
+        <v>13.500999999999999</v>
+      </c>
+      <c r="I37" s="23">
+        <f t="shared" si="2"/>
+        <v>1.4324581430745815</v>
+      </c>
+      <c r="J37" s="24"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>43.67</v>
+        <v>60.19</v>
       </c>
       <c r="C38" s="13">
-        <v>3710</v>
+        <v>3809</v>
       </c>
       <c r="D38" s="14">
-        <v>19797</v>
+        <v>15058</v>
       </c>
       <c r="E38" s="14">
-        <v>17257</v>
+        <v>13501</v>
       </c>
       <c r="F38" s="14">
-        <v>14089</v>
+        <v>10313</v>
       </c>
       <c r="G38" s="15">
-        <f t="shared" si="3"/>
-        <v>19.797000000000001</v>
+        <f t="shared" si="0"/>
+        <v>15.058</v>
       </c>
       <c r="H38" s="15">
-        <f t="shared" si="4"/>
-        <v>17.257000000000001</v>
+        <f t="shared" si="1"/>
+        <v>13.500999999999999</v>
       </c>
       <c r="I38" s="16">
-        <f t="shared" si="5"/>
-        <v>1.4051387607353254</v>
+        <f t="shared" si="2"/>
+        <v>1.4600989042955492</v>
       </c>
       <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="5">
-        <v>302.68</v>
-      </c>
-      <c r="C39" s="6">
-        <v>6953</v>
-      </c>
-      <c r="D39" s="7">
-        <v>18749</v>
-      </c>
-      <c r="E39" s="7">
-        <v>13521</v>
-      </c>
-      <c r="F39" s="7">
-        <v>6693</v>
-      </c>
-      <c r="G39" s="8">
-        <f t="shared" si="3"/>
-        <v>18.748999999999999</v>
-      </c>
-      <c r="H39" s="8">
-        <f t="shared" si="4"/>
-        <v>13.521000000000001</v>
-      </c>
-      <c r="I39" s="9">
-        <f t="shared" si="5"/>
-        <v>2.8012849245480353</v>
-      </c>
-      <c r="J39" s="10"/>
+      <c r="B39" s="19">
+        <v>65</v>
+      </c>
+      <c r="C39" s="20">
+        <v>3845</v>
+      </c>
+      <c r="D39" s="21">
+        <v>15040</v>
+      </c>
+      <c r="E39" s="21">
+        <v>13509</v>
+      </c>
+      <c r="F39" s="21">
+        <v>6902</v>
+      </c>
+      <c r="G39" s="22">
+        <f t="shared" si="0"/>
+        <v>15.04</v>
+      </c>
+      <c r="H39" s="22">
+        <f t="shared" si="1"/>
+        <v>13.509</v>
+      </c>
+      <c r="I39" s="23">
+        <f t="shared" si="2"/>
+        <v>2.1790785279629095</v>
+      </c>
+      <c r="J39" s="24"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>140.68</v>
+        <v>124</v>
       </c>
       <c r="C40" s="13">
-        <v>4965</v>
+        <v>4814</v>
       </c>
       <c r="D40" s="14">
-        <v>17235</v>
+        <v>14377</v>
       </c>
       <c r="E40" s="14">
-        <v>13927</v>
+        <v>12747</v>
       </c>
       <c r="F40" s="14">
-        <v>10711</v>
+        <v>9977</v>
       </c>
       <c r="G40" s="15">
-        <f t="shared" si="3"/>
-        <v>17.234999999999999</v>
+        <f t="shared" si="0"/>
+        <v>14.377000000000001</v>
       </c>
       <c r="H40" s="15">
-        <f t="shared" si="4"/>
-        <v>13.927</v>
+        <f t="shared" si="1"/>
+        <v>12.747</v>
       </c>
       <c r="I40" s="16">
-        <f t="shared" si="5"/>
-        <v>1.6090934553263001</v>
+        <f t="shared" si="2"/>
+        <v>1.4410143329658214</v>
       </c>
       <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="5">
-        <v>60.51</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3703</v>
-      </c>
-      <c r="D41" s="7">
-        <v>16256</v>
-      </c>
-      <c r="E41" s="7">
-        <v>13518</v>
-      </c>
-      <c r="F41" s="7">
-        <v>6700</v>
-      </c>
-      <c r="G41" s="8">
-        <f t="shared" si="3"/>
-        <v>16.256</v>
-      </c>
-      <c r="H41" s="8">
-        <f t="shared" si="4"/>
-        <v>13.518000000000001</v>
-      </c>
-      <c r="I41" s="9">
-        <f t="shared" si="5"/>
-        <v>2.426268656716418</v>
-      </c>
-      <c r="J41" s="10"/>
+      <c r="B41" s="19">
+        <v>177.61</v>
+      </c>
+      <c r="C41" s="20">
+        <v>5367</v>
+      </c>
+      <c r="D41" s="21">
+        <v>13635</v>
+      </c>
+      <c r="E41" s="21">
+        <v>12419</v>
+      </c>
+      <c r="F41" s="21">
+        <v>8285</v>
+      </c>
+      <c r="G41" s="22">
+        <f t="shared" si="0"/>
+        <v>13.635</v>
+      </c>
+      <c r="H41" s="22">
+        <f t="shared" si="1"/>
+        <v>12.419</v>
+      </c>
+      <c r="I41" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6457453228726615</v>
+      </c>
+      <c r="J41" s="24"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="12">
-        <v>65</v>
+        <v>80.13</v>
       </c>
       <c r="C42" s="13">
-        <v>3845</v>
+        <v>4466</v>
       </c>
       <c r="D42" s="14">
-        <v>15979</v>
+        <v>13533</v>
       </c>
       <c r="E42" s="14">
-        <v>13548</v>
+        <v>11084</v>
       </c>
       <c r="F42" s="14">
-        <v>6902</v>
+        <v>7792</v>
       </c>
       <c r="G42" s="15">
-        <f t="shared" si="3"/>
-        <v>15.978999999999999</v>
+        <f t="shared" si="0"/>
+        <v>13.532999999999999</v>
       </c>
       <c r="H42" s="15">
-        <f t="shared" si="4"/>
-        <v>13.548</v>
+        <f t="shared" si="1"/>
+        <v>11.084</v>
       </c>
       <c r="I42" s="16">
-        <f t="shared" si="5"/>
-        <v>2.3151260504201683</v>
+        <f t="shared" si="2"/>
+        <v>1.7367813141683779</v>
       </c>
       <c r="J42" s="17"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="5">
-        <v>60.19</v>
-      </c>
-      <c r="C43" s="6">
-        <v>3809</v>
-      </c>
-      <c r="D43" s="7">
-        <v>15979</v>
-      </c>
-      <c r="E43" s="7">
-        <v>13519</v>
-      </c>
-      <c r="F43" s="7">
-        <v>10313</v>
-      </c>
-      <c r="G43" s="8">
-        <f t="shared" si="3"/>
-        <v>15.978999999999999</v>
-      </c>
-      <c r="H43" s="8">
-        <f t="shared" si="4"/>
-        <v>13.519</v>
-      </c>
-      <c r="I43" s="9">
-        <f t="shared" si="5"/>
-        <v>1.549403665276835</v>
-      </c>
-      <c r="J43" s="10"/>
+      <c r="B43" s="19">
+        <v>60.87</v>
+      </c>
+      <c r="C43" s="20">
+        <v>3801</v>
+      </c>
+      <c r="D43" s="21">
+        <v>13533</v>
+      </c>
+      <c r="E43" s="21">
+        <v>11987</v>
+      </c>
+      <c r="F43" s="21">
+        <v>8017</v>
+      </c>
+      <c r="G43" s="22">
+        <f t="shared" si="0"/>
+        <v>13.532999999999999</v>
+      </c>
+      <c r="H43" s="22">
+        <f t="shared" si="1"/>
+        <v>11.987</v>
+      </c>
+      <c r="I43" s="23">
+        <f t="shared" si="2"/>
+        <v>1.6880379194212298</v>
+      </c>
+      <c r="J43" s="24"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>51</v>
       </c>
       <c r="B44" s="12">
-        <v>124</v>
+        <v>59.79</v>
       </c>
       <c r="C44" s="13">
-        <v>4814</v>
+        <v>3770</v>
       </c>
       <c r="D44" s="14">
-        <v>15979</v>
+        <v>13519</v>
       </c>
       <c r="E44" s="14">
-        <v>12792</v>
+        <v>11590</v>
       </c>
       <c r="F44" s="14">
-        <v>9977</v>
+        <v>9014</v>
       </c>
       <c r="G44" s="15">
-        <f t="shared" si="3"/>
-        <v>15.978999999999999</v>
+        <f t="shared" si="0"/>
+        <v>13.519</v>
       </c>
       <c r="H44" s="15">
-        <f t="shared" si="4"/>
-        <v>12.792</v>
+        <f t="shared" si="1"/>
+        <v>11.59</v>
       </c>
       <c r="I44" s="16">
-        <f t="shared" si="5"/>
-        <v>1.6015836423774681</v>
+        <f t="shared" si="2"/>
+        <v>1.4997781229199023</v>
       </c>
       <c r="J44" s="17"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="5">
-        <v>58.94</v>
-      </c>
-      <c r="C45" s="6">
-        <v>3772</v>
-      </c>
-      <c r="D45" s="7">
-        <v>15950</v>
-      </c>
-      <c r="E45" s="7">
-        <v>13527</v>
-      </c>
-      <c r="F45" s="7">
-        <v>10512</v>
-      </c>
-      <c r="G45" s="8">
-        <f t="shared" si="3"/>
-        <v>15.95</v>
-      </c>
-      <c r="H45" s="8">
-        <f t="shared" si="4"/>
-        <v>13.526999999999999</v>
-      </c>
-      <c r="I45" s="9">
-        <f t="shared" si="5"/>
-        <v>1.5173135464231355</v>
-      </c>
-      <c r="J45" s="10"/>
+      <c r="B45" s="19">
+        <v>59.61</v>
+      </c>
+      <c r="C45" s="20">
+        <v>3784</v>
+      </c>
+      <c r="D45" s="21">
+        <v>13519</v>
+      </c>
+      <c r="E45" s="21">
+        <v>11987</v>
+      </c>
+      <c r="F45" s="21">
+        <v>9228</v>
+      </c>
+      <c r="G45" s="22">
+        <f t="shared" si="0"/>
+        <v>13.519</v>
+      </c>
+      <c r="H45" s="22">
+        <f t="shared" si="1"/>
+        <v>11.987</v>
+      </c>
+      <c r="I45" s="23">
+        <f t="shared" si="2"/>
+        <v>1.4649978326831383</v>
+      </c>
+      <c r="J45" s="24"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>59.79</v>
+        <v>113.78</v>
       </c>
       <c r="C46" s="13">
-        <v>3770</v>
+        <v>4554</v>
       </c>
       <c r="D46" s="14">
-        <v>15411</v>
+        <v>11642</v>
       </c>
       <c r="E46" s="14">
-        <v>11634</v>
+        <v>11084</v>
       </c>
       <c r="F46" s="14">
-        <v>9014</v>
+        <v>8753</v>
       </c>
       <c r="G46" s="15">
-        <f t="shared" si="3"/>
-        <v>15.411</v>
+        <f t="shared" si="0"/>
+        <v>11.641999999999999</v>
       </c>
       <c r="H46" s="15">
-        <f t="shared" si="4"/>
-        <v>11.634</v>
+        <f t="shared" si="1"/>
+        <v>11.084</v>
       </c>
       <c r="I46" s="16">
-        <f t="shared" si="5"/>
-        <v>1.7096738406922565</v>
+        <f t="shared" si="2"/>
+        <v>1.3300582657374613</v>
       </c>
       <c r="J46" s="17"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="5">
-        <v>113.78</v>
-      </c>
-      <c r="C47" s="6">
-        <v>4554</v>
-      </c>
-      <c r="D47" s="7">
-        <v>15273</v>
-      </c>
-      <c r="E47" s="7">
-        <v>11123</v>
-      </c>
-      <c r="F47" s="7">
-        <v>8753</v>
-      </c>
-      <c r="G47" s="8">
-        <f t="shared" si="3"/>
-        <v>15.273</v>
-      </c>
-      <c r="H47" s="8">
-        <f t="shared" si="4"/>
-        <v>11.122999999999999</v>
-      </c>
-      <c r="I47" s="9">
-        <f t="shared" si="5"/>
-        <v>1.7448874671541186</v>
-      </c>
-      <c r="J47" s="10"/>
+      <c r="B47" s="19">
+        <v>18.11</v>
+      </c>
+      <c r="C47" s="20">
+        <v>1911</v>
+      </c>
+      <c r="D47" s="21">
+        <v>11529</v>
+      </c>
+      <c r="E47" s="21">
+        <v>10849</v>
+      </c>
+      <c r="F47" s="21">
+        <v>8310</v>
+      </c>
+      <c r="G47" s="22">
+        <f t="shared" si="0"/>
+        <v>11.529</v>
+      </c>
+      <c r="H47" s="22">
+        <f t="shared" si="1"/>
+        <v>10.849</v>
+      </c>
+      <c r="I47" s="23">
+        <f t="shared" si="2"/>
+        <v>1.3873646209386281</v>
+      </c>
+      <c r="J47" s="24"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="12">
-        <v>60.87</v>
+        <v>70.98</v>
       </c>
       <c r="C48" s="13">
-        <v>3801</v>
+        <v>3651</v>
       </c>
       <c r="D48" s="14">
-        <v>14667</v>
+        <v>11426</v>
       </c>
       <c r="E48" s="14">
-        <v>12020</v>
+        <v>9691</v>
       </c>
       <c r="F48" s="14">
-        <v>8017</v>
+        <v>7484</v>
       </c>
       <c r="G48" s="15">
-        <f t="shared" si="3"/>
-        <v>14.667</v>
+        <f t="shared" si="0"/>
+        <v>11.426</v>
       </c>
       <c r="H48" s="15">
-        <f t="shared" si="4"/>
-        <v>12.02</v>
+        <f t="shared" si="1"/>
+        <v>9.6910000000000007</v>
       </c>
       <c r="I48" s="16">
-        <f t="shared" si="5"/>
-        <v>1.829487339403767</v>
+        <f t="shared" si="2"/>
+        <v>1.5267236771779797</v>
       </c>
       <c r="J48" s="17"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="5">
-        <v>59.61</v>
-      </c>
-      <c r="C49" s="6">
-        <v>3784</v>
-      </c>
-      <c r="D49" s="7">
-        <v>14656</v>
-      </c>
-      <c r="E49" s="7">
-        <v>12023</v>
-      </c>
-      <c r="F49" s="7">
-        <v>9228</v>
-      </c>
-      <c r="G49" s="8">
-        <f t="shared" si="3"/>
-        <v>14.656000000000001</v>
-      </c>
-      <c r="H49" s="8">
-        <f t="shared" si="4"/>
-        <v>12.023</v>
-      </c>
-      <c r="I49" s="9">
-        <f t="shared" si="5"/>
-        <v>1.588209796272215</v>
-      </c>
-      <c r="J49" s="10"/>
+      <c r="B49" s="19">
+        <v>19.78</v>
+      </c>
+      <c r="C49" s="20">
+        <v>2018</v>
+      </c>
+      <c r="D49" s="21">
+        <v>10419</v>
+      </c>
+      <c r="E49" s="21">
+        <v>9645</v>
+      </c>
+      <c r="F49" s="21">
+        <v>8848</v>
+      </c>
+      <c r="G49" s="22">
+        <f t="shared" si="0"/>
+        <v>10.419</v>
+      </c>
+      <c r="H49" s="22">
+        <f t="shared" si="1"/>
+        <v>9.6449999999999996</v>
+      </c>
+      <c r="I49" s="23">
+        <f t="shared" si="2"/>
+        <v>1.1775542495479205</v>
+      </c>
+      <c r="J49" s="24"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B50" s="12">
-        <v>80.13</v>
+        <v>88.51</v>
       </c>
       <c r="C50" s="13">
-        <v>4466</v>
+        <v>3848</v>
       </c>
       <c r="D50" s="14">
-        <v>14524</v>
+        <v>9767</v>
       </c>
       <c r="E50" s="14">
-        <v>11107</v>
+        <v>8662</v>
       </c>
       <c r="F50" s="14">
-        <v>7792</v>
+        <v>6820</v>
       </c>
       <c r="G50" s="15">
-        <f t="shared" si="3"/>
-        <v>14.523999999999999</v>
+        <f t="shared" si="0"/>
+        <v>9.7669999999999995</v>
       </c>
       <c r="H50" s="15">
-        <f t="shared" si="4"/>
-        <v>11.106999999999999</v>
+        <f t="shared" si="1"/>
+        <v>8.6620000000000008</v>
       </c>
       <c r="I50" s="16">
-        <f t="shared" si="5"/>
-        <v>1.8639630390143738</v>
+        <f t="shared" si="2"/>
+        <v>1.4321114369501466</v>
       </c>
       <c r="J50" s="17"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="5">
-        <v>18.11</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1911</v>
-      </c>
-      <c r="D51" s="7">
-        <v>11633</v>
-      </c>
-      <c r="E51" s="7">
-        <v>9580</v>
-      </c>
-      <c r="F51" s="7">
-        <v>8310</v>
-      </c>
-      <c r="G51" s="8">
-        <f t="shared" si="3"/>
-        <v>11.632999999999999</v>
-      </c>
-      <c r="H51" s="8">
-        <f t="shared" si="4"/>
-        <v>9.58</v>
-      </c>
-      <c r="I51" s="9">
-        <f t="shared" si="5"/>
-        <v>1.3998796630565584</v>
-      </c>
-      <c r="J51" s="10"/>
+      <c r="B51" s="19">
+        <v>75.31</v>
+      </c>
+      <c r="C51" s="20">
+        <v>3891</v>
+      </c>
+      <c r="D51" s="21">
+        <v>9113</v>
+      </c>
+      <c r="E51" s="21">
+        <v>7408</v>
+      </c>
+      <c r="F51" s="21">
+        <v>6142</v>
+      </c>
+      <c r="G51" s="22">
+        <f t="shared" si="0"/>
+        <v>9.1129999999999995</v>
+      </c>
+      <c r="H51" s="22">
+        <f t="shared" si="1"/>
+        <v>7.4080000000000004</v>
+      </c>
+      <c r="I51" s="23">
+        <f t="shared" si="2"/>
+        <v>1.4837186584174535</v>
+      </c>
+      <c r="J51" s="24"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="12">
-        <v>70.98</v>
-      </c>
-      <c r="C52" s="13">
-        <v>3651</v>
-      </c>
-      <c r="D52" s="14">
-        <v>11453</v>
-      </c>
-      <c r="E52" s="14">
-        <v>9730</v>
-      </c>
-      <c r="F52" s="14">
-        <v>7484</v>
-      </c>
-      <c r="G52" s="15">
-        <f t="shared" si="3"/>
-        <v>11.452999999999999</v>
-      </c>
-      <c r="H52" s="15">
-        <f t="shared" si="4"/>
-        <v>9.73</v>
-      </c>
-      <c r="I52" s="16">
-        <f t="shared" si="5"/>
-        <v>1.530331373597007</v>
-      </c>
-      <c r="J52" s="17"/>
+      <c r="B52" s="5">
+        <v>149.61000000000001</v>
+      </c>
+      <c r="C52" s="6">
+        <v>5003</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F52" s="7">
+        <v>15887</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J52" s="28" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="5">
+        <v>131.51</v>
+      </c>
+      <c r="C53" s="6">
+        <v>4710</v>
+      </c>
+      <c r="D53" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="5">
-        <v>19.78</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2018</v>
-      </c>
-      <c r="D53" s="7">
-        <v>11036</v>
-      </c>
-      <c r="E53" s="7">
-        <v>9686</v>
+      <c r="E53" s="25" t="s">
+        <v>60</v>
       </c>
       <c r="F53" s="7">
-        <v>8848</v>
-      </c>
-      <c r="G53" s="8">
-        <f t="shared" si="3"/>
-        <v>11.036</v>
-      </c>
-      <c r="H53" s="8">
-        <f t="shared" si="4"/>
-        <v>9.6859999999999999</v>
-      </c>
-      <c r="I53" s="9">
-        <f t="shared" si="5"/>
-        <v>1.2472875226039783</v>
-      </c>
-      <c r="J53" s="10"/>
+        <v>14642</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H53" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I53" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J53" s="28" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="5">
+        <v>67.459999999999994</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3607</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="7">
+        <v>16250</v>
+      </c>
+      <c r="G54" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B54" s="12">
-        <v>88.51</v>
-      </c>
-      <c r="C54" s="13">
-        <v>3848</v>
-      </c>
-      <c r="D54" s="14">
-        <v>10603</v>
-      </c>
-      <c r="E54" s="14">
-        <v>8697</v>
-      </c>
-      <c r="F54" s="14">
-        <v>6820</v>
-      </c>
-      <c r="G54" s="15">
-        <f t="shared" si="3"/>
-        <v>10.603</v>
-      </c>
-      <c r="H54" s="15">
-        <f t="shared" si="4"/>
-        <v>8.6969999999999992</v>
-      </c>
-      <c r="I54" s="16">
-        <f t="shared" si="5"/>
-        <v>1.5546920821114369</v>
-      </c>
-      <c r="J54" s="17"/>
+      <c r="H54" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J54" s="28" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="5">
+        <v>140.69</v>
+      </c>
+      <c r="C55" s="6">
+        <v>4981</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" s="7">
+        <v>14856</v>
+      </c>
+      <c r="G55" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H55" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J55" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B55" s="5">
-        <v>75.31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>3891</v>
-      </c>
-      <c r="D55" s="7">
-        <v>9546</v>
-      </c>
-      <c r="E55" s="7">
-        <v>7441</v>
-      </c>
-      <c r="F55" s="7">
-        <v>6142</v>
-      </c>
-      <c r="G55" s="8">
-        <f t="shared" si="3"/>
-        <v>9.5459999999999994</v>
-      </c>
-      <c r="H55" s="8">
-        <f t="shared" si="4"/>
-        <v>7.4409999999999998</v>
-      </c>
-      <c r="I55" s="9">
-        <f t="shared" si="5"/>
-        <v>1.5542168674698795</v>
-      </c>
-      <c r="J55" s="10"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="19">
+      <c r="A57" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="30">
         <f>SUM(B5:B55)</f>
-        <v>6880.8099999999995</v>
-      </c>
-      <c r="D57" s="20">
+        <v>6880.8099999999986</v>
+      </c>
+      <c r="D57" s="31">
         <f>MAX(D5:D55)</f>
-        <v>27126</v>
-      </c>
-      <c r="G57" s="21">
+        <v>39828</v>
+      </c>
+      <c r="G57" s="32">
         <f>IFERROR(MAX(G5:G55),"")</f>
-        <v>27.126000000000001</v>
-      </c>
-      <c r="I57" s="22">
+        <v>39.828000000000003</v>
+      </c>
+      <c r="I57" s="33">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
-        <v>1.8302101287803956</v>
+        <v>1.762438528300619</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="23" t="s">
-        <v>64</v>
+      <c r="A58" s="34" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2512,88 +2548,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>65</v>
+      <c r="A1" s="35" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>67</v>
+      <c r="A3" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>69</v>
+      <c r="A4" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>71</v>
+      <c r="A5" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>73</v>
+      <c r="A6" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>75</v>
+      <c r="A7" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>77</v>
+      <c r="A8" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>79</v>
+      <c r="A9" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>81</v>
+      <c r="A10" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>83</v>
+      <c r="A11" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>85</v>
+      <c r="A12" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80D2A3C-6A57-4981-B255-8E947EBDFFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE5BDF6-9E8B-4B77-A010-E6BFD4C9FA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>FAZENDA P.PEDRA — distância dos talhões até a sede</t>
   </si>
@@ -72,99 +72,114 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-17</t>
+  </si>
+  <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-05A</t>
+  </si>
+  <si>
+    <t>T-05S</t>
+  </si>
+  <si>
+    <t>T37</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>T34</t>
+  </si>
+  <si>
+    <t>T-16B</t>
+  </si>
+  <si>
+    <t>T38</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-24</t>
+  </si>
+  <si>
+    <t>T-06A</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
+    <t>T-19</t>
+  </si>
+  <si>
+    <t>T-16A</t>
+  </si>
+  <si>
+    <t>T-07A</t>
+  </si>
+  <si>
+    <t>T-18</t>
+  </si>
+  <si>
+    <t>T-15A</t>
+  </si>
+  <si>
     <t>T-23</t>
   </si>
   <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-15B</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-22</t>
+  </si>
+  <si>
+    <t>T-01C</t>
+  </si>
+  <si>
+    <t>T-22A</t>
+  </si>
+  <si>
     <t>T-20</t>
   </si>
   <si>
+    <t>T-01B</t>
+  </si>
+  <si>
     <t>T-12</t>
   </si>
   <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-05S</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-18</t>
-  </si>
-  <si>
-    <t>T-16B</t>
-  </si>
-  <si>
-    <t>T-15B</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T31</t>
-  </si>
-  <si>
-    <t>T-15C</t>
-  </si>
-  <si>
-    <t>T-06A</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-16A</t>
-  </si>
-  <si>
-    <t>T-07A</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T-15A</t>
-  </si>
-  <si>
-    <t>T30</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-01C</t>
-  </si>
-  <si>
-    <t>T-22</t>
-  </si>
-  <si>
-    <t>T-22A</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-13</t>
-  </si>
-  <si>
     <t>T-01A</t>
   </si>
   <si>
@@ -174,36 +189,33 @@
     <t>T-21</t>
   </si>
   <si>
-    <t>T-01B</t>
-  </si>
-  <si>
     <t>T-21A</t>
   </si>
   <si>
+    <t>T-11</t>
+  </si>
+  <si>
+    <t>T-12S</t>
+  </si>
+  <si>
+    <t>T-10S</t>
+  </si>
+  <si>
+    <t>T-10A</t>
+  </si>
+  <si>
+    <t>T-11A</t>
+  </si>
+  <si>
+    <t>T-26</t>
+  </si>
+  <si>
+    <t>T-27</t>
+  </si>
+  <si>
     <t>T-10B</t>
   </si>
   <si>
-    <t>T-10A</t>
-  </si>
-  <si>
-    <t>T-10S</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-12S</t>
-  </si>
-  <si>
-    <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-26</t>
-  </si>
-  <si>
-    <t>T-27</t>
-  </si>
-  <si>
     <t>T-25</t>
   </si>
   <si>
@@ -211,27 +223,6 @@
   </si>
   <si>
     <t>T-29</t>
-  </si>
-  <si>
-    <t>T33</t>
-  </si>
-  <si>
-    <t>sem acesso</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>sem estrada até este talhão</t>
-  </si>
-  <si>
-    <t>T34</t>
-  </si>
-  <si>
-    <t>T37</t>
-  </si>
-  <si>
-    <t>T38</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -310,7 +301,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,17 +347,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
@@ -378,7 +358,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,11 +368,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -422,13 +397,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -436,35 +418,13 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -833,97 +793,97 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>201.87</v>
+        <v>140.75</v>
       </c>
       <c r="C5" s="6">
-        <v>6413</v>
+        <v>5173</v>
       </c>
       <c r="D5" s="7">
-        <v>39828</v>
+        <v>24868</v>
       </c>
       <c r="E5" s="7">
-        <v>36213</v>
+        <v>23146</v>
       </c>
       <c r="F5" s="7">
-        <v>11986</v>
+        <v>15747</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G51" si="0">D5/1000</f>
-        <v>39.828000000000003</v>
+        <f t="shared" ref="G5:G36" si="0">D5/1000</f>
+        <v>24.867999999999999</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H51" si="1">E5/1000</f>
-        <v>36.213000000000001</v>
+        <f t="shared" ref="H5:H36" si="1">E5/1000</f>
+        <v>23.146000000000001</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I51" si="2">IFERROR(D5/F5,"")</f>
-        <v>3.3228766894710495</v>
+        <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
+        <v>1.5792214390042547</v>
       </c>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
-        <v>140.68</v>
-      </c>
-      <c r="C6" s="6">
-        <v>4965</v>
-      </c>
-      <c r="D6" s="7">
-        <v>36293</v>
-      </c>
-      <c r="E6" s="7">
-        <v>34692</v>
-      </c>
-      <c r="F6" s="7">
-        <v>10711</v>
-      </c>
-      <c r="G6" s="8">
-        <f t="shared" si="0"/>
-        <v>36.292999999999999</v>
-      </c>
-      <c r="H6" s="8">
-        <f t="shared" si="1"/>
-        <v>34.692</v>
-      </c>
-      <c r="I6" s="9">
-        <f t="shared" si="2"/>
-        <v>3.388385771636635</v>
-      </c>
-      <c r="J6" s="10"/>
+      <c r="B6" s="12">
+        <v>124.34</v>
+      </c>
+      <c r="C6" s="13">
+        <v>4758</v>
+      </c>
+      <c r="D6" s="14">
+        <v>24768</v>
+      </c>
+      <c r="E6" s="14">
+        <v>24146</v>
+      </c>
+      <c r="F6" s="14">
+        <v>15004</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="0"/>
+        <v>24.768000000000001</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="1"/>
+        <v>24.146000000000001</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="2"/>
+        <v>1.6507597973873633</v>
+      </c>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>174.68</v>
+        <v>175.27</v>
       </c>
       <c r="C7" s="6">
-        <v>5276</v>
+        <v>5486</v>
       </c>
       <c r="D7" s="7">
-        <v>35804</v>
+        <v>24224</v>
       </c>
       <c r="E7" s="7">
-        <v>34302</v>
+        <v>21178</v>
       </c>
       <c r="F7" s="7">
-        <v>9459</v>
+        <v>13634</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>35.804000000000002</v>
+        <v>24.224</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>34.302</v>
+        <v>21.178000000000001</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>3.785178137223808</v>
+        <v>1.7767346340032273</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -932,198 +892,198 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>150.72</v>
+        <v>71.5</v>
       </c>
       <c r="C8" s="13">
-        <v>5638</v>
+        <v>4054</v>
       </c>
       <c r="D8" s="14">
-        <v>31060</v>
+        <v>24199</v>
       </c>
       <c r="E8" s="14">
-        <v>28518</v>
+        <v>23437</v>
       </c>
       <c r="F8" s="14">
-        <v>13240</v>
+        <v>14361</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>31.06</v>
+        <v>24.199000000000002</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>28.518000000000001</v>
+        <v>23.437000000000001</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.3459214501510575</v>
+        <v>1.6850497876192465</v>
       </c>
       <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="19">
-        <v>83.32</v>
-      </c>
-      <c r="C9" s="20">
-        <v>3691</v>
-      </c>
-      <c r="D9" s="21">
-        <v>28627</v>
-      </c>
-      <c r="E9" s="21">
-        <v>27162</v>
-      </c>
-      <c r="F9" s="21">
-        <v>15125</v>
-      </c>
-      <c r="G9" s="22">
-        <f t="shared" si="0"/>
-        <v>28.626999999999999</v>
-      </c>
-      <c r="H9" s="22">
-        <f t="shared" si="1"/>
-        <v>27.161999999999999</v>
-      </c>
-      <c r="I9" s="23">
-        <f t="shared" si="2"/>
-        <v>1.8926942148760331</v>
-      </c>
-      <c r="J9" s="24"/>
+      <c r="B9" s="5">
+        <v>67.459999999999994</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3607</v>
+      </c>
+      <c r="D9" s="7">
+        <v>24081</v>
+      </c>
+      <c r="E9" s="7">
+        <v>22035</v>
+      </c>
+      <c r="F9" s="7">
+        <v>16250</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="0"/>
+        <v>24.081</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="1"/>
+        <v>22.035</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="2"/>
+        <v>1.4819076923076924</v>
+      </c>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>124.34</v>
+        <v>149.61000000000001</v>
       </c>
       <c r="C10" s="13">
-        <v>4758</v>
+        <v>5003</v>
       </c>
       <c r="D10" s="14">
-        <v>25385</v>
+        <v>23804</v>
       </c>
       <c r="E10" s="14">
-        <v>24763</v>
+        <v>21223</v>
       </c>
       <c r="F10" s="14">
-        <v>15004</v>
+        <v>15887</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>25.385000000000002</v>
+        <v>23.803999999999998</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>24.763000000000002</v>
+        <v>21.222999999999999</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.6918821647560651</v>
+        <v>1.4983319695348398</v>
       </c>
       <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="19">
-        <v>140.75</v>
-      </c>
-      <c r="C11" s="20">
-        <v>5173</v>
-      </c>
-      <c r="D11" s="21">
-        <v>25382</v>
-      </c>
-      <c r="E11" s="21">
-        <v>23120</v>
-      </c>
-      <c r="F11" s="21">
-        <v>15747</v>
-      </c>
-      <c r="G11" s="22">
-        <f t="shared" si="0"/>
-        <v>25.382000000000001</v>
-      </c>
-      <c r="H11" s="22">
-        <f t="shared" si="1"/>
-        <v>23.12</v>
-      </c>
-      <c r="I11" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6118625769987933</v>
-      </c>
-      <c r="J11" s="24"/>
+      <c r="B11" s="5">
+        <v>131.51</v>
+      </c>
+      <c r="C11" s="6">
+        <v>4710</v>
+      </c>
+      <c r="D11" s="7">
+        <v>23271</v>
+      </c>
+      <c r="E11" s="7">
+        <v>19919</v>
+      </c>
+      <c r="F11" s="7">
+        <v>14642</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>23.271000000000001</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
+        <v>19.919</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="2"/>
+        <v>1.5893320584619588</v>
+      </c>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>175.27</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="C12" s="13">
-        <v>5486</v>
+        <v>3913</v>
       </c>
       <c r="D12" s="14">
-        <v>24841</v>
+        <v>23203</v>
       </c>
       <c r="E12" s="14">
-        <v>23291</v>
+        <v>21068</v>
       </c>
       <c r="F12" s="14">
-        <v>13634</v>
+        <v>16110</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>24.841000000000001</v>
+        <v>23.202999999999999</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>23.291</v>
+        <v>21.068000000000001</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.821989144785096</v>
+        <v>1.4402855369335816</v>
       </c>
       <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="19">
-        <v>71.5</v>
-      </c>
-      <c r="C13" s="20">
-        <v>4054</v>
-      </c>
-      <c r="D13" s="21">
-        <v>24816</v>
-      </c>
-      <c r="E13" s="21">
-        <v>24054</v>
-      </c>
-      <c r="F13" s="21">
-        <v>14361</v>
-      </c>
-      <c r="G13" s="22">
-        <f t="shared" si="0"/>
-        <v>24.815999999999999</v>
-      </c>
-      <c r="H13" s="22">
-        <f t="shared" si="1"/>
-        <v>24.053999999999998</v>
-      </c>
-      <c r="I13" s="23">
-        <f t="shared" si="2"/>
-        <v>1.7280133695425111</v>
-      </c>
-      <c r="J13" s="24"/>
+      <c r="B13" s="5">
+        <v>140.69</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4981</v>
+      </c>
+      <c r="D13" s="7">
+        <v>23140</v>
+      </c>
+      <c r="E13" s="7">
+        <v>20628</v>
+      </c>
+      <c r="F13" s="7">
+        <v>14856</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>23.14</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="1"/>
+        <v>20.628</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="2"/>
+        <v>1.557619816908993</v>
+      </c>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
@@ -1136,1401 +1096,1405 @@
         <v>7372</v>
       </c>
       <c r="D14" s="14">
-        <v>23342</v>
+        <v>22738</v>
       </c>
       <c r="E14" s="14">
-        <v>21162</v>
+        <v>19115</v>
       </c>
       <c r="F14" s="14">
         <v>11657</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>23.341999999999999</v>
+        <v>22.738</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>21.161999999999999</v>
+        <v>19.114999999999998</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.0024019902204686</v>
+        <v>1.9505876297503646</v>
       </c>
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19">
-        <v>115.23</v>
-      </c>
-      <c r="C15" s="20">
-        <v>4528</v>
-      </c>
-      <c r="D15" s="21">
-        <v>23335</v>
-      </c>
-      <c r="E15" s="21">
-        <v>22531</v>
-      </c>
-      <c r="F15" s="21">
-        <v>14106</v>
-      </c>
-      <c r="G15" s="22">
-        <f t="shared" si="0"/>
-        <v>23.335000000000001</v>
-      </c>
-      <c r="H15" s="22">
-        <f t="shared" si="1"/>
-        <v>22.530999999999999</v>
-      </c>
-      <c r="I15" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6542605983269532</v>
-      </c>
-      <c r="J15" s="24"/>
+      <c r="B15" s="5">
+        <v>83.32</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3691</v>
+      </c>
+      <c r="D15" s="7">
+        <v>22560</v>
+      </c>
+      <c r="E15" s="7">
+        <v>21095</v>
+      </c>
+      <c r="F15" s="7">
+        <v>15125</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>22.56</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="1"/>
+        <v>21.094999999999999</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="2"/>
+        <v>1.4915702479338844</v>
+      </c>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>66.459999999999994</v>
+        <v>132.93</v>
       </c>
       <c r="C16" s="13">
-        <v>3913</v>
+        <v>4758</v>
       </c>
       <c r="D16" s="14">
-        <v>23178</v>
+        <v>22083</v>
       </c>
       <c r="E16" s="14">
-        <v>21042</v>
+        <v>19695</v>
       </c>
       <c r="F16" s="14">
-        <v>16110</v>
+        <v>14217</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>23.178000000000001</v>
+        <v>22.082999999999998</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>21.042000000000002</v>
+        <v>19.695</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.438733705772812</v>
+        <v>1.5532812829710909</v>
       </c>
       <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="19">
-        <v>80.430000000000007</v>
-      </c>
-      <c r="C17" s="20">
-        <v>4103</v>
-      </c>
-      <c r="D17" s="21">
-        <v>22284</v>
-      </c>
-      <c r="E17" s="21">
-        <v>21674</v>
-      </c>
-      <c r="F17" s="21">
-        <v>14168</v>
-      </c>
-      <c r="G17" s="22">
-        <f t="shared" si="0"/>
-        <v>22.283999999999999</v>
-      </c>
-      <c r="H17" s="22">
-        <f t="shared" si="1"/>
-        <v>21.673999999999999</v>
-      </c>
-      <c r="I17" s="23">
-        <f t="shared" si="2"/>
-        <v>1.572840203274986</v>
-      </c>
-      <c r="J17" s="24"/>
+      <c r="B17" s="5">
+        <v>144.9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>4944</v>
+      </c>
+      <c r="D17" s="7">
+        <v>21636</v>
+      </c>
+      <c r="E17" s="7">
+        <v>20656</v>
+      </c>
+      <c r="F17" s="7">
+        <v>15014</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="0"/>
+        <v>21.635999999999999</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="1"/>
+        <v>20.655999999999999</v>
+      </c>
+      <c r="I17" s="9">
+        <f t="shared" si="2"/>
+        <v>1.4410550153190356</v>
+      </c>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>144.9</v>
+        <v>239.17</v>
       </c>
       <c r="C18" s="13">
-        <v>4944</v>
+        <v>6359</v>
       </c>
       <c r="D18" s="14">
-        <v>21610</v>
+        <v>21530</v>
       </c>
       <c r="E18" s="14">
-        <v>20631</v>
+        <v>18647</v>
       </c>
       <c r="F18" s="14">
-        <v>15014</v>
+        <v>15489</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>21.61</v>
+        <v>21.53</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>20.631</v>
+        <v>18.646999999999998</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.439323298254962</v>
+        <v>1.3900187229646845</v>
       </c>
       <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="19">
-        <v>239.17</v>
-      </c>
-      <c r="C19" s="20">
-        <v>6359</v>
-      </c>
-      <c r="D19" s="21">
-        <v>21504</v>
-      </c>
-      <c r="E19" s="21">
-        <v>18621</v>
-      </c>
-      <c r="F19" s="21">
-        <v>15489</v>
-      </c>
-      <c r="G19" s="22">
-        <f t="shared" si="0"/>
-        <v>21.504000000000001</v>
-      </c>
-      <c r="H19" s="22">
-        <f t="shared" si="1"/>
-        <v>18.620999999999999</v>
-      </c>
-      <c r="I19" s="23">
-        <f t="shared" si="2"/>
-        <v>1.3883401123377881</v>
-      </c>
-      <c r="J19" s="24"/>
+      <c r="B19" s="5">
+        <v>136.18</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4817</v>
+      </c>
+      <c r="D19" s="7">
+        <v>21259</v>
+      </c>
+      <c r="E19" s="7">
+        <v>19732</v>
+      </c>
+      <c r="F19" s="7">
+        <v>14928</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>21.259</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>19.731999999999999</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>1.4241023579849947</v>
+      </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>136.18</v>
+        <v>53.96</v>
       </c>
       <c r="C20" s="13">
-        <v>4817</v>
+        <v>3674</v>
       </c>
       <c r="D20" s="14">
-        <v>21249</v>
+        <v>21206</v>
       </c>
       <c r="E20" s="14">
-        <v>19706</v>
+        <v>19339</v>
       </c>
       <c r="F20" s="14">
-        <v>14928</v>
+        <v>13875</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>21.248999999999999</v>
+        <v>21.206</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>19.706</v>
+        <v>19.338999999999999</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.4234324758842443</v>
+        <v>1.5283603603603604</v>
       </c>
       <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="19">
-        <v>132.93</v>
-      </c>
-      <c r="C21" s="20">
-        <v>4758</v>
-      </c>
-      <c r="D21" s="21">
-        <v>21215</v>
-      </c>
-      <c r="E21" s="21">
-        <v>19669</v>
-      </c>
-      <c r="F21" s="21">
-        <v>14217</v>
-      </c>
-      <c r="G21" s="22">
-        <f t="shared" si="0"/>
-        <v>21.215</v>
-      </c>
-      <c r="H21" s="22">
-        <f t="shared" si="1"/>
-        <v>19.669</v>
-      </c>
-      <c r="I21" s="23">
-        <f t="shared" si="2"/>
-        <v>1.4922276148273195</v>
-      </c>
-      <c r="J21" s="24"/>
+      <c r="B21" s="5">
+        <v>150.72</v>
+      </c>
+      <c r="C21" s="6">
+        <v>5638</v>
+      </c>
+      <c r="D21" s="7">
+        <v>21204</v>
+      </c>
+      <c r="E21" s="7">
+        <v>18661</v>
+      </c>
+      <c r="F21" s="7">
+        <v>13240</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>21.204000000000001</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="1"/>
+        <v>18.661000000000001</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="2"/>
+        <v>1.6015105740181268</v>
+      </c>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>278.49</v>
+        <v>56.03</v>
       </c>
       <c r="C22" s="13">
-        <v>7339</v>
+        <v>3746</v>
       </c>
       <c r="D22" s="14">
-        <v>21212</v>
+        <v>21117</v>
       </c>
       <c r="E22" s="14">
-        <v>19208</v>
+        <v>20656</v>
       </c>
       <c r="F22" s="14">
-        <v>9892</v>
+        <v>15750</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>21.212</v>
+        <v>21.117000000000001</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>19.207999999999998</v>
+        <v>20.655999999999999</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>2.144359078042863</v>
+        <v>1.3407619047619048</v>
       </c>
       <c r="J22" s="17"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="19">
-        <v>53.96</v>
-      </c>
-      <c r="C23" s="20">
-        <v>3674</v>
-      </c>
-      <c r="D23" s="21">
-        <v>21189</v>
-      </c>
-      <c r="E23" s="21">
-        <v>19314</v>
-      </c>
-      <c r="F23" s="21">
-        <v>13875</v>
-      </c>
-      <c r="G23" s="22">
-        <f t="shared" si="0"/>
-        <v>21.189</v>
-      </c>
-      <c r="H23" s="22">
-        <f t="shared" si="1"/>
-        <v>19.314</v>
-      </c>
-      <c r="I23" s="23">
-        <f t="shared" si="2"/>
-        <v>1.5271351351351352</v>
-      </c>
-      <c r="J23" s="24"/>
+      <c r="B23" s="5">
+        <v>254.67</v>
+      </c>
+      <c r="C23" s="6">
+        <v>6809</v>
+      </c>
+      <c r="D23" s="7">
+        <v>20845</v>
+      </c>
+      <c r="E23" s="7">
+        <v>17619</v>
+      </c>
+      <c r="F23" s="7">
+        <v>12367</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="0"/>
+        <v>20.844999999999999</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="1"/>
+        <v>17.619</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="2"/>
+        <v>1.6855340826392819</v>
+      </c>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>56.03</v>
+        <v>115.23</v>
       </c>
       <c r="C24" s="13">
-        <v>3746</v>
+        <v>4528</v>
       </c>
       <c r="D24" s="14">
-        <v>21092</v>
+        <v>20668</v>
       </c>
       <c r="E24" s="14">
-        <v>20631</v>
+        <v>19115</v>
       </c>
       <c r="F24" s="14">
-        <v>15750</v>
+        <v>14106</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>21.091999999999999</v>
+        <v>20.667999999999999</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>20.631</v>
+        <v>19.114999999999998</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.3391746031746032</v>
+        <v>1.4651921168297179</v>
       </c>
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="19">
-        <v>254.67</v>
-      </c>
-      <c r="C25" s="20">
-        <v>6809</v>
-      </c>
-      <c r="D25" s="21">
-        <v>19570</v>
-      </c>
-      <c r="E25" s="21">
-        <v>17594</v>
-      </c>
-      <c r="F25" s="21">
-        <v>12367</v>
-      </c>
-      <c r="G25" s="22">
-        <f t="shared" si="0"/>
-        <v>19.57</v>
-      </c>
-      <c r="H25" s="22">
-        <f t="shared" si="1"/>
-        <v>17.594000000000001</v>
-      </c>
-      <c r="I25" s="23">
-        <f t="shared" si="2"/>
-        <v>1.5824371310746341</v>
-      </c>
-      <c r="J25" s="24"/>
+      <c r="B25" s="5">
+        <v>169.72</v>
+      </c>
+      <c r="C25" s="6">
+        <v>5278</v>
+      </c>
+      <c r="D25" s="7">
+        <v>20224</v>
+      </c>
+      <c r="E25" s="7">
+        <v>17619</v>
+      </c>
+      <c r="F25" s="7">
+        <v>13180</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" si="0"/>
+        <v>20.224</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="1"/>
+        <v>17.619</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="2"/>
+        <v>1.5344461305007586</v>
+      </c>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>299.8</v>
+        <v>201.87</v>
       </c>
       <c r="C26" s="13">
-        <v>7001</v>
+        <v>6413</v>
       </c>
       <c r="D26" s="14">
-        <v>19257</v>
+        <v>20105</v>
       </c>
       <c r="E26" s="14">
-        <v>17178</v>
+        <v>16490</v>
       </c>
       <c r="F26" s="14">
-        <v>8178</v>
+        <v>11986</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>19.257000000000001</v>
+        <v>20.105</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>17.178000000000001</v>
+        <v>16.489999999999998</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.3547322083639033</v>
+        <v>1.6773736025362924</v>
       </c>
       <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="19">
-        <v>169.72</v>
-      </c>
-      <c r="C27" s="20">
-        <v>5278</v>
-      </c>
-      <c r="D27" s="21">
-        <v>18861</v>
-      </c>
-      <c r="E27" s="21">
-        <v>17594</v>
-      </c>
-      <c r="F27" s="21">
-        <v>13180</v>
-      </c>
-      <c r="G27" s="22">
-        <f t="shared" si="0"/>
-        <v>18.861000000000001</v>
-      </c>
-      <c r="H27" s="22">
-        <f t="shared" si="1"/>
-        <v>17.594000000000001</v>
-      </c>
-      <c r="I27" s="23">
-        <f t="shared" si="2"/>
-        <v>1.43103186646434</v>
-      </c>
-      <c r="J27" s="24"/>
+      <c r="B27" s="5">
+        <v>270.48</v>
+      </c>
+      <c r="C27" s="6">
+        <v>6729</v>
+      </c>
+      <c r="D27" s="7">
+        <v>19493</v>
+      </c>
+      <c r="E27" s="7">
+        <v>15612</v>
+      </c>
+      <c r="F27" s="7">
+        <v>11611</v>
+      </c>
+      <c r="G27" s="8">
+        <f t="shared" si="0"/>
+        <v>19.492999999999999</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="1"/>
+        <v>15.612</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="2"/>
+        <v>1.6788390319524589</v>
+      </c>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>43.67</v>
+        <v>80.430000000000007</v>
       </c>
       <c r="C28" s="13">
-        <v>3710</v>
+        <v>4103</v>
       </c>
       <c r="D28" s="14">
-        <v>18671</v>
+        <v>19386</v>
       </c>
       <c r="E28" s="14">
-        <v>17219</v>
+        <v>18808</v>
       </c>
       <c r="F28" s="14">
-        <v>14089</v>
+        <v>14168</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>18.670999999999999</v>
+        <v>19.385999999999999</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>17.219000000000001</v>
+        <v>18.808</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.3252182553765348</v>
+        <v>1.3682947487295314</v>
       </c>
       <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="5">
         <v>300.64</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="6">
         <v>7008</v>
       </c>
-      <c r="D29" s="21">
-        <v>17643</v>
-      </c>
-      <c r="E29" s="21">
-        <v>15587</v>
-      </c>
-      <c r="F29" s="21">
+      <c r="D29" s="7">
+        <v>19175</v>
+      </c>
+      <c r="E29" s="7">
+        <v>15612</v>
+      </c>
+      <c r="F29" s="7">
         <v>10680</v>
       </c>
-      <c r="G29" s="22">
-        <f t="shared" si="0"/>
-        <v>17.643000000000001</v>
-      </c>
-      <c r="H29" s="22">
-        <f t="shared" si="1"/>
-        <v>15.587</v>
-      </c>
-      <c r="I29" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6519662921348315</v>
-      </c>
-      <c r="J29" s="24"/>
+      <c r="G29" s="8">
+        <f t="shared" si="0"/>
+        <v>19.175000000000001</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="1"/>
+        <v>15.612</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="2"/>
+        <v>1.7954119850187267</v>
+      </c>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>270.48</v>
+        <v>278.49</v>
       </c>
       <c r="C30" s="13">
-        <v>6729</v>
+        <v>7339</v>
       </c>
       <c r="D30" s="14">
-        <v>17643</v>
+        <v>19169</v>
       </c>
       <c r="E30" s="14">
-        <v>15587</v>
+        <v>17111</v>
       </c>
       <c r="F30" s="14">
-        <v>11611</v>
+        <v>9892</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>17.643000000000001</v>
+        <v>19.169</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>15.587</v>
+        <v>17.111000000000001</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.5195073637068297</v>
+        <v>1.9378285483218762</v>
       </c>
       <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="19">
-        <v>302.68</v>
-      </c>
-      <c r="C31" s="20">
-        <v>6953</v>
-      </c>
-      <c r="D31" s="21">
-        <v>17255</v>
-      </c>
-      <c r="E31" s="21">
-        <v>14983</v>
-      </c>
-      <c r="F31" s="21">
-        <v>6693</v>
-      </c>
-      <c r="G31" s="22">
-        <f t="shared" si="0"/>
-        <v>17.254999999999999</v>
-      </c>
-      <c r="H31" s="22">
-        <f t="shared" si="1"/>
-        <v>14.983000000000001</v>
-      </c>
-      <c r="I31" s="23">
-        <f t="shared" si="2"/>
-        <v>2.5780666367847003</v>
-      </c>
-      <c r="J31" s="24"/>
+      <c r="B31" s="5">
+        <v>43.67</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3710</v>
+      </c>
+      <c r="D31" s="7">
+        <v>18697</v>
+      </c>
+      <c r="E31" s="7">
+        <v>17244</v>
+      </c>
+      <c r="F31" s="7">
+        <v>14089</v>
+      </c>
+      <c r="G31" s="8">
+        <f t="shared" si="0"/>
+        <v>18.696999999999999</v>
+      </c>
+      <c r="H31" s="8">
+        <f t="shared" si="1"/>
+        <v>17.244</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="2"/>
+        <v>1.3270636666903257</v>
+      </c>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>58.7</v>
+        <v>299.8</v>
       </c>
       <c r="C32" s="13">
-        <v>4507</v>
+        <v>7001</v>
       </c>
       <c r="D32" s="14">
-        <v>16968</v>
+        <v>18632</v>
       </c>
       <c r="E32" s="14">
-        <v>15008</v>
+        <v>15094</v>
       </c>
       <c r="F32" s="14">
-        <v>11674</v>
+        <v>8178</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>16.968</v>
+        <v>18.632000000000001</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>15.007999999999999</v>
+        <v>15.093999999999999</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.4534863799897209</v>
+        <v>2.2783076546832968</v>
       </c>
       <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="19">
-        <v>131.93</v>
-      </c>
-      <c r="C33" s="20">
-        <v>5328</v>
-      </c>
-      <c r="D33" s="21">
-        <v>16610</v>
-      </c>
-      <c r="E33" s="21">
-        <v>14351</v>
-      </c>
-      <c r="F33" s="21">
-        <v>11332</v>
-      </c>
-      <c r="G33" s="22">
-        <f t="shared" si="0"/>
-        <v>16.61</v>
-      </c>
-      <c r="H33" s="22">
-        <f t="shared" si="1"/>
-        <v>14.351000000000001</v>
-      </c>
-      <c r="I33" s="23">
-        <f t="shared" si="2"/>
-        <v>1.4657606777267913</v>
-      </c>
-      <c r="J33" s="24"/>
+      <c r="B33" s="5">
+        <v>300.31</v>
+      </c>
+      <c r="C33" s="6">
+        <v>7000</v>
+      </c>
+      <c r="D33" s="7">
+        <v>18611</v>
+      </c>
+      <c r="E33" s="7">
+        <v>15121</v>
+      </c>
+      <c r="F33" s="7">
+        <v>9125</v>
+      </c>
+      <c r="G33" s="8">
+        <f t="shared" si="0"/>
+        <v>18.611000000000001</v>
+      </c>
+      <c r="H33" s="8">
+        <f t="shared" si="1"/>
+        <v>15.121</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="2"/>
+        <v>2.0395616438356163</v>
+      </c>
+      <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>300.31</v>
+        <v>196.28</v>
       </c>
       <c r="C34" s="13">
-        <v>7000</v>
+        <v>6359</v>
       </c>
       <c r="D34" s="14">
-        <v>15638</v>
+        <v>18611</v>
       </c>
       <c r="E34" s="14">
-        <v>13577</v>
+        <v>15365</v>
       </c>
       <c r="F34" s="14">
-        <v>9125</v>
+        <v>10196</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>15.638</v>
+        <v>18.611000000000001</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>13.577</v>
+        <v>15.365</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.7137534246575343</v>
+        <v>1.8253236563358179</v>
       </c>
       <c r="J34" s="17"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="19">
-        <v>196.28</v>
-      </c>
-      <c r="C35" s="20">
-        <v>6359</v>
-      </c>
-      <c r="D35" s="21">
-        <v>15638</v>
-      </c>
-      <c r="E35" s="21">
-        <v>13577</v>
-      </c>
-      <c r="F35" s="21">
-        <v>10196</v>
-      </c>
-      <c r="G35" s="22">
-        <f t="shared" si="0"/>
-        <v>15.638</v>
-      </c>
-      <c r="H35" s="22">
-        <f t="shared" si="1"/>
-        <v>13.577</v>
-      </c>
-      <c r="I35" s="23">
-        <f t="shared" si="2"/>
-        <v>1.5337387210670852</v>
-      </c>
-      <c r="J35" s="24"/>
+      <c r="B35" s="5">
+        <v>58.7</v>
+      </c>
+      <c r="C35" s="6">
+        <v>4507</v>
+      </c>
+      <c r="D35" s="7">
+        <v>16994</v>
+      </c>
+      <c r="E35" s="7">
+        <v>15034</v>
+      </c>
+      <c r="F35" s="7">
+        <v>11674</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="0"/>
+        <v>16.994</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="1"/>
+        <v>15.034000000000001</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" si="2"/>
+        <v>1.4557135514819257</v>
+      </c>
+      <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>60.51</v>
+        <v>302.68</v>
       </c>
       <c r="C36" s="13">
-        <v>3703</v>
+        <v>6953</v>
       </c>
       <c r="D36" s="14">
-        <v>15600</v>
+        <v>16726</v>
       </c>
       <c r="E36" s="14">
-        <v>13480</v>
+        <v>15008</v>
       </c>
       <c r="F36" s="14">
-        <v>6700</v>
+        <v>6693</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>16.725999999999999</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>13.48</v>
+        <v>15.007999999999999</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>2.3283582089552239</v>
+        <v>2.4990288360974153</v>
       </c>
       <c r="J36" s="17"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="19">
-        <v>58.94</v>
-      </c>
-      <c r="C37" s="20">
-        <v>3772</v>
-      </c>
-      <c r="D37" s="21">
-        <v>15058</v>
-      </c>
-      <c r="E37" s="21">
-        <v>13501</v>
-      </c>
-      <c r="F37" s="21">
-        <v>10512</v>
-      </c>
-      <c r="G37" s="22">
-        <f t="shared" si="0"/>
-        <v>15.058</v>
-      </c>
-      <c r="H37" s="22">
-        <f t="shared" si="1"/>
-        <v>13.500999999999999</v>
-      </c>
-      <c r="I37" s="23">
-        <f t="shared" si="2"/>
-        <v>1.4324581430745815</v>
-      </c>
-      <c r="J37" s="24"/>
+      <c r="B37" s="5">
+        <v>131.93</v>
+      </c>
+      <c r="C37" s="6">
+        <v>5328</v>
+      </c>
+      <c r="D37" s="7">
+        <v>16636</v>
+      </c>
+      <c r="E37" s="7">
+        <v>14377</v>
+      </c>
+      <c r="F37" s="7">
+        <v>11332</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" ref="G37:G55" si="3">D37/1000</f>
+        <v>16.635999999999999</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" ref="H37:H55" si="4">E37/1000</f>
+        <v>14.377000000000001</v>
+      </c>
+      <c r="I37" s="9">
+        <f t="shared" ref="I37:I55" si="5">IFERROR(D37/F37,"")</f>
+        <v>1.4680550653018003</v>
+      </c>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>60.19</v>
+        <v>140.68</v>
       </c>
       <c r="C38" s="13">
-        <v>3809</v>
+        <v>4965</v>
       </c>
       <c r="D38" s="14">
-        <v>15058</v>
+        <v>16571</v>
       </c>
       <c r="E38" s="14">
-        <v>13501</v>
+        <v>13918</v>
       </c>
       <c r="F38" s="14">
-        <v>10313</v>
+        <v>10711</v>
       </c>
       <c r="G38" s="15">
-        <f t="shared" si="0"/>
-        <v>15.058</v>
+        <f t="shared" si="3"/>
+        <v>16.571000000000002</v>
       </c>
       <c r="H38" s="15">
-        <f t="shared" si="1"/>
-        <v>13.500999999999999</v>
+        <f t="shared" si="4"/>
+        <v>13.917999999999999</v>
       </c>
       <c r="I38" s="16">
-        <f t="shared" si="2"/>
-        <v>1.4600989042955492</v>
+        <f t="shared" si="5"/>
+        <v>1.5471011110073756</v>
       </c>
       <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="5">
         <v>65</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="6">
         <v>3845</v>
       </c>
-      <c r="D39" s="21">
-        <v>15040</v>
-      </c>
-      <c r="E39" s="21">
-        <v>13509</v>
-      </c>
-      <c r="F39" s="21">
+      <c r="D39" s="7">
+        <v>15522</v>
+      </c>
+      <c r="E39" s="7">
+        <v>13534</v>
+      </c>
+      <c r="F39" s="7">
         <v>6902</v>
       </c>
-      <c r="G39" s="22">
-        <f t="shared" si="0"/>
-        <v>15.04</v>
-      </c>
-      <c r="H39" s="22">
-        <f t="shared" si="1"/>
-        <v>13.509</v>
-      </c>
-      <c r="I39" s="23">
-        <f t="shared" si="2"/>
-        <v>2.1790785279629095</v>
-      </c>
-      <c r="J39" s="24"/>
+      <c r="G39" s="8">
+        <f t="shared" si="3"/>
+        <v>15.522</v>
+      </c>
+      <c r="H39" s="8">
+        <f t="shared" si="4"/>
+        <v>13.534000000000001</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="5"/>
+        <v>2.2489133584468268</v>
+      </c>
+      <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>124</v>
+        <v>174.68</v>
       </c>
       <c r="C40" s="13">
-        <v>4814</v>
+        <v>5276</v>
       </c>
       <c r="D40" s="14">
-        <v>14377</v>
+        <v>15420</v>
       </c>
       <c r="E40" s="14">
-        <v>12747</v>
+        <v>13918</v>
       </c>
       <c r="F40" s="14">
-        <v>9977</v>
+        <v>9459</v>
       </c>
       <c r="G40" s="15">
-        <f t="shared" si="0"/>
-        <v>14.377000000000001</v>
+        <f t="shared" si="3"/>
+        <v>15.42</v>
       </c>
       <c r="H40" s="15">
-        <f t="shared" si="1"/>
-        <v>12.747</v>
+        <f t="shared" si="4"/>
+        <v>13.917999999999999</v>
       </c>
       <c r="I40" s="16">
-        <f t="shared" si="2"/>
-        <v>1.4410143329658214</v>
+        <f t="shared" si="5"/>
+        <v>1.6301934665398035</v>
       </c>
       <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="19">
-        <v>177.61</v>
-      </c>
-      <c r="C41" s="20">
-        <v>5367</v>
-      </c>
-      <c r="D41" s="21">
-        <v>13635</v>
-      </c>
-      <c r="E41" s="21">
-        <v>12419</v>
-      </c>
-      <c r="F41" s="21">
-        <v>8285</v>
-      </c>
-      <c r="G41" s="22">
-        <f t="shared" si="0"/>
-        <v>13.635</v>
-      </c>
-      <c r="H41" s="22">
-        <f t="shared" si="1"/>
-        <v>12.419</v>
-      </c>
-      <c r="I41" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6457453228726615</v>
-      </c>
-      <c r="J41" s="24"/>
+      <c r="B41" s="5">
+        <v>60.51</v>
+      </c>
+      <c r="C41" s="6">
+        <v>3703</v>
+      </c>
+      <c r="D41" s="7">
+        <v>15324</v>
+      </c>
+      <c r="E41" s="7">
+        <v>13506</v>
+      </c>
+      <c r="F41" s="7">
+        <v>6700</v>
+      </c>
+      <c r="G41" s="8">
+        <f t="shared" si="3"/>
+        <v>15.324</v>
+      </c>
+      <c r="H41" s="8">
+        <f t="shared" si="4"/>
+        <v>13.506</v>
+      </c>
+      <c r="I41" s="9">
+        <f t="shared" si="5"/>
+        <v>2.2871641791044777</v>
+      </c>
+      <c r="J41" s="10"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="12">
-        <v>80.13</v>
+        <v>58.94</v>
       </c>
       <c r="C42" s="13">
-        <v>4466</v>
+        <v>3772</v>
       </c>
       <c r="D42" s="14">
-        <v>13533</v>
+        <v>15084</v>
       </c>
       <c r="E42" s="14">
-        <v>11084</v>
+        <v>13526</v>
       </c>
       <c r="F42" s="14">
-        <v>7792</v>
+        <v>10512</v>
       </c>
       <c r="G42" s="15">
-        <f t="shared" si="0"/>
-        <v>13.532999999999999</v>
+        <f t="shared" si="3"/>
+        <v>15.084</v>
       </c>
       <c r="H42" s="15">
-        <f t="shared" si="1"/>
-        <v>11.084</v>
+        <f t="shared" si="4"/>
+        <v>13.526</v>
       </c>
       <c r="I42" s="16">
-        <f t="shared" si="2"/>
-        <v>1.7367813141683779</v>
+        <f t="shared" si="5"/>
+        <v>1.4349315068493151</v>
       </c>
       <c r="J42" s="17"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="19">
-        <v>60.87</v>
-      </c>
-      <c r="C43" s="20">
-        <v>3801</v>
-      </c>
-      <c r="D43" s="21">
-        <v>13533</v>
-      </c>
-      <c r="E43" s="21">
-        <v>11987</v>
-      </c>
-      <c r="F43" s="21">
-        <v>8017</v>
-      </c>
-      <c r="G43" s="22">
-        <f t="shared" si="0"/>
-        <v>13.532999999999999</v>
-      </c>
-      <c r="H43" s="22">
-        <f t="shared" si="1"/>
-        <v>11.987</v>
-      </c>
-      <c r="I43" s="23">
-        <f t="shared" si="2"/>
-        <v>1.6880379194212298</v>
-      </c>
-      <c r="J43" s="24"/>
+      <c r="B43" s="5">
+        <v>60.19</v>
+      </c>
+      <c r="C43" s="6">
+        <v>3809</v>
+      </c>
+      <c r="D43" s="7">
+        <v>15084</v>
+      </c>
+      <c r="E43" s="7">
+        <v>13526</v>
+      </c>
+      <c r="F43" s="7">
+        <v>10313</v>
+      </c>
+      <c r="G43" s="8">
+        <f t="shared" si="3"/>
+        <v>15.084</v>
+      </c>
+      <c r="H43" s="8">
+        <f t="shared" si="4"/>
+        <v>13.526</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="5"/>
+        <v>1.4626199941821003</v>
+      </c>
+      <c r="J43" s="10"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>51</v>
       </c>
       <c r="B44" s="12">
+        <v>124</v>
+      </c>
+      <c r="C44" s="13">
+        <v>4814</v>
+      </c>
+      <c r="D44" s="14">
+        <v>14403</v>
+      </c>
+      <c r="E44" s="14">
+        <v>12773</v>
+      </c>
+      <c r="F44" s="14">
+        <v>9977</v>
+      </c>
+      <c r="G44" s="15">
+        <f t="shared" si="3"/>
+        <v>14.403</v>
+      </c>
+      <c r="H44" s="15">
+        <f t="shared" si="4"/>
+        <v>12.773</v>
+      </c>
+      <c r="I44" s="16">
+        <f t="shared" si="5"/>
+        <v>1.4436203267515286</v>
+      </c>
+      <c r="J44" s="17"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="5">
         <v>59.79</v>
       </c>
-      <c r="C44" s="13">
+      <c r="C45" s="6">
         <v>3770</v>
       </c>
-      <c r="D44" s="14">
-        <v>13519</v>
-      </c>
-      <c r="E44" s="14">
-        <v>11590</v>
-      </c>
-      <c r="F44" s="14">
+      <c r="D45" s="7">
+        <v>13975</v>
+      </c>
+      <c r="E45" s="7">
+        <v>11615</v>
+      </c>
+      <c r="F45" s="7">
         <v>9014</v>
       </c>
-      <c r="G44" s="15">
-        <f t="shared" si="0"/>
-        <v>13.519</v>
-      </c>
-      <c r="H44" s="15">
-        <f t="shared" si="1"/>
-        <v>11.59</v>
-      </c>
-      <c r="I44" s="16">
-        <f t="shared" si="2"/>
-        <v>1.4997781229199023</v>
-      </c>
-      <c r="J44" s="17"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="19">
-        <v>59.61</v>
-      </c>
-      <c r="C45" s="20">
-        <v>3784</v>
-      </c>
-      <c r="D45" s="21">
-        <v>13519</v>
-      </c>
-      <c r="E45" s="21">
-        <v>11987</v>
-      </c>
-      <c r="F45" s="21">
-        <v>9228</v>
-      </c>
-      <c r="G45" s="22">
-        <f t="shared" si="0"/>
-        <v>13.519</v>
-      </c>
-      <c r="H45" s="22">
-        <f t="shared" si="1"/>
-        <v>11.987</v>
-      </c>
-      <c r="I45" s="23">
-        <f t="shared" si="2"/>
-        <v>1.4649978326831383</v>
-      </c>
-      <c r="J45" s="24"/>
+      <c r="G45" s="8">
+        <f t="shared" si="3"/>
+        <v>13.975</v>
+      </c>
+      <c r="H45" s="8">
+        <f t="shared" si="4"/>
+        <v>11.615</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="5"/>
+        <v>1.5503660971821611</v>
+      </c>
+      <c r="J45" s="10"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>113.78</v>
+        <v>59.61</v>
       </c>
       <c r="C46" s="13">
-        <v>4554</v>
+        <v>3784</v>
       </c>
       <c r="D46" s="14">
-        <v>11642</v>
+        <v>13972</v>
       </c>
       <c r="E46" s="14">
-        <v>11084</v>
+        <v>12013</v>
       </c>
       <c r="F46" s="14">
-        <v>8753</v>
+        <v>9228</v>
       </c>
       <c r="G46" s="15">
-        <f t="shared" si="0"/>
-        <v>11.641999999999999</v>
+        <f t="shared" si="3"/>
+        <v>13.972</v>
       </c>
       <c r="H46" s="15">
-        <f t="shared" si="1"/>
-        <v>11.084</v>
+        <f t="shared" si="4"/>
+        <v>12.013</v>
       </c>
       <c r="I46" s="16">
-        <f t="shared" si="2"/>
-        <v>1.3300582657374613</v>
+        <f t="shared" si="5"/>
+        <v>1.5140875596012138</v>
       </c>
       <c r="J46" s="17"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="19">
-        <v>18.11</v>
-      </c>
-      <c r="C47" s="20">
-        <v>1911</v>
-      </c>
-      <c r="D47" s="21">
-        <v>11529</v>
-      </c>
-      <c r="E47" s="21">
-        <v>10849</v>
-      </c>
-      <c r="F47" s="21">
-        <v>8310</v>
-      </c>
-      <c r="G47" s="22">
-        <f t="shared" si="0"/>
-        <v>11.529</v>
-      </c>
-      <c r="H47" s="22">
-        <f t="shared" si="1"/>
-        <v>10.849</v>
-      </c>
-      <c r="I47" s="23">
-        <f t="shared" si="2"/>
-        <v>1.3873646209386281</v>
-      </c>
-      <c r="J47" s="24"/>
+      <c r="B47" s="5">
+        <v>60.87</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3801</v>
+      </c>
+      <c r="D47" s="7">
+        <v>13967</v>
+      </c>
+      <c r="E47" s="7">
+        <v>12013</v>
+      </c>
+      <c r="F47" s="7">
+        <v>8017</v>
+      </c>
+      <c r="G47" s="8">
+        <f t="shared" si="3"/>
+        <v>13.967000000000001</v>
+      </c>
+      <c r="H47" s="8">
+        <f t="shared" si="4"/>
+        <v>12.013</v>
+      </c>
+      <c r="I47" s="9">
+        <f t="shared" si="5"/>
+        <v>1.7421728826244232</v>
+      </c>
+      <c r="J47" s="10"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="12">
-        <v>70.98</v>
+        <v>80.13</v>
       </c>
       <c r="C48" s="13">
-        <v>3651</v>
+        <v>4466</v>
       </c>
       <c r="D48" s="14">
-        <v>11426</v>
+        <v>13565</v>
       </c>
       <c r="E48" s="14">
-        <v>9691</v>
+        <v>11110</v>
       </c>
       <c r="F48" s="14">
-        <v>7484</v>
+        <v>7792</v>
       </c>
       <c r="G48" s="15">
-        <f t="shared" si="0"/>
-        <v>11.426</v>
+        <f t="shared" si="3"/>
+        <v>13.565</v>
       </c>
       <c r="H48" s="15">
-        <f t="shared" si="1"/>
-        <v>9.6910000000000007</v>
+        <f t="shared" si="4"/>
+        <v>11.11</v>
       </c>
       <c r="I48" s="16">
-        <f t="shared" si="2"/>
-        <v>1.5267236771779797</v>
+        <f t="shared" si="5"/>
+        <v>1.740888090349076</v>
       </c>
       <c r="J48" s="17"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="19">
-        <v>19.78</v>
-      </c>
-      <c r="C49" s="20">
-        <v>2018</v>
-      </c>
-      <c r="D49" s="21">
-        <v>10419</v>
-      </c>
-      <c r="E49" s="21">
-        <v>9645</v>
-      </c>
-      <c r="F49" s="21">
-        <v>8848</v>
-      </c>
-      <c r="G49" s="22">
-        <f t="shared" si="0"/>
-        <v>10.419</v>
-      </c>
-      <c r="H49" s="22">
-        <f t="shared" si="1"/>
-        <v>9.6449999999999996</v>
-      </c>
-      <c r="I49" s="23">
-        <f t="shared" si="2"/>
-        <v>1.1775542495479205</v>
-      </c>
-      <c r="J49" s="24"/>
+      <c r="B49" s="5">
+        <v>113.78</v>
+      </c>
+      <c r="C49" s="6">
+        <v>4554</v>
+      </c>
+      <c r="D49" s="7">
+        <v>13152</v>
+      </c>
+      <c r="E49" s="7">
+        <v>11110</v>
+      </c>
+      <c r="F49" s="7">
+        <v>8753</v>
+      </c>
+      <c r="G49" s="8">
+        <f t="shared" si="3"/>
+        <v>13.151999999999999</v>
+      </c>
+      <c r="H49" s="8">
+        <f t="shared" si="4"/>
+        <v>11.11</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="5"/>
+        <v>1.5025705472409459</v>
+      </c>
+      <c r="J49" s="10"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B50" s="12">
-        <v>88.51</v>
+        <v>18.11</v>
       </c>
       <c r="C50" s="13">
-        <v>3848</v>
+        <v>1911</v>
       </c>
       <c r="D50" s="14">
-        <v>9767</v>
+        <v>11562</v>
       </c>
       <c r="E50" s="14">
-        <v>8662</v>
+        <v>10874</v>
       </c>
       <c r="F50" s="14">
-        <v>6820</v>
+        <v>8310</v>
       </c>
       <c r="G50" s="15">
-        <f t="shared" si="0"/>
-        <v>9.7669999999999995</v>
+        <f t="shared" si="3"/>
+        <v>11.561999999999999</v>
       </c>
       <c r="H50" s="15">
-        <f t="shared" si="1"/>
-        <v>8.6620000000000008</v>
+        <f t="shared" si="4"/>
+        <v>10.874000000000001</v>
       </c>
       <c r="I50" s="16">
-        <f t="shared" si="2"/>
-        <v>1.4321114369501466</v>
+        <f t="shared" si="5"/>
+        <v>1.3913357400722022</v>
       </c>
       <c r="J50" s="17"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="19">
-        <v>75.31</v>
-      </c>
-      <c r="C51" s="20">
-        <v>3891</v>
-      </c>
-      <c r="D51" s="21">
-        <v>9113</v>
-      </c>
-      <c r="E51" s="21">
-        <v>7408</v>
-      </c>
-      <c r="F51" s="21">
-        <v>6142</v>
-      </c>
-      <c r="G51" s="22">
-        <f t="shared" si="0"/>
-        <v>9.1129999999999995</v>
-      </c>
-      <c r="H51" s="22">
-        <f t="shared" si="1"/>
-        <v>7.4080000000000004</v>
-      </c>
-      <c r="I51" s="23">
-        <f t="shared" si="2"/>
-        <v>1.4837186584174535</v>
-      </c>
-      <c r="J51" s="24"/>
+      <c r="B51" s="5">
+        <v>70.98</v>
+      </c>
+      <c r="C51" s="6">
+        <v>3651</v>
+      </c>
+      <c r="D51" s="7">
+        <v>11452</v>
+      </c>
+      <c r="E51" s="7">
+        <v>9716</v>
+      </c>
+      <c r="F51" s="7">
+        <v>7484</v>
+      </c>
+      <c r="G51" s="8">
+        <f t="shared" si="3"/>
+        <v>11.452</v>
+      </c>
+      <c r="H51" s="8">
+        <f t="shared" si="4"/>
+        <v>9.7159999999999993</v>
+      </c>
+      <c r="I51" s="9">
+        <f t="shared" si="5"/>
+        <v>1.530197755211117</v>
+      </c>
+      <c r="J51" s="10"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="5">
-        <v>149.61000000000001</v>
-      </c>
-      <c r="C52" s="6">
-        <v>5003</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" s="7">
-        <v>15887</v>
-      </c>
-      <c r="G52" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H52" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I52" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="J52" s="28" t="s">
-        <v>62</v>
-      </c>
+      <c r="B52" s="12">
+        <v>177.61</v>
+      </c>
+      <c r="C52" s="13">
+        <v>5367</v>
+      </c>
+      <c r="D52" s="14">
+        <v>11155</v>
+      </c>
+      <c r="E52" s="14">
+        <v>9602</v>
+      </c>
+      <c r="F52" s="14">
+        <v>8285</v>
+      </c>
+      <c r="G52" s="15">
+        <f t="shared" si="3"/>
+        <v>11.154999999999999</v>
+      </c>
+      <c r="H52" s="15">
+        <f t="shared" si="4"/>
+        <v>9.6020000000000003</v>
+      </c>
+      <c r="I52" s="16">
+        <f t="shared" si="5"/>
+        <v>1.3464091732045866</v>
+      </c>
+      <c r="J52" s="17"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5">
-        <v>131.51</v>
+        <v>19.78</v>
       </c>
       <c r="C53" s="6">
-        <v>4710</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>60</v>
+        <v>2018</v>
+      </c>
+      <c r="D53" s="7">
+        <v>10444</v>
+      </c>
+      <c r="E53" s="7">
+        <v>9670</v>
       </c>
       <c r="F53" s="7">
-        <v>14642</v>
-      </c>
-      <c r="G53" s="26" t="s">
+        <v>8848</v>
+      </c>
+      <c r="G53" s="8">
+        <f t="shared" si="3"/>
+        <v>10.444000000000001</v>
+      </c>
+      <c r="H53" s="8">
+        <f t="shared" si="4"/>
+        <v>9.67</v>
+      </c>
+      <c r="I53" s="9">
+        <f t="shared" si="5"/>
+        <v>1.1803797468354431</v>
+      </c>
+      <c r="J53" s="10"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H53" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I53" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="J53" s="28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="5">
-        <v>67.459999999999994</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3607</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="7">
-        <v>16250</v>
-      </c>
-      <c r="G54" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H54" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I54" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="J54" s="28" t="s">
-        <v>62</v>
-      </c>
+      <c r="B54" s="12">
+        <v>88.51</v>
+      </c>
+      <c r="C54" s="13">
+        <v>3848</v>
+      </c>
+      <c r="D54" s="14">
+        <v>9792</v>
+      </c>
+      <c r="E54" s="14">
+        <v>8688</v>
+      </c>
+      <c r="F54" s="14">
+        <v>6820</v>
+      </c>
+      <c r="G54" s="15">
+        <f t="shared" si="3"/>
+        <v>9.7919999999999998</v>
+      </c>
+      <c r="H54" s="15">
+        <f t="shared" si="4"/>
+        <v>8.6880000000000006</v>
+      </c>
+      <c r="I54" s="16">
+        <f t="shared" si="5"/>
+        <v>1.4357771260997068</v>
+      </c>
+      <c r="J54" s="17"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5">
-        <v>140.69</v>
+        <v>75.31</v>
       </c>
       <c r="C55" s="6">
-        <v>4981</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>60</v>
+        <v>3891</v>
+      </c>
+      <c r="D55" s="7">
+        <v>9138</v>
+      </c>
+      <c r="E55" s="7">
+        <v>7433</v>
       </c>
       <c r="F55" s="7">
-        <v>14856</v>
-      </c>
-      <c r="G55" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I55" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="J55" s="28" t="s">
-        <v>62</v>
-      </c>
+        <v>6142</v>
+      </c>
+      <c r="G55" s="8">
+        <f t="shared" si="3"/>
+        <v>9.1379999999999999</v>
+      </c>
+      <c r="H55" s="8">
+        <f t="shared" si="4"/>
+        <v>7.4329999999999998</v>
+      </c>
+      <c r="I55" s="9">
+        <f t="shared" si="5"/>
+        <v>1.4877889938130902</v>
+      </c>
+      <c r="J55" s="10"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="30">
+      <c r="A57" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="19">
         <f>SUM(B5:B55)</f>
-        <v>6880.8099999999986</v>
-      </c>
-      <c r="D57" s="31">
+        <v>6880.8099999999995</v>
+      </c>
+      <c r="D57" s="20">
         <f>MAX(D5:D55)</f>
-        <v>39828</v>
-      </c>
-      <c r="G57" s="32">
+        <v>24868</v>
+      </c>
+      <c r="G57" s="21">
         <f>IFERROR(MAX(G5:G55),"")</f>
-        <v>39.828000000000003</v>
-      </c>
-      <c r="I57" s="33">
+        <v>24.867999999999999</v>
+      </c>
+      <c r="I57" s="22">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
-        <v>1.762438528300619</v>
+        <v>1.6175094667508989</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="34" t="s">
-        <v>67</v>
+      <c r="A58" s="23" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2548,88 +2512,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="B4" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="37" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="B5" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="37" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="B6" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="37" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+      <c r="B7" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="37" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="B8" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="37" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="25" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="B9" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="37" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="B10" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="37" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
+      <c r="B11" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="37" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="B12" s="26" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE5BDF6-9E8B-4B77-A010-E6BFD4C9FA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46328587-EBE7-493B-B4AD-21A0C27C47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,151 +72,151 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-05A</t>
+  </si>
+  <si>
+    <t>T-05S</t>
+  </si>
+  <si>
     <t>T-17</t>
   </si>
   <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-05S</t>
+    <t>T-16B</t>
   </si>
   <si>
     <t>T37</t>
   </si>
   <si>
+    <t>T-04</t>
+  </si>
+  <si>
     <t>T33</t>
   </si>
   <si>
     <t>T34</t>
   </si>
   <si>
-    <t>T-16B</t>
+    <t>T-06A</t>
   </si>
   <si>
     <t>T38</t>
   </si>
   <si>
-    <t>T-04</t>
+    <t>T-06B</t>
   </si>
   <si>
     <t>T-24</t>
   </si>
   <si>
-    <t>T-06A</t>
-  </si>
-  <si>
-    <t>T-06B</t>
+    <t>T-07B</t>
+  </si>
+  <si>
+    <t>T-16A</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
+    <t>T-07A</t>
+  </si>
+  <si>
+    <t>T-19</t>
   </si>
   <si>
     <t>T31</t>
   </si>
   <si>
-    <t>T-15C</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>T-16A</t>
-  </si>
-  <si>
-    <t>T-07A</t>
-  </si>
-  <si>
     <t>T-18</t>
   </si>
   <si>
+    <t>T-23</t>
+  </si>
+  <si>
     <t>T-15A</t>
   </si>
   <si>
-    <t>T-23</t>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-15B</t>
+  </si>
+  <si>
+    <t>T-08</t>
   </si>
   <si>
     <t>T-14</t>
   </si>
   <si>
-    <t>T-15B</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-03</t>
+    <t>T-02</t>
   </si>
   <si>
     <t>T30</t>
   </si>
   <si>
-    <t>T-02</t>
-  </si>
-  <si>
     <t>T-09</t>
   </si>
   <si>
+    <t>T-22</t>
+  </si>
+  <si>
     <t>T-13</t>
   </si>
   <si>
-    <t>T-22</t>
-  </si>
-  <si>
     <t>T-01C</t>
   </si>
   <si>
+    <t>T-20</t>
+  </si>
+  <si>
     <t>T-22A</t>
   </si>
   <si>
-    <t>T-20</t>
-  </si>
-  <si>
     <t>T-01B</t>
   </si>
   <si>
+    <t>T-01A</t>
+  </si>
+  <si>
+    <t>T-10B</t>
+  </si>
+  <si>
     <t>T-12</t>
   </si>
   <si>
-    <t>T-01A</t>
-  </si>
-  <si>
     <t>T-20S</t>
   </si>
   <si>
     <t>T-21</t>
   </si>
   <si>
+    <t>T-12S</t>
+  </si>
+  <si>
+    <t>T-10S</t>
+  </si>
+  <si>
+    <t>T-11A</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
+    <t>T-10A</t>
+  </si>
+  <si>
     <t>T-21A</t>
   </si>
   <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-12S</t>
-  </si>
-  <si>
-    <t>T-10S</t>
-  </si>
-  <si>
-    <t>T-10A</t>
-  </si>
-  <si>
-    <t>T-11A</t>
+    <t>T-27</t>
+  </si>
+  <si>
+    <t>T-25</t>
   </si>
   <si>
     <t>T-26</t>
-  </si>
-  <si>
-    <t>T-27</t>
-  </si>
-  <si>
-    <t>T-10B</t>
-  </si>
-  <si>
-    <t>T-25</t>
   </si>
   <si>
     <t>T-28</t>
@@ -793,31 +793,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>140.75</v>
+        <v>124.34</v>
       </c>
       <c r="C5" s="6">
-        <v>5173</v>
+        <v>4758</v>
       </c>
       <c r="D5" s="7">
-        <v>24868</v>
+        <v>24759</v>
       </c>
       <c r="E5" s="7">
-        <v>23146</v>
+        <v>24137</v>
       </c>
       <c r="F5" s="7">
-        <v>15747</v>
+        <v>15004</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G36" si="0">D5/1000</f>
-        <v>24.867999999999999</v>
+        <v>24.759</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H36" si="1">E5/1000</f>
-        <v>23.146000000000001</v>
+        <v>24.137</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
-        <v>1.5792214390042547</v>
+        <v>1.6501599573447081</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -826,31 +826,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>124.34</v>
+        <v>175.27</v>
       </c>
       <c r="C6" s="13">
-        <v>4758</v>
+        <v>5486</v>
       </c>
       <c r="D6" s="14">
-        <v>24768</v>
+        <v>24215</v>
       </c>
       <c r="E6" s="14">
-        <v>24146</v>
+        <v>21167</v>
       </c>
       <c r="F6" s="14">
-        <v>15004</v>
+        <v>13634</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>24.768000000000001</v>
+        <v>24.215</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>24.146000000000001</v>
+        <v>21.167000000000002</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.6507597973873633</v>
+        <v>1.7760745195833945</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -859,31 +859,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>175.27</v>
+        <v>71.5</v>
       </c>
       <c r="C7" s="6">
-        <v>5486</v>
+        <v>4054</v>
       </c>
       <c r="D7" s="7">
-        <v>24224</v>
+        <v>24190</v>
       </c>
       <c r="E7" s="7">
-        <v>21178</v>
+        <v>23428</v>
       </c>
       <c r="F7" s="7">
-        <v>13634</v>
+        <v>14361</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>24.224</v>
+        <v>24.19</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>21.178000000000001</v>
+        <v>23.428000000000001</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.7767346340032273</v>
+        <v>1.6844230903140449</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -892,31 +892,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>71.5</v>
+        <v>140.75</v>
       </c>
       <c r="C8" s="13">
-        <v>4054</v>
+        <v>5173</v>
       </c>
       <c r="D8" s="14">
-        <v>24199</v>
+        <v>23868</v>
       </c>
       <c r="E8" s="14">
-        <v>23437</v>
+        <v>20924</v>
       </c>
       <c r="F8" s="14">
-        <v>14361</v>
+        <v>15747</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>24.199000000000002</v>
+        <v>23.867999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>23.437000000000001</v>
+        <v>20.923999999999999</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.6850497876192465</v>
+        <v>1.5157172794818061</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -925,31 +925,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>67.459999999999994</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="C9" s="6">
-        <v>3607</v>
+        <v>3913</v>
       </c>
       <c r="D9" s="7">
-        <v>24081</v>
+        <v>23204</v>
       </c>
       <c r="E9" s="7">
-        <v>22035</v>
+        <v>21068</v>
       </c>
       <c r="F9" s="7">
-        <v>16250</v>
+        <v>16110</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>24.081</v>
+        <v>23.204000000000001</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>22.035</v>
+        <v>21.068000000000001</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.4819076923076924</v>
+        <v>1.4403476101800123</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -958,31 +958,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>149.61000000000001</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="C10" s="13">
-        <v>5003</v>
+        <v>3607</v>
       </c>
       <c r="D10" s="14">
-        <v>23804</v>
+        <v>22978</v>
       </c>
       <c r="E10" s="14">
-        <v>21223</v>
+        <v>20938</v>
       </c>
       <c r="F10" s="14">
-        <v>15887</v>
+        <v>16250</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>23.803999999999998</v>
+        <v>22.978000000000002</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>21.222999999999999</v>
+        <v>20.937999999999999</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.4983319695348398</v>
+        <v>1.4140307692307692</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -991,31 +991,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>131.51</v>
+        <v>302.63</v>
       </c>
       <c r="C11" s="6">
-        <v>4710</v>
+        <v>7372</v>
       </c>
       <c r="D11" s="7">
-        <v>23271</v>
+        <v>22738</v>
       </c>
       <c r="E11" s="7">
-        <v>19919</v>
+        <v>19115</v>
       </c>
       <c r="F11" s="7">
-        <v>14642</v>
+        <v>11657</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>23.271000000000001</v>
+        <v>22.738</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>19.919</v>
+        <v>19.114999999999998</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.5893320584619588</v>
+        <v>1.9505876297503646</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1024,31 +1024,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>66.459999999999994</v>
+        <v>149.61000000000001</v>
       </c>
       <c r="C12" s="13">
-        <v>3913</v>
+        <v>5003</v>
       </c>
       <c r="D12" s="14">
-        <v>23203</v>
+        <v>22707</v>
       </c>
       <c r="E12" s="14">
-        <v>21068</v>
+        <v>20126</v>
       </c>
       <c r="F12" s="14">
-        <v>16110</v>
+        <v>15887</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>23.202999999999999</v>
+        <v>22.707000000000001</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>21.068000000000001</v>
+        <v>20.126000000000001</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.4402855369335816</v>
+        <v>1.4292818027317933</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1057,31 +1057,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>140.69</v>
+        <v>131.51</v>
       </c>
       <c r="C13" s="6">
-        <v>4981</v>
+        <v>4710</v>
       </c>
       <c r="D13" s="7">
-        <v>23140</v>
+        <v>22174</v>
       </c>
       <c r="E13" s="7">
-        <v>20628</v>
+        <v>18823</v>
       </c>
       <c r="F13" s="7">
-        <v>14856</v>
+        <v>14642</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>23.14</v>
+        <v>22.173999999999999</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>20.628</v>
+        <v>18.823</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.557619816908993</v>
+        <v>1.5144105996448574</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1090,31 +1090,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>302.63</v>
+        <v>132.93</v>
       </c>
       <c r="C14" s="13">
-        <v>7372</v>
+        <v>4758</v>
       </c>
       <c r="D14" s="14">
-        <v>22738</v>
+        <v>22075</v>
       </c>
       <c r="E14" s="14">
-        <v>19115</v>
+        <v>19695</v>
       </c>
       <c r="F14" s="14">
-        <v>11657</v>
+        <v>14217</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>22.738</v>
+        <v>22.074999999999999</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>19.114999999999998</v>
+        <v>19.695</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.9505876297503646</v>
+        <v>1.5527185763522544</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1123,31 +1123,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>83.32</v>
+        <v>140.69</v>
       </c>
       <c r="C15" s="6">
-        <v>3691</v>
+        <v>4981</v>
       </c>
       <c r="D15" s="7">
-        <v>22560</v>
+        <v>22035</v>
       </c>
       <c r="E15" s="7">
-        <v>21095</v>
+        <v>19531</v>
       </c>
       <c r="F15" s="7">
-        <v>15125</v>
+        <v>14856</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>22.56</v>
+        <v>22.035</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>21.094999999999999</v>
+        <v>19.530999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.4915702479338844</v>
+        <v>1.4832390953150243</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1156,31 +1156,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>132.93</v>
+        <v>144.9</v>
       </c>
       <c r="C16" s="13">
-        <v>4758</v>
+        <v>4944</v>
       </c>
       <c r="D16" s="14">
-        <v>22083</v>
+        <v>21636</v>
       </c>
       <c r="E16" s="14">
-        <v>19695</v>
+        <v>20656</v>
       </c>
       <c r="F16" s="14">
-        <v>14217</v>
+        <v>15014</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>22.082999999999998</v>
+        <v>21.635999999999999</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>19.695</v>
+        <v>20.655999999999999</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.5532812829710909</v>
+        <v>1.4410550153190356</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1189,31 +1189,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>144.9</v>
+        <v>83.32</v>
       </c>
       <c r="C17" s="6">
-        <v>4944</v>
+        <v>3691</v>
       </c>
       <c r="D17" s="7">
-        <v>21636</v>
+        <v>21580</v>
       </c>
       <c r="E17" s="7">
-        <v>20656</v>
+        <v>20114</v>
       </c>
       <c r="F17" s="7">
-        <v>15014</v>
+        <v>15125</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>21.635999999999999</v>
+        <v>21.58</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>20.655999999999999</v>
+        <v>20.114000000000001</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.4410550153190356</v>
+        <v>1.4267768595041321</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1222,31 +1222,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>239.17</v>
+        <v>53.96</v>
       </c>
       <c r="C18" s="13">
-        <v>6359</v>
+        <v>3674</v>
       </c>
       <c r="D18" s="14">
-        <v>21530</v>
+        <v>21197</v>
       </c>
       <c r="E18" s="14">
-        <v>18647</v>
+        <v>19335</v>
       </c>
       <c r="F18" s="14">
-        <v>15489</v>
+        <v>13875</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>21.53</v>
+        <v>21.196999999999999</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>18.646999999999998</v>
+        <v>19.335000000000001</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.3900187229646845</v>
+        <v>1.5277117117117116</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1255,31 +1255,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>136.18</v>
+        <v>56.03</v>
       </c>
       <c r="C19" s="6">
-        <v>4817</v>
+        <v>3746</v>
       </c>
       <c r="D19" s="7">
-        <v>21259</v>
+        <v>21118</v>
       </c>
       <c r="E19" s="7">
-        <v>19732</v>
+        <v>20656</v>
       </c>
       <c r="F19" s="7">
-        <v>14928</v>
+        <v>15750</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>21.259</v>
+        <v>21.117999999999999</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>19.731999999999999</v>
+        <v>20.655999999999999</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.4241023579849947</v>
+        <v>1.3408253968253969</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1288,31 +1288,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>53.96</v>
+        <v>136.18</v>
       </c>
       <c r="C20" s="13">
-        <v>3674</v>
+        <v>4817</v>
       </c>
       <c r="D20" s="14">
-        <v>21206</v>
+        <v>21088</v>
       </c>
       <c r="E20" s="14">
-        <v>19339</v>
+        <v>19732</v>
       </c>
       <c r="F20" s="14">
-        <v>13875</v>
+        <v>14928</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>21.206</v>
+        <v>21.088000000000001</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>19.338999999999999</v>
+        <v>19.731999999999999</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.5283603603603604</v>
+        <v>1.412647374062165</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1321,31 +1321,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>150.72</v>
+        <v>254.67</v>
       </c>
       <c r="C21" s="6">
-        <v>5638</v>
+        <v>6809</v>
       </c>
       <c r="D21" s="7">
-        <v>21204</v>
+        <v>20832</v>
       </c>
       <c r="E21" s="7">
-        <v>18661</v>
+        <v>17622</v>
       </c>
       <c r="F21" s="7">
-        <v>13240</v>
+        <v>12367</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>21.204000000000001</v>
+        <v>20.832000000000001</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>18.661000000000001</v>
+        <v>17.622</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.6015105740181268</v>
+        <v>1.6844828980350934</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1354,31 +1354,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>56.03</v>
+        <v>150.72</v>
       </c>
       <c r="C22" s="13">
-        <v>3746</v>
+        <v>5638</v>
       </c>
       <c r="D22" s="14">
-        <v>21117</v>
+        <v>20820</v>
       </c>
       <c r="E22" s="14">
-        <v>20656</v>
+        <v>17681</v>
       </c>
       <c r="F22" s="14">
-        <v>15750</v>
+        <v>13240</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>21.117000000000001</v>
+        <v>20.82</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>20.655999999999999</v>
+        <v>17.681000000000001</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.3407619047619048</v>
+        <v>1.5725075528700907</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1387,31 +1387,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>254.67</v>
+        <v>239.17</v>
       </c>
       <c r="C23" s="6">
-        <v>6809</v>
+        <v>6359</v>
       </c>
       <c r="D23" s="7">
-        <v>20845</v>
+        <v>20433</v>
       </c>
       <c r="E23" s="7">
-        <v>17619</v>
+        <v>17550</v>
       </c>
       <c r="F23" s="7">
-        <v>12367</v>
+        <v>15489</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>20.844999999999999</v>
+        <v>20.433</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>17.619</v>
+        <v>17.55</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.6855340826392819</v>
+        <v>1.3191942668990897</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1426,25 +1426,25 @@
         <v>4528</v>
       </c>
       <c r="D24" s="14">
-        <v>20668</v>
+        <v>20391</v>
       </c>
       <c r="E24" s="14">
-        <v>19115</v>
+        <v>18838</v>
       </c>
       <c r="F24" s="14">
         <v>14106</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>20.667999999999999</v>
+        <v>20.390999999999998</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>19.114999999999998</v>
+        <v>18.838000000000001</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.4651921168297179</v>
+        <v>1.4455550829434283</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1453,31 +1453,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>169.72</v>
+        <v>201.87</v>
       </c>
       <c r="C25" s="6">
-        <v>5278</v>
+        <v>6413</v>
       </c>
       <c r="D25" s="7">
-        <v>20224</v>
+        <v>20105</v>
       </c>
       <c r="E25" s="7">
-        <v>17619</v>
+        <v>16490</v>
       </c>
       <c r="F25" s="7">
-        <v>13180</v>
+        <v>11986</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>20.224</v>
+        <v>20.105</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>17.619</v>
+        <v>16.489999999999998</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.5344461305007586</v>
+        <v>1.6773736025362924</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1486,31 +1486,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>201.87</v>
+        <v>169.72</v>
       </c>
       <c r="C26" s="13">
-        <v>6413</v>
+        <v>5278</v>
       </c>
       <c r="D26" s="14">
-        <v>20105</v>
+        <v>19943</v>
       </c>
       <c r="E26" s="14">
-        <v>16490</v>
+        <v>17622</v>
       </c>
       <c r="F26" s="14">
-        <v>11986</v>
+        <v>13180</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>20.105</v>
+        <v>19.943000000000001</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>16.489999999999998</v>
+        <v>17.622</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>1.6773736025362924</v>
+        <v>1.5131259484066768</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1519,31 +1519,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>270.48</v>
+        <v>278.49</v>
       </c>
       <c r="C27" s="6">
-        <v>6729</v>
+        <v>7339</v>
       </c>
       <c r="D27" s="7">
-        <v>19493</v>
+        <v>19674</v>
       </c>
       <c r="E27" s="7">
-        <v>15612</v>
+        <v>17111</v>
       </c>
       <c r="F27" s="7">
-        <v>11611</v>
+        <v>9892</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>19.492999999999999</v>
+        <v>19.673999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>15.612</v>
+        <v>17.111000000000001</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.6788390319524589</v>
+        <v>1.9888799029518802</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1558,25 +1558,25 @@
         <v>4103</v>
       </c>
       <c r="D28" s="14">
-        <v>19386</v>
+        <v>19378</v>
       </c>
       <c r="E28" s="14">
-        <v>18808</v>
+        <v>18809</v>
       </c>
       <c r="F28" s="14">
         <v>14168</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>19.385999999999999</v>
+        <v>19.378</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>18.808</v>
+        <v>18.809000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.3682947487295314</v>
+        <v>1.3677300959909655</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1591,25 +1591,25 @@
         <v>7008</v>
       </c>
       <c r="D29" s="7">
-        <v>19175</v>
+        <v>19163</v>
       </c>
       <c r="E29" s="7">
-        <v>15612</v>
+        <v>15617</v>
       </c>
       <c r="F29" s="7">
         <v>10680</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>19.175000000000001</v>
+        <v>19.163</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>15.612</v>
+        <v>15.617000000000001</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.7954119850187267</v>
+        <v>1.7942883895131085</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1618,31 +1618,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>278.49</v>
+        <v>270.48</v>
       </c>
       <c r="C30" s="13">
-        <v>7339</v>
+        <v>6729</v>
       </c>
       <c r="D30" s="14">
-        <v>19169</v>
+        <v>19005</v>
       </c>
       <c r="E30" s="14">
-        <v>17111</v>
+        <v>15617</v>
       </c>
       <c r="F30" s="14">
-        <v>9892</v>
+        <v>11611</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>19.169</v>
+        <v>19.004999999999999</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>17.111000000000001</v>
+        <v>15.617000000000001</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.9378285483218762</v>
+        <v>1.6368099216260443</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1651,31 +1651,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>43.67</v>
+        <v>299.8</v>
       </c>
       <c r="C31" s="6">
-        <v>3710</v>
+        <v>7001</v>
       </c>
       <c r="D31" s="7">
-        <v>18697</v>
+        <v>18626</v>
       </c>
       <c r="E31" s="7">
-        <v>17244</v>
+        <v>15102</v>
       </c>
       <c r="F31" s="7">
-        <v>14089</v>
+        <v>8178</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>18.696999999999999</v>
+        <v>18.626000000000001</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>17.244</v>
+        <v>15.102</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.3270636666903257</v>
+        <v>2.277573978967963</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1684,31 +1684,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>299.8</v>
+        <v>43.67</v>
       </c>
       <c r="C32" s="13">
-        <v>7001</v>
+        <v>3710</v>
       </c>
       <c r="D32" s="14">
-        <v>18632</v>
+        <v>17600</v>
       </c>
       <c r="E32" s="14">
-        <v>15094</v>
+        <v>16147</v>
       </c>
       <c r="F32" s="14">
-        <v>8178</v>
+        <v>14089</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>18.632000000000001</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>15.093999999999999</v>
+        <v>16.146999999999998</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>2.2783076546832968</v>
+        <v>1.2492015047199942</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1723,25 +1723,25 @@
         <v>7000</v>
       </c>
       <c r="D33" s="7">
-        <v>18611</v>
+        <v>17163</v>
       </c>
       <c r="E33" s="7">
-        <v>15121</v>
+        <v>13608</v>
       </c>
       <c r="F33" s="7">
         <v>9125</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>18.611000000000001</v>
+        <v>17.163</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>15.121</v>
+        <v>13.608000000000001</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>2.0395616438356163</v>
+        <v>1.8808767123287671</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1750,31 +1750,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>196.28</v>
+        <v>58.7</v>
       </c>
       <c r="C34" s="13">
-        <v>6359</v>
+        <v>4507</v>
       </c>
       <c r="D34" s="14">
-        <v>18611</v>
+        <v>16994</v>
       </c>
       <c r="E34" s="14">
-        <v>15365</v>
+        <v>15034</v>
       </c>
       <c r="F34" s="14">
-        <v>10196</v>
+        <v>11674</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>18.611000000000001</v>
+        <v>16.994</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>15.365</v>
+        <v>15.034000000000001</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.8253236563358179</v>
+        <v>1.4557135514819257</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1783,31 +1783,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>58.7</v>
+        <v>196.28</v>
       </c>
       <c r="C35" s="6">
-        <v>4507</v>
+        <v>6359</v>
       </c>
       <c r="D35" s="7">
-        <v>16994</v>
+        <v>16820</v>
       </c>
       <c r="E35" s="7">
-        <v>15034</v>
+        <v>13608</v>
       </c>
       <c r="F35" s="7">
-        <v>11674</v>
+        <v>10196</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>16.994</v>
+        <v>16.82</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>15.034000000000001</v>
+        <v>13.608000000000001</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.4557135514819257</v>
+        <v>1.64966653589643</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1822,25 +1822,25 @@
         <v>6953</v>
       </c>
       <c r="D36" s="14">
-        <v>16726</v>
+        <v>16627</v>
       </c>
       <c r="E36" s="14">
-        <v>15008</v>
+        <v>13506</v>
       </c>
       <c r="F36" s="14">
         <v>6693</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>16.725999999999999</v>
+        <v>16.626999999999999</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>15.007999999999999</v>
+        <v>13.506</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>2.4990288360974153</v>
+        <v>2.4842372628118929</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1849,31 +1849,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>131.93</v>
+        <v>140.68</v>
       </c>
       <c r="C37" s="6">
-        <v>5328</v>
+        <v>4965</v>
       </c>
       <c r="D37" s="7">
-        <v>16636</v>
+        <v>16571</v>
       </c>
       <c r="E37" s="7">
-        <v>14377</v>
+        <v>13918</v>
       </c>
       <c r="F37" s="7">
-        <v>11332</v>
+        <v>10711</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" ref="G37:G55" si="3">D37/1000</f>
-        <v>16.635999999999999</v>
+        <v>16.571000000000002</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H55" si="4">E37/1000</f>
-        <v>14.377000000000001</v>
+        <v>13.917999999999999</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I55" si="5">IFERROR(D37/F37,"")</f>
-        <v>1.4680550653018003</v>
+        <v>1.5471011110073756</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1882,31 +1882,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>140.68</v>
+        <v>131.93</v>
       </c>
       <c r="C38" s="13">
-        <v>4965</v>
+        <v>5328</v>
       </c>
       <c r="D38" s="14">
-        <v>16571</v>
+        <v>15539</v>
       </c>
       <c r="E38" s="14">
-        <v>13918</v>
+        <v>13280</v>
       </c>
       <c r="F38" s="14">
-        <v>10711</v>
+        <v>11332</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="3"/>
-        <v>16.571000000000002</v>
+        <v>15.539</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
-        <v>13.917999999999999</v>
+        <v>13.28</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v>1.5471011110073756</v>
+        <v>1.3712495587716202</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1948,31 +1948,31 @@
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>174.68</v>
+        <v>60.51</v>
       </c>
       <c r="C40" s="13">
-        <v>5276</v>
+        <v>3703</v>
       </c>
       <c r="D40" s="14">
-        <v>15420</v>
+        <v>15324</v>
       </c>
       <c r="E40" s="14">
-        <v>13918</v>
+        <v>13506</v>
       </c>
       <c r="F40" s="14">
-        <v>9459</v>
+        <v>6700</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="3"/>
-        <v>15.42</v>
+        <v>15.324</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="4"/>
-        <v>13.917999999999999</v>
+        <v>13.506</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>1.6301934665398035</v>
+        <v>2.2871641791044777</v>
       </c>
       <c r="J40" s="17"/>
     </row>
@@ -1981,31 +1981,31 @@
         <v>48</v>
       </c>
       <c r="B41" s="5">
-        <v>60.51</v>
+        <v>177.61</v>
       </c>
       <c r="C41" s="6">
-        <v>3703</v>
+        <v>5367</v>
       </c>
       <c r="D41" s="7">
-        <v>15324</v>
+        <v>15170</v>
       </c>
       <c r="E41" s="7">
-        <v>13506</v>
+        <v>12444</v>
       </c>
       <c r="F41" s="7">
-        <v>6700</v>
+        <v>8285</v>
       </c>
       <c r="G41" s="8">
         <f t="shared" si="3"/>
-        <v>15.324</v>
+        <v>15.17</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="4"/>
-        <v>13.506</v>
+        <v>12.444000000000001</v>
       </c>
       <c r="I41" s="9">
         <f t="shared" si="5"/>
-        <v>2.2871641791044777</v>
+        <v>1.8310199155099578</v>
       </c>
       <c r="J41" s="10"/>
     </row>
@@ -2014,31 +2014,31 @@
         <v>49</v>
       </c>
       <c r="B42" s="12">
-        <v>58.94</v>
+        <v>174.68</v>
       </c>
       <c r="C42" s="13">
-        <v>3772</v>
+        <v>5276</v>
       </c>
       <c r="D42" s="14">
-        <v>15084</v>
+        <v>15092</v>
       </c>
       <c r="E42" s="14">
-        <v>13526</v>
+        <v>12418</v>
       </c>
       <c r="F42" s="14">
-        <v>10512</v>
+        <v>9459</v>
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>15.084</v>
+        <v>15.092000000000001</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
-        <v>13.526</v>
+        <v>12.417999999999999</v>
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>1.4349315068493151</v>
+        <v>1.5955174965641188</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2047,10 +2047,10 @@
         <v>50</v>
       </c>
       <c r="B43" s="5">
-        <v>60.19</v>
+        <v>58.94</v>
       </c>
       <c r="C43" s="6">
-        <v>3809</v>
+        <v>3772</v>
       </c>
       <c r="D43" s="7">
         <v>15084</v>
@@ -2059,7 +2059,7 @@
         <v>13526</v>
       </c>
       <c r="F43" s="7">
-        <v>10313</v>
+        <v>10512</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>1.4626199941821003</v>
+        <v>1.4349315068493151</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2080,31 +2080,31 @@
         <v>51</v>
       </c>
       <c r="B44" s="12">
-        <v>124</v>
+        <v>60.19</v>
       </c>
       <c r="C44" s="13">
-        <v>4814</v>
+        <v>3809</v>
       </c>
       <c r="D44" s="14">
-        <v>14403</v>
+        <v>15084</v>
       </c>
       <c r="E44" s="14">
-        <v>12773</v>
+        <v>13121</v>
       </c>
       <c r="F44" s="14">
-        <v>9977</v>
+        <v>10313</v>
       </c>
       <c r="G44" s="15">
         <f t="shared" si="3"/>
-        <v>14.403</v>
+        <v>15.084</v>
       </c>
       <c r="H44" s="15">
         <f t="shared" si="4"/>
-        <v>12.773</v>
+        <v>13.121</v>
       </c>
       <c r="I44" s="16">
         <f t="shared" si="5"/>
-        <v>1.4436203267515286</v>
+        <v>1.4626199941821003</v>
       </c>
       <c r="J44" s="17"/>
     </row>
@@ -2113,31 +2113,31 @@
         <v>52</v>
       </c>
       <c r="B45" s="5">
-        <v>59.79</v>
+        <v>59.61</v>
       </c>
       <c r="C45" s="6">
-        <v>3770</v>
+        <v>3784</v>
       </c>
       <c r="D45" s="7">
-        <v>13975</v>
+        <v>13972</v>
       </c>
       <c r="E45" s="7">
-        <v>11615</v>
+        <v>12013</v>
       </c>
       <c r="F45" s="7">
-        <v>9014</v>
+        <v>9228</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="3"/>
-        <v>13.975</v>
+        <v>13.972</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="4"/>
-        <v>11.615</v>
+        <v>12.013</v>
       </c>
       <c r="I45" s="9">
         <f t="shared" si="5"/>
-        <v>1.5503660971821611</v>
+        <v>1.5140875596012138</v>
       </c>
       <c r="J45" s="10"/>
     </row>
@@ -2146,23 +2146,23 @@
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>59.61</v>
+        <v>60.87</v>
       </c>
       <c r="C46" s="13">
-        <v>3784</v>
+        <v>3801</v>
       </c>
       <c r="D46" s="14">
-        <v>13972</v>
+        <v>13967</v>
       </c>
       <c r="E46" s="14">
         <v>12013</v>
       </c>
       <c r="F46" s="14">
-        <v>9228</v>
+        <v>8017</v>
       </c>
       <c r="G46" s="15">
         <f t="shared" si="3"/>
-        <v>13.972</v>
+        <v>13.967000000000001</v>
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
-        <v>1.5140875596012138</v>
+        <v>1.7421728826244232</v>
       </c>
       <c r="J46" s="17"/>
     </row>
@@ -2179,31 +2179,31 @@
         <v>54</v>
       </c>
       <c r="B47" s="5">
-        <v>60.87</v>
+        <v>113.78</v>
       </c>
       <c r="C47" s="6">
-        <v>3801</v>
+        <v>4554</v>
       </c>
       <c r="D47" s="7">
-        <v>13967</v>
+        <v>13952</v>
       </c>
       <c r="E47" s="7">
-        <v>12013</v>
+        <v>11110</v>
       </c>
       <c r="F47" s="7">
-        <v>8017</v>
+        <v>8753</v>
       </c>
       <c r="G47" s="8">
         <f t="shared" si="3"/>
-        <v>13.967000000000001</v>
+        <v>13.952</v>
       </c>
       <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>12.013</v>
+        <v>11.11</v>
       </c>
       <c r="I47" s="9">
         <f t="shared" si="5"/>
-        <v>1.7421728826244232</v>
+        <v>1.5939677824745802</v>
       </c>
       <c r="J47" s="10"/>
     </row>
@@ -2212,31 +2212,31 @@
         <v>55</v>
       </c>
       <c r="B48" s="12">
-        <v>80.13</v>
+        <v>59.79</v>
       </c>
       <c r="C48" s="13">
-        <v>4466</v>
+        <v>3770</v>
       </c>
       <c r="D48" s="14">
-        <v>13565</v>
+        <v>13575</v>
       </c>
       <c r="E48" s="14">
-        <v>11110</v>
+        <v>11615</v>
       </c>
       <c r="F48" s="14">
-        <v>7792</v>
+        <v>9014</v>
       </c>
       <c r="G48" s="15">
         <f t="shared" si="3"/>
-        <v>13.565</v>
+        <v>13.574999999999999</v>
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>11.11</v>
+        <v>11.615</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
-        <v>1.740888090349076</v>
+        <v>1.5059906811626358</v>
       </c>
       <c r="J48" s="17"/>
     </row>
@@ -2245,23 +2245,23 @@
         <v>56</v>
       </c>
       <c r="B49" s="5">
-        <v>113.78</v>
+        <v>80.13</v>
       </c>
       <c r="C49" s="6">
-        <v>4554</v>
+        <v>4466</v>
       </c>
       <c r="D49" s="7">
-        <v>13152</v>
+        <v>13565</v>
       </c>
       <c r="E49" s="7">
         <v>11110</v>
       </c>
       <c r="F49" s="7">
-        <v>8753</v>
+        <v>7792</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="3"/>
-        <v>13.151999999999999</v>
+        <v>13.565</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
-        <v>1.5025705472409459</v>
+        <v>1.740888090349076</v>
       </c>
       <c r="J49" s="10"/>
     </row>
@@ -2278,31 +2278,31 @@
         <v>57</v>
       </c>
       <c r="B50" s="12">
-        <v>18.11</v>
+        <v>124</v>
       </c>
       <c r="C50" s="13">
-        <v>1911</v>
+        <v>4814</v>
       </c>
       <c r="D50" s="14">
-        <v>11562</v>
+        <v>13306</v>
       </c>
       <c r="E50" s="14">
-        <v>10874</v>
+        <v>11676</v>
       </c>
       <c r="F50" s="14">
-        <v>8310</v>
+        <v>9977</v>
       </c>
       <c r="G50" s="15">
         <f t="shared" si="3"/>
-        <v>11.561999999999999</v>
+        <v>13.305999999999999</v>
       </c>
       <c r="H50" s="15">
         <f t="shared" si="4"/>
-        <v>10.874000000000001</v>
+        <v>11.676</v>
       </c>
       <c r="I50" s="16">
         <f t="shared" si="5"/>
-        <v>1.3913357400722022</v>
+        <v>1.3336674351007316</v>
       </c>
       <c r="J50" s="17"/>
     </row>
@@ -2317,25 +2317,25 @@
         <v>3651</v>
       </c>
       <c r="D51" s="7">
-        <v>11452</v>
+        <v>10821</v>
       </c>
       <c r="E51" s="7">
-        <v>9716</v>
+        <v>8572</v>
       </c>
       <c r="F51" s="7">
         <v>7484</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="3"/>
-        <v>11.452</v>
+        <v>10.821</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="4"/>
-        <v>9.7159999999999993</v>
+        <v>8.5719999999999992</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="5"/>
-        <v>1.530197755211117</v>
+        <v>1.4458845537145912</v>
       </c>
       <c r="J51" s="10"/>
     </row>
@@ -2344,31 +2344,31 @@
         <v>59</v>
       </c>
       <c r="B52" s="12">
-        <v>177.61</v>
+        <v>19.78</v>
       </c>
       <c r="C52" s="13">
-        <v>5367</v>
+        <v>2018</v>
       </c>
       <c r="D52" s="14">
-        <v>11155</v>
+        <v>10444</v>
       </c>
       <c r="E52" s="14">
-        <v>9602</v>
+        <v>9670</v>
       </c>
       <c r="F52" s="14">
-        <v>8285</v>
+        <v>8848</v>
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>11.154999999999999</v>
+        <v>10.444000000000001</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
-        <v>9.6020000000000003</v>
+        <v>9.67</v>
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>1.3464091732045866</v>
+        <v>1.1803797468354431</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2377,31 +2377,31 @@
         <v>60</v>
       </c>
       <c r="B53" s="5">
-        <v>19.78</v>
+        <v>18.11</v>
       </c>
       <c r="C53" s="6">
-        <v>2018</v>
+        <v>1911</v>
       </c>
       <c r="D53" s="7">
-        <v>10444</v>
+        <v>10061</v>
       </c>
       <c r="E53" s="7">
-        <v>9670</v>
+        <v>9580</v>
       </c>
       <c r="F53" s="7">
-        <v>8848</v>
+        <v>8310</v>
       </c>
       <c r="G53" s="8">
         <f t="shared" si="3"/>
-        <v>10.444000000000001</v>
+        <v>10.061</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="4"/>
-        <v>9.67</v>
+        <v>9.58</v>
       </c>
       <c r="I53" s="9">
         <f t="shared" si="5"/>
-        <v>1.1803797468354431</v>
+        <v>1.2107099879663057</v>
       </c>
       <c r="J53" s="10"/>
     </row>
@@ -2416,25 +2416,25 @@
         <v>3848</v>
       </c>
       <c r="D54" s="14">
-        <v>9792</v>
+        <v>9202</v>
       </c>
       <c r="E54" s="14">
-        <v>8688</v>
+        <v>8639</v>
       </c>
       <c r="F54" s="14">
         <v>6820</v>
       </c>
       <c r="G54" s="15">
         <f t="shared" si="3"/>
-        <v>9.7919999999999998</v>
+        <v>9.202</v>
       </c>
       <c r="H54" s="15">
         <f t="shared" si="4"/>
-        <v>8.6880000000000006</v>
+        <v>8.6389999999999993</v>
       </c>
       <c r="I54" s="16">
         <f t="shared" si="5"/>
-        <v>1.4357771260997068</v>
+        <v>1.3492668621700881</v>
       </c>
       <c r="J54" s="17"/>
     </row>
@@ -2477,19 +2477,19 @@
       </c>
       <c r="B57" s="19">
         <f>SUM(B5:B55)</f>
-        <v>6880.8099999999995</v>
+        <v>6880.8099999999986</v>
       </c>
       <c r="D57" s="20">
         <f>MAX(D5:D55)</f>
-        <v>24868</v>
+        <v>24759</v>
       </c>
       <c r="G57" s="21">
         <f>IFERROR(MAX(G5:G55),"")</f>
-        <v>24.867999999999999</v>
+        <v>24.759</v>
       </c>
       <c r="I57" s="22">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
-        <v>1.6175094667508989</v>
+        <v>1.5968734547368444</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46328587-EBE7-493B-B4AD-21A0C27C47C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0843373C-DADE-41B0-BC03-773DB20E0E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0843373C-DADE-41B0-BC03-773DB20E0E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5758E7-A36C-42A3-8786-79CB5A1DEC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,24 +96,24 @@
     <t>T33</t>
   </si>
   <si>
+    <t>T-06A</t>
+  </si>
+  <si>
+    <t>T38</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T-24</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
     <t>T34</t>
   </si>
   <si>
-    <t>T-06A</t>
-  </si>
-  <si>
-    <t>T38</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-24</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
     <t>T-16A</t>
   </si>
   <si>
@@ -123,6 +123,9 @@
     <t>T-07A</t>
   </si>
   <si>
+    <t>T-03</t>
+  </si>
+  <si>
     <t>T-19</t>
   </si>
   <si>
@@ -132,42 +135,39 @@
     <t>T-18</t>
   </si>
   <si>
+    <t>T-15A</t>
+  </si>
+  <si>
+    <t>T-15B</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
     <t>T-23</t>
   </si>
   <si>
-    <t>T-15A</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-15B</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T30</t>
-  </si>
-  <si>
     <t>T-09</t>
   </si>
   <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-01C</t>
+  </si>
+  <si>
     <t>T-22</t>
   </si>
   <si>
-    <t>T-13</t>
-  </si>
-  <si>
-    <t>T-01C</t>
-  </si>
-  <si>
     <t>T-20</t>
   </si>
   <si>
@@ -192,22 +192,22 @@
     <t>T-21</t>
   </si>
   <si>
+    <t>T-10S</t>
+  </si>
+  <si>
+    <t>T-10A</t>
+  </si>
+  <si>
     <t>T-12S</t>
   </si>
   <si>
-    <t>T-10S</t>
+    <t>T-21A</t>
+  </si>
+  <si>
+    <t>T-11</t>
   </si>
   <si>
     <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-10A</t>
-  </si>
-  <si>
-    <t>T-21A</t>
   </si>
   <si>
     <t>T-27</t>
@@ -964,7 +964,7 @@
         <v>3607</v>
       </c>
       <c r="D10" s="14">
-        <v>22978</v>
+        <v>22977</v>
       </c>
       <c r="E10" s="14">
         <v>20938</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>22.978000000000002</v>
+        <v>22.977</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.4140307692307692</v>
+        <v>1.4139692307692309</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -997,7 +997,7 @@
         <v>7372</v>
       </c>
       <c r="D11" s="7">
-        <v>22738</v>
+        <v>22713</v>
       </c>
       <c r="E11" s="7">
         <v>19115</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>22.738</v>
+        <v>22.713000000000001</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.9505876297503646</v>
+        <v>1.9484429956249465</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1057,31 +1057,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>131.51</v>
+        <v>132.93</v>
       </c>
       <c r="C13" s="6">
-        <v>4710</v>
+        <v>4758</v>
       </c>
       <c r="D13" s="7">
-        <v>22174</v>
+        <v>22075</v>
       </c>
       <c r="E13" s="7">
-        <v>18823</v>
+        <v>19695</v>
       </c>
       <c r="F13" s="7">
-        <v>14642</v>
+        <v>14217</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>22.173999999999999</v>
+        <v>22.074999999999999</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>18.823</v>
+        <v>19.695</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.5144105996448574</v>
+        <v>1.5527185763522544</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1090,31 +1090,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>132.93</v>
+        <v>140.69</v>
       </c>
       <c r="C14" s="13">
-        <v>4758</v>
+        <v>4981</v>
       </c>
       <c r="D14" s="14">
-        <v>22075</v>
+        <v>22035</v>
       </c>
       <c r="E14" s="14">
-        <v>19695</v>
+        <v>19531</v>
       </c>
       <c r="F14" s="14">
-        <v>14217</v>
+        <v>14856</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>22.074999999999999</v>
+        <v>22.035</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>19.695</v>
+        <v>19.530999999999999</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.5527185763522544</v>
+        <v>1.4832390953150243</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1123,31 +1123,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>140.69</v>
+        <v>144.9</v>
       </c>
       <c r="C15" s="6">
-        <v>4981</v>
+        <v>4944</v>
       </c>
       <c r="D15" s="7">
-        <v>22035</v>
+        <v>21636</v>
       </c>
       <c r="E15" s="7">
-        <v>19531</v>
+        <v>20656</v>
       </c>
       <c r="F15" s="7">
-        <v>14856</v>
+        <v>15014</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>22.035</v>
+        <v>21.635999999999999</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>19.530999999999999</v>
+        <v>20.655999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.4832390953150243</v>
+        <v>1.4410550153190356</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1156,31 +1156,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>144.9</v>
+        <v>83.32</v>
       </c>
       <c r="C16" s="13">
-        <v>4944</v>
+        <v>3691</v>
       </c>
       <c r="D16" s="14">
-        <v>21636</v>
+        <v>21580</v>
       </c>
       <c r="E16" s="14">
-        <v>20656</v>
+        <v>20114</v>
       </c>
       <c r="F16" s="14">
-        <v>15014</v>
+        <v>15125</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>21.635999999999999</v>
+        <v>21.58</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>20.655999999999999</v>
+        <v>20.114000000000001</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.4410550153190356</v>
+        <v>1.4267768595041321</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1189,31 +1189,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>83.32</v>
+        <v>53.96</v>
       </c>
       <c r="C17" s="6">
-        <v>3691</v>
+        <v>3674</v>
       </c>
       <c r="D17" s="7">
-        <v>21580</v>
+        <v>21197</v>
       </c>
       <c r="E17" s="7">
-        <v>20114</v>
+        <v>19335</v>
       </c>
       <c r="F17" s="7">
-        <v>15125</v>
+        <v>13875</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>21.58</v>
+        <v>21.196999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>20.114000000000001</v>
+        <v>19.335000000000001</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.4267768595041321</v>
+        <v>1.5277117117117116</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1222,31 +1222,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>53.96</v>
+        <v>131.51</v>
       </c>
       <c r="C18" s="13">
-        <v>3674</v>
+        <v>4710</v>
       </c>
       <c r="D18" s="14">
-        <v>21197</v>
+        <v>21163</v>
       </c>
       <c r="E18" s="14">
-        <v>19335</v>
+        <v>18822</v>
       </c>
       <c r="F18" s="14">
-        <v>13875</v>
+        <v>14642</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>21.196999999999999</v>
+        <v>21.163</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>19.335000000000001</v>
+        <v>18.821999999999999</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.5277117117117116</v>
+        <v>1.4453626553749488</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1354,31 +1354,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>150.72</v>
+        <v>278.49</v>
       </c>
       <c r="C22" s="13">
-        <v>5638</v>
+        <v>7339</v>
       </c>
       <c r="D22" s="14">
-        <v>20820</v>
+        <v>20679</v>
       </c>
       <c r="E22" s="14">
-        <v>17681</v>
+        <v>17111</v>
       </c>
       <c r="F22" s="14">
-        <v>13240</v>
+        <v>9892</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>20.82</v>
+        <v>20.678999999999998</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>17.681000000000001</v>
+        <v>17.111000000000001</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.5725075528700907</v>
+        <v>2.0904771532551556</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1387,31 +1387,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>239.17</v>
+        <v>150.72</v>
       </c>
       <c r="C23" s="6">
-        <v>6359</v>
+        <v>5638</v>
       </c>
       <c r="D23" s="7">
-        <v>20433</v>
+        <v>20496</v>
       </c>
       <c r="E23" s="7">
-        <v>17550</v>
+        <v>17681</v>
       </c>
       <c r="F23" s="7">
-        <v>15489</v>
+        <v>13240</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>20.433</v>
+        <v>20.495999999999999</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>17.55</v>
+        <v>17.681000000000001</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.3191942668990897</v>
+        <v>1.5480362537764349</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1420,31 +1420,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>115.23</v>
+        <v>239.17</v>
       </c>
       <c r="C24" s="13">
-        <v>4528</v>
+        <v>6359</v>
       </c>
       <c r="D24" s="14">
-        <v>20391</v>
+        <v>20433</v>
       </c>
       <c r="E24" s="14">
-        <v>18838</v>
+        <v>17560</v>
       </c>
       <c r="F24" s="14">
-        <v>14106</v>
+        <v>15489</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>20.390999999999998</v>
+        <v>20.433</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>18.838000000000001</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.4455550829434283</v>
+        <v>1.3191942668990897</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1453,31 +1453,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>201.87</v>
+        <v>115.23</v>
       </c>
       <c r="C25" s="6">
-        <v>6413</v>
+        <v>4528</v>
       </c>
       <c r="D25" s="7">
-        <v>20105</v>
+        <v>20391</v>
       </c>
       <c r="E25" s="7">
-        <v>16490</v>
+        <v>18838</v>
       </c>
       <c r="F25" s="7">
-        <v>11986</v>
+        <v>14106</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>20.105</v>
+        <v>20.390999999999998</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>16.489999999999998</v>
+        <v>18.838000000000001</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.6773736025362924</v>
+        <v>1.4455550829434283</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1519,31 +1519,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>278.49</v>
+        <v>80.430000000000007</v>
       </c>
       <c r="C27" s="6">
-        <v>7339</v>
+        <v>4103</v>
       </c>
       <c r="D27" s="7">
-        <v>19674</v>
+        <v>19377</v>
       </c>
       <c r="E27" s="7">
-        <v>17111</v>
+        <v>18809</v>
       </c>
       <c r="F27" s="7">
-        <v>9892</v>
+        <v>14168</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>19.673999999999999</v>
+        <v>19.376999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>17.111000000000001</v>
+        <v>18.809000000000001</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.9888799029518802</v>
+        <v>1.3676595143986447</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1552,31 +1552,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>80.430000000000007</v>
+        <v>300.64</v>
       </c>
       <c r="C28" s="13">
-        <v>4103</v>
+        <v>7008</v>
       </c>
       <c r="D28" s="14">
-        <v>19378</v>
+        <v>19163</v>
       </c>
       <c r="E28" s="14">
-        <v>18809</v>
+        <v>15617</v>
       </c>
       <c r="F28" s="14">
-        <v>14168</v>
+        <v>10680</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>19.378</v>
+        <v>19.163</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>18.809000000000001</v>
+        <v>15.617000000000001</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.3677300959909655</v>
+        <v>1.7942883895131085</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1585,23 +1585,23 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>300.64</v>
+        <v>270.48</v>
       </c>
       <c r="C29" s="6">
-        <v>7008</v>
+        <v>6729</v>
       </c>
       <c r="D29" s="7">
-        <v>19163</v>
+        <v>19005</v>
       </c>
       <c r="E29" s="7">
         <v>15617</v>
       </c>
       <c r="F29" s="7">
-        <v>10680</v>
+        <v>11611</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>19.163</v>
+        <v>19.004999999999999</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.7942883895131085</v>
+        <v>1.6368099216260443</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1618,31 +1618,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>270.48</v>
+        <v>299.8</v>
       </c>
       <c r="C30" s="13">
-        <v>6729</v>
+        <v>7001</v>
       </c>
       <c r="D30" s="14">
-        <v>19005</v>
+        <v>18656</v>
       </c>
       <c r="E30" s="14">
-        <v>15617</v>
+        <v>15102</v>
       </c>
       <c r="F30" s="14">
-        <v>11611</v>
+        <v>8178</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>19.004999999999999</v>
+        <v>18.655999999999999</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>15.617000000000001</v>
+        <v>15.102</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.6368099216260443</v>
+        <v>2.2812423575446319</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1651,31 +1651,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>299.8</v>
+        <v>43.67</v>
       </c>
       <c r="C31" s="6">
-        <v>7001</v>
+        <v>3710</v>
       </c>
       <c r="D31" s="7">
-        <v>18626</v>
+        <v>18026</v>
       </c>
       <c r="E31" s="7">
-        <v>15102</v>
+        <v>16147</v>
       </c>
       <c r="F31" s="7">
-        <v>8178</v>
+        <v>14089</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>18.626000000000001</v>
+        <v>18.026</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>15.102</v>
+        <v>16.146999999999998</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>2.277573978967963</v>
+        <v>1.2794378593228759</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1684,31 +1684,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>43.67</v>
+        <v>201.87</v>
       </c>
       <c r="C32" s="13">
-        <v>3710</v>
+        <v>6413</v>
       </c>
       <c r="D32" s="14">
-        <v>17600</v>
+        <v>17832</v>
       </c>
       <c r="E32" s="14">
-        <v>16147</v>
+        <v>15852</v>
       </c>
       <c r="F32" s="14">
-        <v>14089</v>
+        <v>11986</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
+        <v>17.832000000000001</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>16.146999999999998</v>
+        <v>15.852</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.2492015047199942</v>
+        <v>1.4877356916402469</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1750,31 +1750,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>58.7</v>
+        <v>196.28</v>
       </c>
       <c r="C34" s="13">
-        <v>4507</v>
+        <v>6359</v>
       </c>
       <c r="D34" s="14">
-        <v>16994</v>
+        <v>16795</v>
       </c>
       <c r="E34" s="14">
-        <v>15034</v>
+        <v>13608</v>
       </c>
       <c r="F34" s="14">
-        <v>11674</v>
+        <v>10196</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>16.994</v>
+        <v>16.795000000000002</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>15.034000000000001</v>
+        <v>13.608000000000001</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.4557135514819257</v>
+        <v>1.6472145939584151</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1783,31 +1783,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>196.28</v>
+        <v>302.68</v>
       </c>
       <c r="C35" s="6">
-        <v>6359</v>
+        <v>6953</v>
       </c>
       <c r="D35" s="7">
-        <v>16820</v>
+        <v>16655</v>
       </c>
       <c r="E35" s="7">
-        <v>13608</v>
+        <v>13506</v>
       </c>
       <c r="F35" s="7">
-        <v>10196</v>
+        <v>6693</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>16.82</v>
+        <v>16.655000000000001</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>13.608000000000001</v>
+        <v>13.506</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.64966653589643</v>
+        <v>2.488420738084566</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1816,31 +1816,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>302.68</v>
+        <v>58.7</v>
       </c>
       <c r="C36" s="13">
-        <v>6953</v>
+        <v>4507</v>
       </c>
       <c r="D36" s="14">
-        <v>16627</v>
+        <v>16139</v>
       </c>
       <c r="E36" s="14">
-        <v>13506</v>
+        <v>14394</v>
       </c>
       <c r="F36" s="14">
-        <v>6693</v>
+        <v>11674</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>16.626999999999999</v>
+        <v>16.138999999999999</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>13.506</v>
+        <v>14.394</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>2.4842372628118929</v>
+        <v>1.3824738735651876</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1855,25 +1855,25 @@
         <v>4965</v>
       </c>
       <c r="D37" s="7">
-        <v>16571</v>
+        <v>15932</v>
       </c>
       <c r="E37" s="7">
-        <v>13918</v>
+        <v>13280</v>
       </c>
       <c r="F37" s="7">
         <v>10711</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" ref="G37:G55" si="3">D37/1000</f>
-        <v>16.571000000000002</v>
+        <v>15.932</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H55" si="4">E37/1000</f>
-        <v>13.917999999999999</v>
+        <v>13.28</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I55" si="5">IFERROR(D37/F37,"")</f>
-        <v>1.5471011110073756</v>
+        <v>1.4874428157968445</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1888,7 +1888,7 @@
         <v>5328</v>
       </c>
       <c r="D38" s="14">
-        <v>15539</v>
+        <v>15765</v>
       </c>
       <c r="E38" s="14">
         <v>13280</v>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="G38" s="15">
         <f t="shared" si="3"/>
-        <v>15.539</v>
+        <v>15.765000000000001</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v>1.3712495587716202</v>
+        <v>1.3911930815390046</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -2020,25 +2020,25 @@
         <v>5276</v>
       </c>
       <c r="D42" s="14">
-        <v>15092</v>
+        <v>14782</v>
       </c>
       <c r="E42" s="14">
-        <v>12418</v>
+        <v>12417</v>
       </c>
       <c r="F42" s="14">
         <v>9459</v>
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>15.092000000000001</v>
+        <v>14.782</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
-        <v>12.417999999999999</v>
+        <v>12.417</v>
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>1.5955174965641188</v>
+        <v>1.5627444761602707</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2053,25 +2053,25 @@
         <v>3772</v>
       </c>
       <c r="D43" s="7">
-        <v>15084</v>
+        <v>14444</v>
       </c>
       <c r="E43" s="7">
-        <v>13526</v>
+        <v>12879</v>
       </c>
       <c r="F43" s="7">
         <v>10512</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
-        <v>15.084</v>
+        <v>14.444000000000001</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="4"/>
-        <v>13.526</v>
+        <v>12.879</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>1.4349315068493151</v>
+        <v>1.3740487062404871</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2086,25 +2086,25 @@
         <v>3809</v>
       </c>
       <c r="D44" s="14">
-        <v>15084</v>
+        <v>14444</v>
       </c>
       <c r="E44" s="14">
-        <v>13121</v>
+        <v>12475</v>
       </c>
       <c r="F44" s="14">
         <v>10313</v>
       </c>
       <c r="G44" s="15">
         <f t="shared" si="3"/>
-        <v>15.084</v>
+        <v>14.444000000000001</v>
       </c>
       <c r="H44" s="15">
         <f t="shared" si="4"/>
-        <v>13.121</v>
+        <v>12.475</v>
       </c>
       <c r="I44" s="16">
         <f t="shared" si="5"/>
-        <v>1.4626199941821003</v>
+        <v>1.4005623969746921</v>
       </c>
       <c r="J44" s="17"/>
     </row>
@@ -2113,23 +2113,23 @@
         <v>52</v>
       </c>
       <c r="B45" s="5">
-        <v>59.61</v>
+        <v>60.87</v>
       </c>
       <c r="C45" s="6">
-        <v>3784</v>
+        <v>3801</v>
       </c>
       <c r="D45" s="7">
-        <v>13972</v>
+        <v>13967</v>
       </c>
       <c r="E45" s="7">
         <v>12013</v>
       </c>
       <c r="F45" s="7">
-        <v>9228</v>
+        <v>8017</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="3"/>
-        <v>13.972</v>
+        <v>13.967000000000001</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="4"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="I45" s="9">
         <f t="shared" si="5"/>
-        <v>1.5140875596012138</v>
+        <v>1.7421728826244232</v>
       </c>
       <c r="J45" s="10"/>
     </row>
@@ -2146,31 +2146,31 @@
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>60.87</v>
+        <v>80.13</v>
       </c>
       <c r="C46" s="13">
-        <v>3801</v>
+        <v>4466</v>
       </c>
       <c r="D46" s="14">
-        <v>13967</v>
+        <v>13565</v>
       </c>
       <c r="E46" s="14">
-        <v>12013</v>
+        <v>11110</v>
       </c>
       <c r="F46" s="14">
-        <v>8017</v>
+        <v>7792</v>
       </c>
       <c r="G46" s="15">
         <f t="shared" si="3"/>
-        <v>13.967000000000001</v>
+        <v>13.565</v>
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
-        <v>12.013</v>
+        <v>11.11</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
-        <v>1.7421728826244232</v>
+        <v>1.740888090349076</v>
       </c>
       <c r="J46" s="17"/>
     </row>
@@ -2179,31 +2179,31 @@
         <v>54</v>
       </c>
       <c r="B47" s="5">
-        <v>113.78</v>
+        <v>59.61</v>
       </c>
       <c r="C47" s="6">
-        <v>4554</v>
+        <v>3784</v>
       </c>
       <c r="D47" s="7">
-        <v>13952</v>
+        <v>13334</v>
       </c>
       <c r="E47" s="7">
-        <v>11110</v>
+        <v>12013</v>
       </c>
       <c r="F47" s="7">
-        <v>8753</v>
+        <v>9228</v>
       </c>
       <c r="G47" s="8">
         <f t="shared" si="3"/>
-        <v>13.952</v>
+        <v>13.334</v>
       </c>
       <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>11.11</v>
+        <v>12.013</v>
       </c>
       <c r="I47" s="9">
         <f t="shared" si="5"/>
-        <v>1.5939677824745802</v>
+        <v>1.4449501517121803</v>
       </c>
       <c r="J47" s="10"/>
     </row>
@@ -2212,31 +2212,31 @@
         <v>55</v>
       </c>
       <c r="B48" s="12">
-        <v>59.79</v>
+        <v>124</v>
       </c>
       <c r="C48" s="13">
-        <v>3770</v>
+        <v>4814</v>
       </c>
       <c r="D48" s="14">
-        <v>13575</v>
+        <v>13306</v>
       </c>
       <c r="E48" s="14">
-        <v>11615</v>
+        <v>11669</v>
       </c>
       <c r="F48" s="14">
-        <v>9014</v>
+        <v>9977</v>
       </c>
       <c r="G48" s="15">
         <f t="shared" si="3"/>
-        <v>13.574999999999999</v>
+        <v>13.305999999999999</v>
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>11.615</v>
+        <v>11.669</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
-        <v>1.5059906811626358</v>
+        <v>1.3336674351007316</v>
       </c>
       <c r="J48" s="17"/>
     </row>
@@ -2245,31 +2245,31 @@
         <v>56</v>
       </c>
       <c r="B49" s="5">
-        <v>80.13</v>
+        <v>59.79</v>
       </c>
       <c r="C49" s="6">
-        <v>4466</v>
+        <v>3770</v>
       </c>
       <c r="D49" s="7">
-        <v>13565</v>
+        <v>13215</v>
       </c>
       <c r="E49" s="7">
-        <v>11110</v>
+        <v>11607</v>
       </c>
       <c r="F49" s="7">
-        <v>7792</v>
+        <v>9014</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="3"/>
-        <v>13.565</v>
+        <v>13.215</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
-        <v>11.11</v>
+        <v>11.606999999999999</v>
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
-        <v>1.740888090349076</v>
+        <v>1.4660528067450633</v>
       </c>
       <c r="J49" s="10"/>
     </row>
@@ -2278,31 +2278,31 @@
         <v>57</v>
       </c>
       <c r="B50" s="12">
-        <v>124</v>
+        <v>113.78</v>
       </c>
       <c r="C50" s="13">
-        <v>4814</v>
+        <v>4554</v>
       </c>
       <c r="D50" s="14">
-        <v>13306</v>
+        <v>12814</v>
       </c>
       <c r="E50" s="14">
-        <v>11676</v>
+        <v>10936</v>
       </c>
       <c r="F50" s="14">
-        <v>9977</v>
+        <v>8753</v>
       </c>
       <c r="G50" s="15">
         <f t="shared" si="3"/>
-        <v>13.305999999999999</v>
+        <v>12.814</v>
       </c>
       <c r="H50" s="15">
         <f t="shared" si="4"/>
-        <v>11.676</v>
+        <v>10.936</v>
       </c>
       <c r="I50" s="16">
         <f t="shared" si="5"/>
-        <v>1.3336674351007316</v>
+        <v>1.4639552153547355</v>
       </c>
       <c r="J50" s="17"/>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="I57" s="22">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
-        <v>1.5968734547368444</v>
+        <v>1.584011570234338</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5758E7-A36C-42A3-8786-79CB5A1DEC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52477BA4-B489-4B91-9244-B0E767A182FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -2386,7 +2386,7 @@
         <v>10061</v>
       </c>
       <c r="E53" s="7">
-        <v>9580</v>
+        <v>9574</v>
       </c>
       <c r="F53" s="7">
         <v>8310</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H53" s="8">
         <f t="shared" si="4"/>
-        <v>9.58</v>
+        <v>9.5739999999999998</v>
       </c>
       <c r="I53" s="9">
         <f t="shared" si="5"/>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52477BA4-B489-4B91-9244-B0E767A182FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C0E6AB-41F2-4E2B-A7BD-944DBE70BE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C0E6AB-41F2-4E2B-A7BD-944DBE70BE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053B67B6-11EB-4425-AAED-204C7A0ECCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053B67B6-11EB-4425-AAED-204C7A0ECCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CC8F98-2B63-416E-8A42-58AFD3C11CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -313,49 +313,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CC8F98-2B63-416E-8A42-58AFD3C11CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072D8A2F-9FC6-45F4-B10D-D8FD535ED400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -87,54 +87,54 @@
     <t>T-16B</t>
   </si>
   <si>
+    <t>T-04</t>
+  </si>
+  <si>
     <t>T37</t>
   </si>
   <si>
-    <t>T-04</t>
+    <t>T-06A</t>
   </si>
   <si>
     <t>T33</t>
   </si>
   <si>
-    <t>T-06A</t>
+    <t>T-06B</t>
   </si>
   <si>
     <t>T38</t>
   </si>
   <si>
-    <t>T-06B</t>
-  </si>
-  <si>
     <t>T-24</t>
   </si>
   <si>
     <t>T-07B</t>
   </si>
   <si>
+    <t>T-16A</t>
+  </si>
+  <si>
+    <t>T-15C</t>
+  </si>
+  <si>
+    <t>T-07A</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
     <t>T34</t>
   </si>
   <si>
-    <t>T-16A</t>
-  </si>
-  <si>
-    <t>T-15C</t>
-  </si>
-  <si>
-    <t>T-07A</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
     <t>T-19</t>
   </si>
   <si>
+    <t>T-18</t>
+  </si>
+  <si>
     <t>T31</t>
   </si>
   <si>
-    <t>T-18</t>
-  </si>
-  <si>
     <t>T-15A</t>
   </si>
   <si>
@@ -159,52 +159,52 @@
     <t>T-09</t>
   </si>
   <si>
+    <t>T-01C</t>
+  </si>
+  <si>
     <t>T-13</t>
   </si>
   <si>
-    <t>T-01C</t>
+    <t>T-01B</t>
   </si>
   <si>
     <t>T-22</t>
   </si>
   <si>
+    <t>T-01A</t>
+  </si>
+  <si>
     <t>T-20</t>
   </si>
   <si>
+    <t>T-10B</t>
+  </si>
+  <si>
     <t>T-22A</t>
   </si>
   <si>
-    <t>T-01B</t>
-  </si>
-  <si>
-    <t>T-01A</t>
-  </si>
-  <si>
-    <t>T-10B</t>
-  </si>
-  <si>
     <t>T-12</t>
   </si>
   <si>
+    <t>T-10S</t>
+  </si>
+  <si>
     <t>T-20S</t>
   </si>
   <si>
     <t>T-21</t>
   </si>
   <si>
-    <t>T-10S</t>
-  </si>
-  <si>
     <t>T-10A</t>
   </si>
   <si>
+    <t>T-11</t>
+  </si>
+  <si>
     <t>T-12S</t>
   </si>
   <si>
     <t>T-21A</t>
-  </si>
-  <si>
-    <t>T-11</t>
   </si>
   <si>
     <t>T-11A</t>
@@ -313,58 +313,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -808,25 +799,25 @@
         <v>4758</v>
       </c>
       <c r="D5" s="7">
-        <v>24759</v>
+        <v>25406</v>
       </c>
       <c r="E5" s="7">
-        <v>24137</v>
+        <v>24785</v>
       </c>
       <c r="F5" s="7">
         <v>15004</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G36" si="0">D5/1000</f>
-        <v>24.759</v>
+        <v>25.405999999999999</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H36" si="1">E5/1000</f>
-        <v>24.137</v>
+        <v>24.785</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
-        <v>1.6501599573447081</v>
+        <v>1.6932817915222607</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -841,25 +832,25 @@
         <v>5486</v>
       </c>
       <c r="D6" s="14">
-        <v>24215</v>
+        <v>24863</v>
       </c>
       <c r="E6" s="14">
-        <v>21167</v>
+        <v>21815</v>
       </c>
       <c r="F6" s="14">
         <v>13634</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>24.215</v>
+        <v>24.863</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>21.167000000000002</v>
+        <v>21.815000000000001</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.7760745195833945</v>
+        <v>1.8236027578113541</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -874,25 +865,25 @@
         <v>4054</v>
       </c>
       <c r="D7" s="7">
-        <v>24190</v>
+        <v>24837</v>
       </c>
       <c r="E7" s="7">
-        <v>23428</v>
+        <v>24076</v>
       </c>
       <c r="F7" s="7">
         <v>14361</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>24.19</v>
+        <v>24.837</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>23.428000000000001</v>
+        <v>24.076000000000001</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.6844230903140449</v>
+        <v>1.729475663254648</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -907,25 +898,25 @@
         <v>5173</v>
       </c>
       <c r="D8" s="14">
-        <v>23868</v>
+        <v>24371</v>
       </c>
       <c r="E8" s="14">
-        <v>20924</v>
+        <v>21267</v>
       </c>
       <c r="F8" s="14">
         <v>15747</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>23.867999999999999</v>
+        <v>24.370999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>20.923999999999999</v>
+        <v>21.266999999999999</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.5157172794818061</v>
+        <v>1.5476598717215977</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -940,25 +931,25 @@
         <v>3913</v>
       </c>
       <c r="D9" s="7">
-        <v>23204</v>
+        <v>23851</v>
       </c>
       <c r="E9" s="7">
-        <v>21068</v>
+        <v>21716</v>
       </c>
       <c r="F9" s="7">
         <v>16110</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>23.204000000000001</v>
+        <v>23.850999999999999</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>21.068000000000001</v>
+        <v>21.716000000000001</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.4403476101800123</v>
+        <v>1.4805090006207324</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -967,31 +958,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>67.459999999999994</v>
+        <v>302.63</v>
       </c>
       <c r="C10" s="13">
-        <v>3607</v>
+        <v>7372</v>
       </c>
       <c r="D10" s="14">
-        <v>22977</v>
+        <v>23361</v>
       </c>
       <c r="E10" s="14">
-        <v>20938</v>
+        <v>19763</v>
       </c>
       <c r="F10" s="14">
-        <v>16250</v>
+        <v>11657</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>22.977</v>
+        <v>23.361000000000001</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>20.937999999999999</v>
+        <v>19.763000000000002</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.4139692307692309</v>
+        <v>2.0040319121557864</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1000,31 +991,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>302.63</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="C11" s="6">
-        <v>7372</v>
+        <v>3607</v>
       </c>
       <c r="D11" s="7">
-        <v>22713</v>
+        <v>22977</v>
       </c>
       <c r="E11" s="7">
-        <v>19115</v>
+        <v>20938</v>
       </c>
       <c r="F11" s="7">
-        <v>11657</v>
+        <v>16250</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>22.713000000000001</v>
+        <v>22.977</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>19.114999999999998</v>
+        <v>20.937999999999999</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.9484429956249465</v>
+        <v>1.4139692307692309</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1033,31 +1024,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>149.61000000000001</v>
+        <v>132.93</v>
       </c>
       <c r="C12" s="13">
-        <v>5003</v>
+        <v>4758</v>
       </c>
       <c r="D12" s="14">
-        <v>22707</v>
+        <v>22722</v>
       </c>
       <c r="E12" s="14">
-        <v>20126</v>
+        <v>20343</v>
       </c>
       <c r="F12" s="14">
-        <v>15887</v>
+        <v>14217</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>22.707000000000001</v>
+        <v>22.722000000000001</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>20.126000000000001</v>
+        <v>20.343</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.4292818027317933</v>
+        <v>1.5982274741506648</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1066,31 +1057,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>132.93</v>
+        <v>149.61000000000001</v>
       </c>
       <c r="C13" s="6">
-        <v>4758</v>
+        <v>5003</v>
       </c>
       <c r="D13" s="7">
-        <v>22075</v>
+        <v>22707</v>
       </c>
       <c r="E13" s="7">
-        <v>19695</v>
+        <v>20126</v>
       </c>
       <c r="F13" s="7">
-        <v>14217</v>
+        <v>15887</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>22.074999999999999</v>
+        <v>22.707000000000001</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>19.695</v>
+        <v>20.126000000000001</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.5527185763522544</v>
+        <v>1.4292818027317933</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1099,31 +1090,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>140.69</v>
+        <v>144.9</v>
       </c>
       <c r="C14" s="13">
-        <v>4981</v>
+        <v>4944</v>
       </c>
       <c r="D14" s="14">
-        <v>22035</v>
+        <v>22283</v>
       </c>
       <c r="E14" s="14">
-        <v>19531</v>
+        <v>21304</v>
       </c>
       <c r="F14" s="14">
-        <v>14856</v>
+        <v>15014</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>22.035</v>
+        <v>22.283000000000001</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>19.530999999999999</v>
+        <v>21.303999999999998</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.4832390953150243</v>
+        <v>1.4841481284134808</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1132,31 +1123,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>144.9</v>
+        <v>140.69</v>
       </c>
       <c r="C15" s="6">
-        <v>4944</v>
+        <v>4981</v>
       </c>
       <c r="D15" s="7">
-        <v>21636</v>
+        <v>22035</v>
       </c>
       <c r="E15" s="7">
-        <v>20656</v>
+        <v>19531</v>
       </c>
       <c r="F15" s="7">
-        <v>15014</v>
+        <v>14856</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>21.635999999999999</v>
+        <v>22.035</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>20.655999999999999</v>
+        <v>19.530999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.4410550153190356</v>
+        <v>1.4832390953150243</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1171,25 +1162,25 @@
         <v>3691</v>
       </c>
       <c r="D16" s="14">
-        <v>21580</v>
+        <v>21922</v>
       </c>
       <c r="E16" s="14">
-        <v>20114</v>
+        <v>20457</v>
       </c>
       <c r="F16" s="14">
         <v>15125</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>21.58</v>
+        <v>21.922000000000001</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>20.114000000000001</v>
+        <v>20.457000000000001</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.4267768595041321</v>
+        <v>1.4493884297520661</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1204,25 +1195,25 @@
         <v>3674</v>
       </c>
       <c r="D17" s="7">
-        <v>21197</v>
+        <v>21845</v>
       </c>
       <c r="E17" s="7">
-        <v>19335</v>
+        <v>19982</v>
       </c>
       <c r="F17" s="7">
         <v>13875</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>21.196999999999999</v>
+        <v>21.844999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>19.335000000000001</v>
+        <v>19.981999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.5277117117117116</v>
+        <v>1.5744144144144143</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1231,31 +1222,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>131.51</v>
+        <v>56.03</v>
       </c>
       <c r="C18" s="13">
-        <v>4710</v>
+        <v>3746</v>
       </c>
       <c r="D18" s="14">
-        <v>21163</v>
+        <v>21765</v>
       </c>
       <c r="E18" s="14">
-        <v>18822</v>
+        <v>21304</v>
       </c>
       <c r="F18" s="14">
-        <v>14642</v>
+        <v>15750</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>21.163</v>
+        <v>21.765000000000001</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>18.821999999999999</v>
+        <v>21.303999999999998</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.4453626553749488</v>
+        <v>1.381904761904762</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1264,31 +1255,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>56.03</v>
+        <v>136.18</v>
       </c>
       <c r="C19" s="6">
-        <v>3746</v>
+        <v>4817</v>
       </c>
       <c r="D19" s="7">
-        <v>21118</v>
+        <v>21585</v>
       </c>
       <c r="E19" s="7">
-        <v>20656</v>
+        <v>20379</v>
       </c>
       <c r="F19" s="7">
-        <v>15750</v>
+        <v>14928</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>21.117999999999999</v>
+        <v>21.585000000000001</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>20.655999999999999</v>
+        <v>20.379000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.3408253968253969</v>
+        <v>1.4459405144694535</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1297,31 +1288,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>136.18</v>
+        <v>254.67</v>
       </c>
       <c r="C20" s="13">
-        <v>4817</v>
+        <v>6809</v>
       </c>
       <c r="D20" s="14">
-        <v>21088</v>
+        <v>21480</v>
       </c>
       <c r="E20" s="14">
-        <v>19732</v>
+        <v>18270</v>
       </c>
       <c r="F20" s="14">
-        <v>14928</v>
+        <v>12367</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>21.088000000000001</v>
+        <v>21.48</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>19.731999999999999</v>
+        <v>18.27</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.412647374062165</v>
+        <v>1.736880407536185</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1330,31 +1321,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>254.67</v>
+        <v>278.49</v>
       </c>
       <c r="C21" s="6">
-        <v>6809</v>
+        <v>7339</v>
       </c>
       <c r="D21" s="7">
-        <v>20832</v>
+        <v>21326</v>
       </c>
       <c r="E21" s="7">
-        <v>17622</v>
+        <v>17758</v>
       </c>
       <c r="F21" s="7">
-        <v>12367</v>
+        <v>9892</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>20.832000000000001</v>
+        <v>21.326000000000001</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>17.622</v>
+        <v>17.757999999999999</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.6844828980350934</v>
+        <v>2.1558835422563689</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1363,31 +1354,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>278.49</v>
+        <v>131.51</v>
       </c>
       <c r="C22" s="13">
-        <v>7339</v>
+        <v>4710</v>
       </c>
       <c r="D22" s="14">
-        <v>20679</v>
+        <v>21163</v>
       </c>
       <c r="E22" s="14">
-        <v>17111</v>
+        <v>18822</v>
       </c>
       <c r="F22" s="14">
-        <v>9892</v>
+        <v>14642</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>20.678999999999998</v>
+        <v>21.163</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>17.111000000000001</v>
+        <v>18.821999999999999</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>2.0904771532551556</v>
+        <v>1.4453626553749488</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1402,25 +1393,25 @@
         <v>5638</v>
       </c>
       <c r="D23" s="7">
-        <v>20496</v>
+        <v>20838</v>
       </c>
       <c r="E23" s="7">
-        <v>17681</v>
+        <v>18023</v>
       </c>
       <c r="F23" s="7">
         <v>13240</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>20.495999999999999</v>
+        <v>20.838000000000001</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>17.681000000000001</v>
+        <v>18.023</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.5480362537764349</v>
+        <v>1.5738670694864048</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1429,31 +1420,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>239.17</v>
+        <v>115.23</v>
       </c>
       <c r="C24" s="13">
-        <v>6359</v>
+        <v>4528</v>
       </c>
       <c r="D24" s="14">
-        <v>20433</v>
+        <v>20733</v>
       </c>
       <c r="E24" s="14">
-        <v>17560</v>
+        <v>19180</v>
       </c>
       <c r="F24" s="14">
-        <v>15489</v>
+        <v>14106</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>20.433</v>
+        <v>20.733000000000001</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>17.559999999999999</v>
+        <v>19.18</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.3191942668990897</v>
+        <v>1.4698000850701829</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1462,31 +1453,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>115.23</v>
+        <v>239.17</v>
       </c>
       <c r="C25" s="6">
-        <v>4528</v>
+        <v>6359</v>
       </c>
       <c r="D25" s="7">
-        <v>20391</v>
+        <v>20433</v>
       </c>
       <c r="E25" s="7">
-        <v>18838</v>
+        <v>17560</v>
       </c>
       <c r="F25" s="7">
-        <v>14106</v>
+        <v>15489</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>20.390999999999998</v>
+        <v>20.433</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>18.838000000000001</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.4455550829434283</v>
+        <v>1.3191942668990897</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1501,25 +1492,25 @@
         <v>5278</v>
       </c>
       <c r="D26" s="14">
-        <v>19943</v>
+        <v>20286</v>
       </c>
       <c r="E26" s="14">
-        <v>17622</v>
+        <v>18270</v>
       </c>
       <c r="F26" s="14">
         <v>13180</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>19.943000000000001</v>
+        <v>20.286000000000001</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>17.622</v>
+        <v>18.27</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>1.5131259484066768</v>
+        <v>1.5391502276176023</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1534,25 +1525,25 @@
         <v>4103</v>
       </c>
       <c r="D27" s="7">
-        <v>19377</v>
+        <v>20025</v>
       </c>
       <c r="E27" s="7">
-        <v>18809</v>
+        <v>19456</v>
       </c>
       <c r="F27" s="7">
         <v>14168</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>19.376999999999999</v>
+        <v>20.024999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>18.809000000000001</v>
+        <v>19.456</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.3676595143986447</v>
+        <v>1.4133963862224732</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1567,25 +1558,25 @@
         <v>7008</v>
       </c>
       <c r="D28" s="14">
-        <v>19163</v>
+        <v>19811</v>
       </c>
       <c r="E28" s="14">
-        <v>15617</v>
+        <v>16264</v>
       </c>
       <c r="F28" s="14">
         <v>10680</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>19.163</v>
+        <v>19.811</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>15.617000000000001</v>
+        <v>16.263999999999999</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.7942883895131085</v>
+        <v>1.8549625468164794</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1600,25 +1591,25 @@
         <v>6729</v>
       </c>
       <c r="D29" s="7">
-        <v>19005</v>
+        <v>19491</v>
       </c>
       <c r="E29" s="7">
-        <v>15617</v>
+        <v>16264</v>
       </c>
       <c r="F29" s="7">
         <v>11611</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>19.004999999999999</v>
+        <v>19.491</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>15.617000000000001</v>
+        <v>16.263999999999999</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.6368099216260443</v>
+        <v>1.6786667815003014</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1633,25 +1624,25 @@
         <v>7001</v>
       </c>
       <c r="D30" s="14">
-        <v>18656</v>
+        <v>19304</v>
       </c>
       <c r="E30" s="14">
-        <v>15102</v>
+        <v>15750</v>
       </c>
       <c r="F30" s="14">
         <v>8178</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>18.655999999999999</v>
+        <v>19.303999999999998</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>15.102</v>
+        <v>15.75</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>2.2812423575446319</v>
+        <v>2.3604793348006847</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1732,25 +1723,25 @@
         <v>7000</v>
       </c>
       <c r="D33" s="7">
-        <v>17163</v>
+        <v>17810</v>
       </c>
       <c r="E33" s="7">
-        <v>13608</v>
+        <v>14255</v>
       </c>
       <c r="F33" s="7">
         <v>9125</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>17.163</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>13.608000000000001</v>
+        <v>14.255000000000001</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.8808767123287671</v>
+        <v>1.9517808219178083</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1759,31 +1750,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>196.28</v>
+        <v>302.68</v>
       </c>
       <c r="C34" s="13">
-        <v>6359</v>
+        <v>6953</v>
       </c>
       <c r="D34" s="14">
-        <v>16795</v>
+        <v>17303</v>
       </c>
       <c r="E34" s="14">
-        <v>13608</v>
+        <v>14153</v>
       </c>
       <c r="F34" s="14">
-        <v>10196</v>
+        <v>6693</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>16.795000000000002</v>
+        <v>17.303000000000001</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>13.608000000000001</v>
+        <v>14.153</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.6472145939584151</v>
+        <v>2.5852383086807111</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1792,31 +1783,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>302.68</v>
+        <v>196.28</v>
       </c>
       <c r="C35" s="6">
-        <v>6953</v>
+        <v>6359</v>
       </c>
       <c r="D35" s="7">
-        <v>16655</v>
+        <v>17114</v>
       </c>
       <c r="E35" s="7">
-        <v>13506</v>
+        <v>14255</v>
       </c>
       <c r="F35" s="7">
-        <v>6693</v>
+        <v>10196</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>16.655000000000001</v>
+        <v>17.114000000000001</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>13.506</v>
+        <v>14.255000000000001</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>2.488420738084566</v>
+        <v>1.6785013730874854</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1825,31 +1816,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>58.7</v>
+        <v>65</v>
       </c>
       <c r="C36" s="13">
-        <v>4507</v>
+        <v>3845</v>
       </c>
       <c r="D36" s="14">
-        <v>16139</v>
+        <v>16170</v>
       </c>
       <c r="E36" s="14">
-        <v>14394</v>
+        <v>14182</v>
       </c>
       <c r="F36" s="14">
-        <v>11674</v>
+        <v>6902</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>16.138999999999999</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>14.394</v>
+        <v>14.182</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.3824738735651876</v>
+        <v>2.3427991886409738</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1858,31 +1849,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>140.68</v>
+        <v>58.7</v>
       </c>
       <c r="C37" s="6">
-        <v>4965</v>
+        <v>4507</v>
       </c>
       <c r="D37" s="7">
-        <v>15932</v>
+        <v>16139</v>
       </c>
       <c r="E37" s="7">
-        <v>13280</v>
+        <v>14394</v>
       </c>
       <c r="F37" s="7">
-        <v>10711</v>
+        <v>11674</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" ref="G37:G55" si="3">D37/1000</f>
-        <v>15.932</v>
+        <v>16.138999999999999</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H55" si="4">E37/1000</f>
-        <v>13.28</v>
+        <v>14.394</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I55" si="5">IFERROR(D37/F37,"")</f>
-        <v>1.4874428157968445</v>
+        <v>1.3824738735651876</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1891,31 +1882,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>131.93</v>
+        <v>60.51</v>
       </c>
       <c r="C38" s="13">
-        <v>5328</v>
+        <v>3703</v>
       </c>
       <c r="D38" s="14">
-        <v>15765</v>
+        <v>15971</v>
       </c>
       <c r="E38" s="14">
-        <v>13280</v>
+        <v>14153</v>
       </c>
       <c r="F38" s="14">
-        <v>11332</v>
+        <v>6700</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="3"/>
-        <v>15.765000000000001</v>
+        <v>15.971</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
-        <v>13.28</v>
+        <v>14.153</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v>1.3911930815390046</v>
+        <v>2.383731343283582</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1924,31 +1915,31 @@
         <v>46</v>
       </c>
       <c r="B39" s="5">
-        <v>65</v>
+        <v>140.68</v>
       </c>
       <c r="C39" s="6">
-        <v>3845</v>
+        <v>4965</v>
       </c>
       <c r="D39" s="7">
-        <v>15522</v>
+        <v>15932</v>
       </c>
       <c r="E39" s="7">
-        <v>13534</v>
+        <v>13280</v>
       </c>
       <c r="F39" s="7">
-        <v>6902</v>
+        <v>10711</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="3"/>
-        <v>15.522</v>
+        <v>15.932</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="4"/>
-        <v>13.534000000000001</v>
+        <v>13.28</v>
       </c>
       <c r="I39" s="9">
         <f t="shared" si="5"/>
-        <v>2.2489133584468268</v>
+        <v>1.4874428157968445</v>
       </c>
       <c r="J39" s="10"/>
     </row>
@@ -1957,31 +1948,31 @@
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>60.51</v>
+        <v>177.61</v>
       </c>
       <c r="C40" s="13">
-        <v>3703</v>
+        <v>5367</v>
       </c>
       <c r="D40" s="14">
-        <v>15324</v>
+        <v>15817</v>
       </c>
       <c r="E40" s="14">
-        <v>13506</v>
+        <v>13092</v>
       </c>
       <c r="F40" s="14">
-        <v>6700</v>
+        <v>8285</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="3"/>
-        <v>15.324</v>
+        <v>15.817</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="4"/>
-        <v>13.506</v>
+        <v>13.092000000000001</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>2.2871641791044777</v>
+        <v>1.9091128545564273</v>
       </c>
       <c r="J40" s="17"/>
     </row>
@@ -1990,31 +1981,31 @@
         <v>48</v>
       </c>
       <c r="B41" s="5">
-        <v>177.61</v>
+        <v>131.93</v>
       </c>
       <c r="C41" s="6">
-        <v>5367</v>
+        <v>5328</v>
       </c>
       <c r="D41" s="7">
-        <v>15170</v>
+        <v>15765</v>
       </c>
       <c r="E41" s="7">
-        <v>12444</v>
+        <v>13280</v>
       </c>
       <c r="F41" s="7">
-        <v>8285</v>
+        <v>11332</v>
       </c>
       <c r="G41" s="8">
         <f t="shared" si="3"/>
-        <v>15.17</v>
+        <v>15.765000000000001</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="4"/>
-        <v>12.444000000000001</v>
+        <v>13.28</v>
       </c>
       <c r="I41" s="9">
         <f t="shared" si="5"/>
-        <v>1.8310199155099578</v>
+        <v>1.3911930815390046</v>
       </c>
       <c r="J41" s="10"/>
     </row>
@@ -2029,25 +2020,25 @@
         <v>5276</v>
       </c>
       <c r="D42" s="14">
-        <v>14782</v>
+        <v>15095</v>
       </c>
       <c r="E42" s="14">
-        <v>12417</v>
+        <v>13065</v>
       </c>
       <c r="F42" s="14">
         <v>9459</v>
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>14.782</v>
+        <v>15.095000000000001</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
-        <v>12.417</v>
+        <v>13.065</v>
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>1.5627444761602707</v>
+        <v>1.5958346548260915</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2056,31 +2047,31 @@
         <v>50</v>
       </c>
       <c r="B43" s="5">
-        <v>58.94</v>
+        <v>60.87</v>
       </c>
       <c r="C43" s="6">
-        <v>3772</v>
+        <v>3801</v>
       </c>
       <c r="D43" s="7">
-        <v>14444</v>
+        <v>14614</v>
       </c>
       <c r="E43" s="7">
-        <v>12879</v>
+        <v>12660</v>
       </c>
       <c r="F43" s="7">
-        <v>10512</v>
+        <v>8017</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
-        <v>14.444000000000001</v>
+        <v>14.614000000000001</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="4"/>
-        <v>12.879</v>
+        <v>12.66</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>1.3740487062404871</v>
+        <v>1.8228763876761882</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2089,19 +2080,19 @@
         <v>51</v>
       </c>
       <c r="B44" s="12">
-        <v>60.19</v>
+        <v>58.94</v>
       </c>
       <c r="C44" s="13">
-        <v>3809</v>
+        <v>3772</v>
       </c>
       <c r="D44" s="14">
         <v>14444</v>
       </c>
       <c r="E44" s="14">
-        <v>12475</v>
+        <v>12879</v>
       </c>
       <c r="F44" s="14">
-        <v>10313</v>
+        <v>10512</v>
       </c>
       <c r="G44" s="15">
         <f t="shared" si="3"/>
@@ -2109,11 +2100,11 @@
       </c>
       <c r="H44" s="15">
         <f t="shared" si="4"/>
-        <v>12.475</v>
+        <v>12.879</v>
       </c>
       <c r="I44" s="16">
         <f t="shared" si="5"/>
-        <v>1.4005623969746921</v>
+        <v>1.3740487062404871</v>
       </c>
       <c r="J44" s="17"/>
     </row>
@@ -2122,31 +2113,31 @@
         <v>52</v>
       </c>
       <c r="B45" s="5">
-        <v>60.87</v>
+        <v>60.19</v>
       </c>
       <c r="C45" s="6">
-        <v>3801</v>
+        <v>3809</v>
       </c>
       <c r="D45" s="7">
-        <v>13967</v>
+        <v>14444</v>
       </c>
       <c r="E45" s="7">
-        <v>12013</v>
+        <v>12475</v>
       </c>
       <c r="F45" s="7">
-        <v>8017</v>
+        <v>10313</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="3"/>
-        <v>13.967000000000001</v>
+        <v>14.444000000000001</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="4"/>
-        <v>12.013</v>
+        <v>12.475</v>
       </c>
       <c r="I45" s="9">
         <f t="shared" si="5"/>
-        <v>1.7421728826244232</v>
+        <v>1.4005623969746921</v>
       </c>
       <c r="J45" s="10"/>
     </row>
@@ -2161,25 +2152,25 @@
         <v>4466</v>
       </c>
       <c r="D46" s="14">
-        <v>13565</v>
+        <v>14213</v>
       </c>
       <c r="E46" s="14">
-        <v>11110</v>
+        <v>11747</v>
       </c>
       <c r="F46" s="14">
         <v>7792</v>
       </c>
       <c r="G46" s="15">
         <f t="shared" si="3"/>
-        <v>13.565</v>
+        <v>14.212999999999999</v>
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
-        <v>11.11</v>
+        <v>11.747</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
-        <v>1.740888090349076</v>
+        <v>1.8240503080082136</v>
       </c>
       <c r="J46" s="17"/>
     </row>
@@ -2188,31 +2179,31 @@
         <v>54</v>
       </c>
       <c r="B47" s="5">
-        <v>59.61</v>
+        <v>59.79</v>
       </c>
       <c r="C47" s="6">
-        <v>3784</v>
+        <v>3770</v>
       </c>
       <c r="D47" s="7">
-        <v>13334</v>
+        <v>13544</v>
       </c>
       <c r="E47" s="7">
-        <v>12013</v>
+        <v>12254</v>
       </c>
       <c r="F47" s="7">
-        <v>9228</v>
+        <v>9014</v>
       </c>
       <c r="G47" s="8">
         <f t="shared" si="3"/>
-        <v>13.334</v>
+        <v>13.544</v>
       </c>
       <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>12.013</v>
+        <v>12.254</v>
       </c>
       <c r="I47" s="9">
         <f t="shared" si="5"/>
-        <v>1.4449501517121803</v>
+        <v>1.5025515864211227</v>
       </c>
       <c r="J47" s="10"/>
     </row>
@@ -2221,31 +2212,31 @@
         <v>55</v>
       </c>
       <c r="B48" s="12">
-        <v>124</v>
+        <v>59.61</v>
       </c>
       <c r="C48" s="13">
-        <v>4814</v>
+        <v>3784</v>
       </c>
       <c r="D48" s="14">
-        <v>13306</v>
+        <v>13544</v>
       </c>
       <c r="E48" s="14">
-        <v>11669</v>
+        <v>12660</v>
       </c>
       <c r="F48" s="14">
-        <v>9977</v>
+        <v>9228</v>
       </c>
       <c r="G48" s="15">
         <f t="shared" si="3"/>
-        <v>13.305999999999999</v>
+        <v>13.544</v>
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>11.669</v>
+        <v>12.66</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
-        <v>1.3336674351007316</v>
+        <v>1.4677069787602948</v>
       </c>
       <c r="J48" s="17"/>
     </row>
@@ -2254,31 +2245,31 @@
         <v>56</v>
       </c>
       <c r="B49" s="5">
-        <v>59.79</v>
+        <v>124</v>
       </c>
       <c r="C49" s="6">
-        <v>3770</v>
+        <v>4814</v>
       </c>
       <c r="D49" s="7">
-        <v>13215</v>
+        <v>13306</v>
       </c>
       <c r="E49" s="7">
-        <v>11607</v>
+        <v>11669</v>
       </c>
       <c r="F49" s="7">
-        <v>9014</v>
+        <v>9977</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="3"/>
-        <v>13.215</v>
+        <v>13.305999999999999</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
-        <v>11.606999999999999</v>
+        <v>11.669</v>
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
-        <v>1.4660528067450633</v>
+        <v>1.3336674351007316</v>
       </c>
       <c r="J49" s="10"/>
     </row>
@@ -2293,7 +2284,7 @@
         <v>4554</v>
       </c>
       <c r="D50" s="14">
-        <v>12814</v>
+        <v>13138</v>
       </c>
       <c r="E50" s="14">
         <v>10936</v>
@@ -2303,7 +2294,7 @@
       </c>
       <c r="G50" s="15">
         <f t="shared" si="3"/>
-        <v>12.814</v>
+        <v>13.138</v>
       </c>
       <c r="H50" s="15">
         <f t="shared" si="4"/>
@@ -2311,7 +2302,7 @@
       </c>
       <c r="I50" s="16">
         <f t="shared" si="5"/>
-        <v>1.4639552153547355</v>
+        <v>1.5009710956243574</v>
       </c>
       <c r="J50" s="17"/>
     </row>
@@ -2486,19 +2477,19 @@
       </c>
       <c r="B57" s="19">
         <f>SUM(B5:B55)</f>
-        <v>6880.8099999999986</v>
+        <v>6880.8099999999995</v>
       </c>
       <c r="D57" s="20">
         <f>MAX(D5:D55)</f>
-        <v>24759</v>
+        <v>25406</v>
       </c>
       <c r="G57" s="21">
         <f>IFERROR(MAX(G5:G55),"")</f>
-        <v>24.759</v>
+        <v>25.405999999999999</v>
       </c>
       <c r="I57" s="22">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
-        <v>1.584011570234338</v>
+        <v>1.6169110795833495</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072D8A2F-9FC6-45F4-B10D-D8FD535ED400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03094E01-5416-4059-84C4-74FA8C121BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -313,49 +313,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03094E01-5416-4059-84C4-74FA8C121BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0B340C-E800-4D97-9B16-8FDC5BF6FF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -210,6 +210,9 @@
     <t>T-11A</t>
   </si>
   <si>
+    <t>T-29</t>
+  </si>
+  <si>
     <t>T-27</t>
   </si>
   <si>
@@ -220,9 +223,6 @@
   </si>
   <si>
     <t>T-28</t>
-  </si>
-  <si>
-    <t>T-29</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -2320,31 +2320,31 @@
         <v>58</v>
       </c>
       <c r="B51" s="5">
-        <v>70.98</v>
+        <v>75.31</v>
       </c>
       <c r="C51" s="6">
-        <v>3651</v>
+        <v>3891</v>
       </c>
       <c r="D51" s="7">
-        <v>10821</v>
+        <v>12585</v>
       </c>
       <c r="E51" s="7">
-        <v>8572</v>
+        <v>9673</v>
       </c>
       <c r="F51" s="7">
-        <v>7484</v>
+        <v>6142</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="3"/>
-        <v>10.821</v>
+        <v>12.585000000000001</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="4"/>
-        <v>8.5719999999999992</v>
+        <v>9.673</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="5"/>
-        <v>1.4458845537145912</v>
+        <v>2.0490068381634647</v>
       </c>
       <c r="J51" s="10"/>
     </row>
@@ -2353,31 +2353,31 @@
         <v>59</v>
       </c>
       <c r="B52" s="12">
-        <v>19.78</v>
+        <v>70.98</v>
       </c>
       <c r="C52" s="13">
-        <v>2018</v>
+        <v>3651</v>
       </c>
       <c r="D52" s="14">
-        <v>10444</v>
+        <v>11405</v>
       </c>
       <c r="E52" s="14">
-        <v>9670</v>
+        <v>8572</v>
       </c>
       <c r="F52" s="14">
-        <v>8848</v>
+        <v>7484</v>
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>10.444000000000001</v>
+        <v>11.404999999999999</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
-        <v>9.67</v>
+        <v>8.5719999999999992</v>
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>1.1803797468354431</v>
+        <v>1.5239176910742918</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2386,31 +2386,31 @@
         <v>60</v>
       </c>
       <c r="B53" s="5">
-        <v>18.11</v>
+        <v>19.78</v>
       </c>
       <c r="C53" s="6">
-        <v>1911</v>
+        <v>2018</v>
       </c>
       <c r="D53" s="7">
-        <v>10061</v>
+        <v>10444</v>
       </c>
       <c r="E53" s="7">
-        <v>9574</v>
+        <v>9670</v>
       </c>
       <c r="F53" s="7">
-        <v>8310</v>
+        <v>8848</v>
       </c>
       <c r="G53" s="8">
         <f t="shared" si="3"/>
-        <v>10.061</v>
+        <v>10.444000000000001</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="4"/>
-        <v>9.5739999999999998</v>
+        <v>9.67</v>
       </c>
       <c r="I53" s="9">
         <f t="shared" si="5"/>
-        <v>1.2107099879663057</v>
+        <v>1.1803797468354431</v>
       </c>
       <c r="J53" s="10"/>
     </row>
@@ -2419,31 +2419,31 @@
         <v>61</v>
       </c>
       <c r="B54" s="12">
-        <v>88.51</v>
+        <v>18.11</v>
       </c>
       <c r="C54" s="13">
-        <v>3848</v>
+        <v>1911</v>
       </c>
       <c r="D54" s="14">
-        <v>9202</v>
+        <v>10061</v>
       </c>
       <c r="E54" s="14">
-        <v>8639</v>
+        <v>9574</v>
       </c>
       <c r="F54" s="14">
-        <v>6820</v>
+        <v>8310</v>
       </c>
       <c r="G54" s="15">
         <f t="shared" si="3"/>
-        <v>9.202</v>
+        <v>10.061</v>
       </c>
       <c r="H54" s="15">
         <f t="shared" si="4"/>
-        <v>8.6389999999999993</v>
+        <v>9.5739999999999998</v>
       </c>
       <c r="I54" s="16">
         <f t="shared" si="5"/>
-        <v>1.3492668621700881</v>
+        <v>1.2107099879663057</v>
       </c>
       <c r="J54" s="17"/>
     </row>
@@ -2452,31 +2452,31 @@
         <v>62</v>
       </c>
       <c r="B55" s="5">
-        <v>75.31</v>
+        <v>88.51</v>
       </c>
       <c r="C55" s="6">
-        <v>3891</v>
+        <v>3848</v>
       </c>
       <c r="D55" s="7">
-        <v>9138</v>
+        <v>9724</v>
       </c>
       <c r="E55" s="7">
-        <v>7433</v>
+        <v>8639</v>
       </c>
       <c r="F55" s="7">
-        <v>6142</v>
+        <v>6820</v>
       </c>
       <c r="G55" s="8">
         <f t="shared" si="3"/>
-        <v>9.1379999999999999</v>
+        <v>9.7240000000000002</v>
       </c>
       <c r="H55" s="8">
         <f t="shared" si="4"/>
-        <v>7.4329999999999998</v>
+        <v>8.6389999999999993</v>
       </c>
       <c r="I55" s="9">
         <f t="shared" si="5"/>
-        <v>1.4877889938130902</v>
+        <v>1.4258064516129032</v>
       </c>
       <c r="J55" s="10"/>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="I57" s="22">
         <f>IFERROR(AVERAGE(I5:I55),"")</f>
-        <v>1.6169110795833495</v>
+        <v>1.6309461888216414</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PPEDRA_distancias.xlsx
+++ b/FAZENDA_PPEDRA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0B340C-E800-4D97-9B16-8FDC5BF6FF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03683081-1C35-4C76-8E09-0765C2D05F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -313,58 +313,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
